--- a/data/input/Inventory_snapshot_WM.xlsx
+++ b/data/input/Inventory_snapshot_WM.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 8\White_Mulberry\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 9\White_Mulberry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F93F852F-CD6F-4422-954A-AB8518F5A336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{716C67A1-9D3B-4408-9B90-8753AAEF0265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D49B0F4C-5F9E-467E-8AD9-9E638F42404F}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$167</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1153" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1390" uniqueCount="247">
   <si>
     <t>SKU</t>
   </si>
@@ -75,63 +75,216 @@
     <t>Week</t>
   </si>
   <si>
+    <t>Amazon</t>
+  </si>
+  <si>
+    <t>1p</t>
+  </si>
+  <si>
+    <t>FBA79476</t>
+  </si>
+  <si>
+    <t>FBA79478</t>
+  </si>
+  <si>
+    <t>FBA79612</t>
+  </si>
+  <si>
+    <t>FBA79613</t>
+  </si>
+  <si>
+    <t>FBA79614</t>
+  </si>
+  <si>
+    <t>FBA79615</t>
+  </si>
+  <si>
+    <t>FBA79616</t>
+  </si>
+  <si>
+    <t>FBA79617</t>
+  </si>
+  <si>
+    <t>FBA76382</t>
+  </si>
+  <si>
+    <t>FBA76383</t>
+  </si>
+  <si>
+    <t>FBA76388</t>
+  </si>
+  <si>
+    <t>FBA76415</t>
+  </si>
+  <si>
+    <t>FBA76416</t>
+  </si>
+  <si>
+    <t>FBA76417</t>
+  </si>
+  <si>
+    <t>FBA76418</t>
+  </si>
+  <si>
+    <t>FBA76765</t>
+  </si>
+  <si>
+    <t>FBA79164</t>
+  </si>
+  <si>
+    <t>FBA79165</t>
+  </si>
+  <si>
+    <t>FBA79167</t>
+  </si>
+  <si>
+    <t>FBA79176</t>
+  </si>
+  <si>
+    <t>FBA79177</t>
+  </si>
+  <si>
+    <t>FBA79178</t>
+  </si>
+  <si>
+    <t>FBA79179</t>
+  </si>
+  <si>
+    <t>FBA79433</t>
+  </si>
+  <si>
+    <t>FBA79435</t>
+  </si>
+  <si>
+    <t>FBA79477</t>
+  </si>
+  <si>
+    <t>FBA79479</t>
+  </si>
+  <si>
+    <t>FBA79658</t>
+  </si>
+  <si>
+    <t>FBA79659</t>
+  </si>
+  <si>
+    <t>FBA79660</t>
+  </si>
+  <si>
+    <t>FBA79661</t>
+  </si>
+  <si>
+    <t>FBA79662</t>
+  </si>
+  <si>
+    <t>FBA79663</t>
+  </si>
+  <si>
+    <t>FBA79667</t>
+  </si>
+  <si>
+    <t>FBA79668</t>
+  </si>
+  <si>
+    <t>FBA79669</t>
+  </si>
+  <si>
+    <t>FBA79670</t>
+  </si>
+  <si>
+    <t>FBK76387</t>
+  </si>
+  <si>
+    <t>FBK76764</t>
+  </si>
+  <si>
+    <t>FBA79790</t>
+  </si>
+  <si>
+    <t>B0DB5VG39T</t>
+  </si>
+  <si>
+    <t>B0DB5W4TCP</t>
+  </si>
+  <si>
+    <t>B0DP2WC5VW</t>
+  </si>
+  <si>
+    <t>B0DP2VVRND</t>
+  </si>
+  <si>
+    <t>B0DP313R77</t>
+  </si>
+  <si>
+    <t>B0DP2Z5DQ9</t>
+  </si>
+  <si>
     <t>B0DP3194QN</t>
   </si>
   <si>
-    <t>B0DB5VG39T</t>
-  </si>
-  <si>
     <t>B0DP32F346</t>
   </si>
   <si>
-    <t>B0DP2VVRND</t>
+    <t>B0FN4DSQ6P</t>
+  </si>
+  <si>
+    <t>B0BF4T7SWK</t>
+  </si>
+  <si>
+    <t>B0BF4TKQKN</t>
+  </si>
+  <si>
+    <t>B0BF4VRJJ1</t>
+  </si>
+  <si>
+    <t>B0BFWD6SNF</t>
+  </si>
+  <si>
+    <t>B0BFW59TRG</t>
+  </si>
+  <si>
+    <t>B0BFVMDJ2K</t>
+  </si>
+  <si>
+    <t>B0BFVNS8HS</t>
+  </si>
+  <si>
+    <t>B0BMQQQ7YD</t>
+  </si>
+  <si>
+    <t>B0CPFN27Z2</t>
+  </si>
+  <si>
+    <t>B0CPFPT6DZ</t>
+  </si>
+  <si>
+    <t>B0CPFS24ML</t>
+  </si>
+  <si>
+    <t>B0CPT25SD8</t>
+  </si>
+  <si>
+    <t>B0CPT34B2L</t>
+  </si>
+  <si>
+    <t>B0CPT2NY5M</t>
+  </si>
+  <si>
+    <t>B0CPT3Q25C</t>
+  </si>
+  <si>
+    <t>B0DC3JRBW1</t>
+  </si>
+  <si>
+    <t>B0DC3NPKGF</t>
+  </si>
+  <si>
+    <t>B0DB5VVPSB</t>
   </si>
   <si>
     <t>B0DB5YTQZV</t>
   </si>
   <si>
-    <t>B0DP2WC5VW</t>
-  </si>
-  <si>
-    <t>B0BF4T7SWK</t>
-  </si>
-  <si>
-    <t>B0BFWD6SNF</t>
-  </si>
-  <si>
-    <t>B0BFW59TRG</t>
-  </si>
-  <si>
-    <t>B0BFVMDJ2K</t>
-  </si>
-  <si>
-    <t>B0BFVNS8HS</t>
-  </si>
-  <si>
-    <t>B0BMQQQ7YD</t>
-  </si>
-  <si>
-    <t>B0CPFN27Z2</t>
-  </si>
-  <si>
-    <t>B0CPFPT6DZ</t>
-  </si>
-  <si>
-    <t>B0CPFS24ML</t>
-  </si>
-  <si>
-    <t>B0CPT2YJX2</t>
-  </si>
-  <si>
-    <t>B0CPT34B2L</t>
-  </si>
-  <si>
-    <t>B0CPT2NY5M</t>
-  </si>
-  <si>
-    <t>B0CPT3Q25C</t>
-  </si>
-  <si>
     <t>B0DQ1PKNSP</t>
   </si>
   <si>
@@ -147,24 +300,24 @@
     <t>B0DQ4YWSMC</t>
   </si>
   <si>
+    <t>B0DQPFL835</t>
+  </si>
+  <si>
     <t>B0DQPK7MFH</t>
   </si>
   <si>
+    <t>B0DQPLMQQ7</t>
+  </si>
+  <si>
+    <t>B0DQPGLK2T</t>
+  </si>
+  <si>
     <t>B0BF4S7V8C</t>
   </si>
   <si>
     <t>B0BMV1WPHL</t>
   </si>
   <si>
-    <t>Amazon</t>
-  </si>
-  <si>
-    <t>B0DB5W4TCP</t>
-  </si>
-  <si>
-    <t>B0DP2Z5DQ9</t>
-  </si>
-  <si>
     <t>B0FN4FHH5Y</t>
   </si>
   <si>
@@ -177,9 +330,6 @@
     <t>B0FN4D3C89</t>
   </si>
   <si>
-    <t>B0FN4DSQ6P</t>
-  </si>
-  <si>
     <t>B0FN4HDM6Z</t>
   </si>
   <si>
@@ -189,168 +339,9 @@
     <t>B0FN81FD8M</t>
   </si>
   <si>
-    <t>B0DP313R77</t>
-  </si>
-  <si>
-    <t>B0BF4TKQKN</t>
-  </si>
-  <si>
-    <t>B0CPT25SD8</t>
-  </si>
-  <si>
-    <t>B0DC3JRBW1</t>
-  </si>
-  <si>
-    <t>B0DQPFL835</t>
-  </si>
-  <si>
-    <t>B0DQPLMQQ7</t>
-  </si>
-  <si>
-    <t>B0DQPGLK2T</t>
-  </si>
-  <si>
-    <t>B0FHVWHQHR</t>
-  </si>
-  <si>
-    <t>B0DB5VVPSB</t>
-  </si>
-  <si>
-    <t>1p</t>
-  </si>
-  <si>
     <t>White Mulberry</t>
   </si>
   <si>
-    <t>B0BF4VRJJ1</t>
-  </si>
-  <si>
-    <t>B0DC3NPKGF</t>
-  </si>
-  <si>
-    <t>FBA79476</t>
-  </si>
-  <si>
-    <t>FBA79478</t>
-  </si>
-  <si>
-    <t>FBA79612</t>
-  </si>
-  <si>
-    <t>FBA79613</t>
-  </si>
-  <si>
-    <t>FBA79614</t>
-  </si>
-  <si>
-    <t>FBA79615</t>
-  </si>
-  <si>
-    <t>FBA79616</t>
-  </si>
-  <si>
-    <t>FBA79617</t>
-  </si>
-  <si>
-    <t>FBA76382</t>
-  </si>
-  <si>
-    <t>FBA76383</t>
-  </si>
-  <si>
-    <t>FBA76388</t>
-  </si>
-  <si>
-    <t>FBA76415</t>
-  </si>
-  <si>
-    <t>FBA76416</t>
-  </si>
-  <si>
-    <t>FBA76417</t>
-  </si>
-  <si>
-    <t>FBA76418</t>
-  </si>
-  <si>
-    <t>FBA76765</t>
-  </si>
-  <si>
-    <t>FBA79164</t>
-  </si>
-  <si>
-    <t>FBA79165</t>
-  </si>
-  <si>
-    <t>FBA79167</t>
-  </si>
-  <si>
-    <t>FBA79176</t>
-  </si>
-  <si>
-    <t>FBA79177</t>
-  </si>
-  <si>
-    <t>FBA79178</t>
-  </si>
-  <si>
-    <t>FBA79179</t>
-  </si>
-  <si>
-    <t>FBA79433</t>
-  </si>
-  <si>
-    <t>FBA79435</t>
-  </si>
-  <si>
-    <t>FBA79477</t>
-  </si>
-  <si>
-    <t>FBA79479</t>
-  </si>
-  <si>
-    <t>FBA79658</t>
-  </si>
-  <si>
-    <t>FBA79659</t>
-  </si>
-  <si>
-    <t>FBA79660</t>
-  </si>
-  <si>
-    <t>FBA79661</t>
-  </si>
-  <si>
-    <t>FBA79662</t>
-  </si>
-  <si>
-    <t>FBA79663</t>
-  </si>
-  <si>
-    <t>FBA79667</t>
-  </si>
-  <si>
-    <t>FBA79668</t>
-  </si>
-  <si>
-    <t>FBA79669</t>
-  </si>
-  <si>
-    <t>FBA79670</t>
-  </si>
-  <si>
-    <t>FBK76387</t>
-  </si>
-  <si>
-    <t>FBK76764</t>
-  </si>
-  <si>
-    <t>FBA79790</t>
-  </si>
-  <si>
-    <t>Week 8</t>
-  </si>
-  <si>
     <t>WM-MD09-BK</t>
   </si>
   <si>
@@ -606,15 +597,30 @@
     <t>AMPM</t>
   </si>
   <si>
-    <t>B2B - AMPM</t>
-  </si>
-  <si>
     <t>GS1ML</t>
   </si>
   <si>
+    <t>HA1ML</t>
+  </si>
+  <si>
+    <t>B2B-AMPM</t>
+  </si>
+  <si>
     <t>YNT</t>
   </si>
   <si>
+    <t>Na</t>
+  </si>
+  <si>
+    <t>WM-LOD-BK</t>
+  </si>
+  <si>
+    <t>WM-LOD-IN</t>
+  </si>
+  <si>
+    <t>POSS-01</t>
+  </si>
+  <si>
     <t>1P</t>
   </si>
   <si>
@@ -627,13 +633,13 @@
     <t>Dispatch Partner</t>
   </si>
   <si>
+    <t>Week 9</t>
+  </si>
+  <si>
     <t>FBA79789</t>
   </si>
   <si>
-    <t>WM-LOD-BK</t>
-  </si>
-  <si>
-    <t>WM-LOD-IN</t>
+    <t>B0DQPLCZ3G</t>
   </si>
   <si>
     <t>FBA79784</t>
@@ -642,9 +648,6 @@
     <t>FBA79786</t>
   </si>
   <si>
-    <t>POSS-01</t>
-  </si>
-  <si>
     <t>FBA79787</t>
   </si>
   <si>
@@ -663,44 +666,125 @@
     <t>FBA76391</t>
   </si>
   <si>
+    <t>B0BF4WQNJR</t>
+  </si>
+  <si>
     <t>FBA79664</t>
   </si>
   <si>
+    <t>B0DQPKMRN1</t>
+  </si>
+  <si>
     <t>FBA76389</t>
   </si>
   <si>
+    <t>B0BF4XF7SD</t>
+  </si>
+  <si>
     <t>FBA76384</t>
   </si>
   <si>
+    <t>B0BF4VWQXG</t>
+  </si>
+  <si>
     <t>FBA76865</t>
   </si>
   <si>
+    <t>B0BF4Y92MW</t>
+  </si>
+  <si>
     <t>FBA76385</t>
   </si>
   <si>
+    <t>B0BF4WD8Z8</t>
+  </si>
+  <si>
     <t>FBA76386</t>
   </si>
   <si>
+    <t>B0BF51HCY4</t>
+  </si>
+  <si>
     <t>FBA79666</t>
   </si>
   <si>
+    <t>B0DQPG9FSN</t>
+  </si>
+  <si>
     <t>FBA76419</t>
   </si>
   <si>
+    <t>B0BFW5K3F1</t>
+  </si>
+  <si>
     <t>FBA79434</t>
   </si>
   <si>
+    <t>B0DC3SJMZ6</t>
+  </si>
+  <si>
     <t>FBA79785</t>
   </si>
   <si>
+    <t>B0FN4HDBN5</t>
+  </si>
+  <si>
+    <t>B0FN4GJ9S1</t>
+  </si>
+  <si>
     <t>FBA79610</t>
+  </si>
+  <si>
+    <t>B0DSG4F8D9</t>
+  </si>
+  <si>
+    <t>FBA79608</t>
+  </si>
+  <si>
+    <t>B0DSG2BD4H</t>
+  </si>
+  <si>
+    <t>Monitor Arm</t>
+  </si>
+  <si>
+    <t>TV Wall Mount</t>
+  </si>
+  <si>
+    <t>Desk-Adjustable</t>
+  </si>
+  <si>
+    <t>Manual</t>
+  </si>
+  <si>
+    <t>Motorized</t>
+  </si>
+  <si>
+    <t>Desk</t>
+  </si>
+  <si>
+    <t>L-Shaped Desk</t>
+  </si>
+  <si>
+    <t>USB-Motorized</t>
+  </si>
+  <si>
+    <t>Gaming Desk</t>
+  </si>
+  <si>
+    <t>To Check</t>
+  </si>
+  <si>
+    <t>POS Stand</t>
+  </si>
+  <si>
+    <t>Table</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -722,14 +806,25 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color indexed="8"/>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Bookman Old Style"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -739,6 +834,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -767,12 +868,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -780,13 +880,30 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2" xr:uid="{E7D5D066-AB08-4CB1-9280-450D4556FEF5}"/>
     <cellStyle name="Normal 6" xfId="1" xr:uid="{E5F241CE-C0FC-4730-81C9-F1901EB82A3C}"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="76">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -843,6 +960,720 @@
       </font>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
@@ -1187,19 +2018,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}">
-  <dimension ref="A1:L168"/>
+  <dimension ref="A1:L167"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="23.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12" style="1" customWidth="1"/>
     <col min="11" max="11" width="9.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="16384" width="8.88671875" style="1"/>
@@ -1245,4356 +2076,5246 @@
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>60</v>
+        <v>54</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="I2">
         <v>3</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>64</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" t="s">
-        <v>60</v>
+        <v>55</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" t="s">
-        <v>60</v>
+        <v>56</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>60</v>
+        <v>57</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" t="s">
-        <v>60</v>
+        <v>58</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" t="s">
-        <v>60</v>
+        <v>59</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C8" t="s">
-        <v>60</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="K8" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" t="s">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="I9">
         <v>2</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" t="s">
-        <v>60</v>
+        <v>62</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>236</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>71</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" t="s">
-        <v>60</v>
+        <v>63</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>238</v>
       </c>
       <c r="I11">
         <v>8</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C12" t="s">
-        <v>60</v>
+        <v>64</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>239</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
-      </c>
-      <c r="C13" t="s">
-        <v>60</v>
+        <v>65</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>239</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" t="s">
-        <v>60</v>
+        <v>66</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="I14">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" t="s">
-        <v>60</v>
+        <v>67</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>197</v>
+        <v>191</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="I15">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>76</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" t="s">
-        <v>60</v>
+        <v>68</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="I16">
-        <v>127</v>
+        <v>239</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" t="s">
-        <v>60</v>
+        <v>69</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>198</v>
+        <v>192</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="I17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="B18" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" t="s">
-        <v>60</v>
+        <v>70</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>239</v>
       </c>
       <c r="I18">
         <v>6</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" t="s">
-        <v>60</v>
+        <v>71</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>242</v>
       </c>
       <c r="I19">
         <v>3</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" t="s">
-        <v>60</v>
+        <v>72</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>242</v>
       </c>
       <c r="I20">
         <v>1</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" t="s">
-        <v>60</v>
+        <v>73</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>243</v>
       </c>
       <c r="I21">
-        <v>150</v>
+        <v>63</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>97</v>
+        <v>48</v>
       </c>
       <c r="B22" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" t="s">
-        <v>60</v>
+        <v>200</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>244</v>
       </c>
       <c r="I22">
         <v>2</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>82</v>
+        <v>33</v>
       </c>
       <c r="B23" t="s">
-        <v>52</v>
-      </c>
-      <c r="C23" t="s">
-        <v>60</v>
+        <v>74</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>238</v>
       </c>
       <c r="I23">
         <v>0</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>83</v>
+        <v>34</v>
       </c>
       <c r="B24" t="s">
-        <v>28</v>
-      </c>
-      <c r="C24" t="s">
-        <v>60</v>
+        <v>75</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>239</v>
       </c>
       <c r="I24">
         <v>0</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="B25" t="s">
-        <v>29</v>
-      </c>
-      <c r="C25" t="s">
-        <v>60</v>
+        <v>76</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>239</v>
       </c>
       <c r="I25">
         <v>13</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="B26" t="s">
-        <v>30</v>
-      </c>
-      <c r="C26" t="s">
-        <v>60</v>
+        <v>77</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>239</v>
       </c>
       <c r="I26">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>86</v>
+        <v>37</v>
       </c>
       <c r="B27" t="s">
-        <v>53</v>
-      </c>
-      <c r="C27" t="s">
-        <v>60</v>
+        <v>78</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>239</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>87</v>
+        <v>38</v>
       </c>
       <c r="B28" t="s">
-        <v>62</v>
-      </c>
-      <c r="C28" t="s">
-        <v>60</v>
+        <v>79</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>242</v>
       </c>
       <c r="I28">
         <v>0</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>58</v>
-      </c>
-      <c r="C29" t="s">
-        <v>60</v>
+        <v>80</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="I29">
         <v>0</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>89</v>
+        <v>40</v>
       </c>
       <c r="B30" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" t="s">
-        <v>60</v>
+        <v>81</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="I30">
         <v>0</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="B31" t="s">
-        <v>17</v>
-      </c>
-      <c r="C31" t="s">
-        <v>60</v>
+        <v>58</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="I31">
         <v>0</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="B32" t="s">
-        <v>50</v>
-      </c>
-      <c r="C32" t="s">
         <v>60</v>
       </c>
+      <c r="C32" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="D32" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="I32">
         <v>0</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="B33" t="s">
+        <v>82</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="I33">
+        <v>25</v>
+      </c>
+      <c r="J33" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C33" t="s">
-        <v>60</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="I33">
-        <v>0</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="K33" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="B34" t="s">
-        <v>31</v>
-      </c>
-      <c r="C34" t="s">
-        <v>60</v>
+        <v>83</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>238</v>
       </c>
       <c r="I34">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>91</v>
+        <v>43</v>
       </c>
       <c r="B35" t="s">
-        <v>32</v>
-      </c>
-      <c r="C35" t="s">
-        <v>60</v>
+        <v>84</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>108</v>
+        <v>172</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>239</v>
       </c>
       <c r="I35">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="B36" t="s">
-        <v>33</v>
-      </c>
-      <c r="C36" t="s">
-        <v>60</v>
+        <v>85</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>239</v>
       </c>
       <c r="I36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>93</v>
+        <v>45</v>
       </c>
       <c r="B37" t="s">
-        <v>34</v>
-      </c>
-      <c r="C37" t="s">
-        <v>60</v>
+        <v>86</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>239</v>
       </c>
       <c r="I37">
-        <v>3</v>
+        <v>63</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>94</v>
+        <v>46</v>
       </c>
       <c r="B38" t="s">
-        <v>35</v>
-      </c>
-      <c r="C38" t="s">
-        <v>60</v>
+        <v>87</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>177</v>
+        <v>165</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="I38">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="B39" t="s">
-        <v>54</v>
-      </c>
-      <c r="C39" t="s">
-        <v>60</v>
+        <v>88</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>168</v>
+        <v>161</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="I39">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="B40" t="s">
-        <v>36</v>
-      </c>
-      <c r="C40" t="s">
-        <v>60</v>
+        <v>200</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>244</v>
       </c>
       <c r="I40">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>97</v>
+        <v>49</v>
       </c>
       <c r="B41" t="s">
-        <v>27</v>
-      </c>
-      <c r="C41" t="s">
-        <v>60</v>
+        <v>89</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="I41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>98</v>
+        <v>50</v>
       </c>
       <c r="B42" t="s">
-        <v>55</v>
-      </c>
-      <c r="C42" t="s">
-        <v>60</v>
+        <v>90</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="I42">
         <v>0</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="43" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>99</v>
+        <v>51</v>
       </c>
       <c r="B43" t="s">
-        <v>56</v>
-      </c>
-      <c r="C43" t="s">
-        <v>60</v>
+        <v>91</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>167</v>
+        <v>103</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>238</v>
       </c>
       <c r="I43">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="B44" t="s">
-        <v>37</v>
-      </c>
-      <c r="C44" t="s">
-        <v>60</v>
+        <v>92</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>106</v>
+        <v>133</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>238</v>
       </c>
       <c r="I44">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>101</v>
+        <v>14</v>
       </c>
       <c r="B45" t="s">
-        <v>38</v>
-      </c>
-      <c r="C45" t="s">
-        <v>60</v>
+        <v>54</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>136</v>
+        <v>157</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="I45">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="46" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="B46" t="s">
-        <v>13</v>
-      </c>
-      <c r="C46" t="s">
-        <v>60</v>
+        <v>80</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="I46">
-        <v>99</v>
+        <v>40</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>88</v>
+        <v>15</v>
       </c>
       <c r="B47" t="s">
-        <v>58</v>
-      </c>
-      <c r="C47" t="s">
-        <v>60</v>
+        <v>55</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="I47">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="B48" t="s">
+        <v>81</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="I48">
         <v>40</v>
       </c>
-      <c r="C48" t="s">
-        <v>60</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="I48">
-        <v>134</v>
-      </c>
       <c r="J48" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="49" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>89</v>
+        <v>16</v>
       </c>
       <c r="B49" t="s">
-        <v>16</v>
-      </c>
-      <c r="C49" t="s">
-        <v>60</v>
+        <v>56</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>163</v>
+        <v>166</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="I49">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="50" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="B50" t="s">
-        <v>17</v>
-      </c>
-      <c r="C50" t="s">
-        <v>60</v>
+        <v>57</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="I50">
-        <v>120</v>
+        <v>3</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="B51" t="s">
-        <v>15</v>
-      </c>
-      <c r="C51" t="s">
-        <v>60</v>
+        <v>58</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="I51">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="52" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>67</v>
+        <v>19</v>
       </c>
       <c r="B52" t="s">
-        <v>50</v>
-      </c>
-      <c r="C52" t="s">
-        <v>60</v>
+        <v>59</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="I52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="53" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="B53" t="s">
-        <v>41</v>
-      </c>
-      <c r="C53" t="s">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="I53">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>70</v>
-      </c>
-      <c r="B54" t="s">
-        <v>14</v>
-      </c>
-      <c r="C54" t="s">
-        <v>60</v>
+      <c r="A54" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B54" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="I54">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="55" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>102</v>
+        <v>32</v>
       </c>
       <c r="B55" t="s">
-        <v>57</v>
-      </c>
-      <c r="C55" t="s">
-        <v>60</v>
+        <v>73</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>186</v>
+        <v>153</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>243</v>
       </c>
       <c r="I55">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="56" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>81</v>
+        <v>201</v>
       </c>
       <c r="B56" t="s">
-        <v>26</v>
-      </c>
-      <c r="C56" t="s">
-        <v>60</v>
+        <v>93</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>156</v>
+        <v>175</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>245</v>
       </c>
       <c r="I56">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="57" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B57" t="s">
-        <v>42</v>
-      </c>
-      <c r="C57" t="s">
-        <v>60</v>
+        <v>94</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>178</v>
+        <v>193</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>245</v>
       </c>
       <c r="I57">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="58" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B58" t="s">
-        <v>43</v>
-      </c>
-      <c r="C58" t="s">
-        <v>60</v>
+        <v>95</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>201</v>
+        <v>178</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>236</v>
       </c>
       <c r="I58">
-        <v>196</v>
+        <v>68</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="59" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B59" t="s">
-        <v>44</v>
-      </c>
-      <c r="C59" t="s">
-        <v>60</v>
+        <v>96</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>181</v>
       </c>
+      <c r="E59" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>236</v>
+      </c>
       <c r="I59">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B60" t="s">
-        <v>45</v>
-      </c>
-      <c r="C60" t="s">
-        <v>60</v>
+        <v>62</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>236</v>
       </c>
       <c r="I60">
-        <v>77</v>
+        <v>180</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="61" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="B61" t="s">
-        <v>46</v>
-      </c>
-      <c r="C61" t="s">
-        <v>60</v>
+        <v>97</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>236</v>
       </c>
       <c r="I61">
-        <v>360</v>
+        <v>72</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="62" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B62" t="s">
-        <v>47</v>
-      </c>
-      <c r="C62" t="s">
-        <v>60</v>
+        <v>98</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>187</v>
+        <v>179</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="I62">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="63" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B63" t="s">
-        <v>48</v>
-      </c>
-      <c r="C63" t="s">
-        <v>60</v>
+        <v>99</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="I63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="64" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>206</v>
+        <v>14</v>
       </c>
       <c r="B64" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C64" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>183</v>
+        <v>157</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="I64">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="65" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="B65" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="C65" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="I65">
         <v>4</v>
       </c>
       <c r="J65" s="1" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="66" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="B66" t="s">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="C66" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="I66">
-        <v>14</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="I66"/>
       <c r="J66" s="1" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="67" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="B67" t="s">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="C67" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>173</v>
+        <v>160</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="I67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="68" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="B68" t="s">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="C68" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>171</v>
+        <v>158</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="I68"/>
       <c r="J68" s="1" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="B69" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C69" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="I69"/>
+        <v>171</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="I69">
+        <v>18</v>
+      </c>
       <c r="J69" s="1" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="70" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>89</v>
+        <v>17</v>
       </c>
       <c r="B70" t="s">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="C70" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>163</v>
+        <v>167</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="I70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="71" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="B71" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C71" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="I71"/>
+        <v>170</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="I71">
+        <v>1</v>
+      </c>
       <c r="J71" s="1" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="72" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="B72" t="s">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="C72" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="I72">
-        <v>2</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="I72"/>
       <c r="J72" s="1" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="73" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="B73" t="s">
-        <v>13</v>
-      </c>
-      <c r="C73" t="s">
-        <v>60</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="I73">
-        <v>7</v>
+        <v>74</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="I73" s="4">
+        <v>0</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>59</v>
+        <v>185</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="74" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="B74" t="s">
-        <v>13</v>
-      </c>
-      <c r="C74" t="s">
-        <v>60</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="I74" s="1">
-        <v>0</v>
+        <v>63</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="I74" s="4">
+        <v>1</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="75" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="B75" t="s">
-        <v>13</v>
-      </c>
-      <c r="C75" t="s">
-        <v>60</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="I75" s="1">
-        <v>1</v>
+        <v>91</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="I75" s="4">
+        <v>0</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="76" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="B76" t="s">
-        <v>13</v>
-      </c>
-      <c r="C76" t="s">
-        <v>60</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="I76" s="1">
-        <v>0</v>
+        <v>82</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D76" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="I76" s="4">
+        <v>14</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="77" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="B77" t="s">
-        <v>13</v>
-      </c>
-      <c r="C77" t="s">
-        <v>60</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="I77" s="1">
+        <v>83</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="I77" s="4">
         <v>14</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="78" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
-        <v>91</v>
-      </c>
-      <c r="B78" t="s">
-        <v>13</v>
-      </c>
-      <c r="C78" t="s">
-        <v>60</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="I78" s="1">
-        <v>14</v>
+      <c r="A78" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B78" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D78" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="I78" s="4">
+        <v>0</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="79" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" t="e">
         <v>#N/A</v>
       </c>
-      <c r="B79" t="s">
-        <v>13</v>
-      </c>
-      <c r="C79" t="s">
-        <v>60</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="I79" s="1">
-        <v>0</v>
+      <c r="B79" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="I79" s="4">
+        <v>15</v>
       </c>
       <c r="J79" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="80" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" t="e">
         <v>#N/A</v>
       </c>
-      <c r="B80" t="s">
-        <v>13</v>
-      </c>
-      <c r="C80" t="s">
-        <v>60</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="I80" s="1">
-        <v>15</v>
+      <c r="B80" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="I80" s="4">
+        <v>0</v>
       </c>
       <c r="J80" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="81" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" t="e">
         <v>#N/A</v>
       </c>
-      <c r="B81" t="s">
-        <v>13</v>
-      </c>
-      <c r="C81" t="s">
-        <v>60</v>
-      </c>
-      <c r="D81" s="1" t="s">
+      <c r="B81" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D81" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="I81" s="4">
+        <v>0</v>
+      </c>
+      <c r="J81" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="K81" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="L81" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>36</v>
+      </c>
+      <c r="B82" t="s">
+        <v>77</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D82" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="I82" s="4">
+        <v>59</v>
+      </c>
+      <c r="J82" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="K82" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="L82" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B83" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D83" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="I81" s="1">
-        <v>0</v>
-      </c>
-      <c r="J81" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="K81" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="L81" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B82" t="s">
-        <v>13</v>
-      </c>
-      <c r="C82" t="s">
-        <v>60</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="I82" s="1">
-        <v>0</v>
-      </c>
-      <c r="J82" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="K82" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="L82" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
-        <v>85</v>
-      </c>
-      <c r="B83" t="s">
-        <v>13</v>
-      </c>
-      <c r="C83" t="s">
-        <v>60</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="I83" s="1">
-        <v>59</v>
+      <c r="I83" s="4">
+        <v>0</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="84" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" t="e">
         <v>#N/A</v>
       </c>
-      <c r="B84" t="s">
-        <v>13</v>
-      </c>
-      <c r="C84" t="s">
-        <v>60</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="I84" s="1">
+      <c r="B84" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D84" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="I84" s="4">
         <v>0</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="85" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" t="e">
         <v>#N/A</v>
       </c>
-      <c r="B85" t="s">
-        <v>13</v>
-      </c>
-      <c r="C85" t="s">
-        <v>60</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="I85" s="1">
+      <c r="B85" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D85" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="I85" s="4">
         <v>0</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="86" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" t="e">
-        <v>#N/A</v>
+      <c r="A86" t="s">
+        <v>23</v>
       </c>
       <c r="B86" t="s">
-        <v>13</v>
-      </c>
-      <c r="C86" t="s">
-        <v>60</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="I86" s="1">
+        <v>64</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D86" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="I86" s="4">
         <v>0</v>
       </c>
       <c r="J86" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="87" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="B87" t="s">
-        <v>13</v>
-      </c>
-      <c r="C87" t="s">
-        <v>60</v>
-      </c>
-      <c r="D87" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D87" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="I87" s="4">
+        <v>0</v>
+      </c>
+      <c r="J87" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="K87" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="L87" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A88" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B88" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D88" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="I88" s="4">
+        <v>0</v>
+      </c>
+      <c r="J88" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="K88" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="L88" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>25</v>
+      </c>
+      <c r="B89" t="s">
+        <v>66</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D89" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="I87" s="1">
-        <v>0</v>
-      </c>
-      <c r="J87" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="K87" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="L87" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
-        <v>73</v>
-      </c>
-      <c r="B88" t="s">
-        <v>13</v>
-      </c>
-      <c r="C88" t="s">
-        <v>60</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="I88" s="1">
-        <v>0</v>
-      </c>
-      <c r="J88" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="K88" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="L88" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="89" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B89" t="s">
-        <v>13</v>
-      </c>
-      <c r="C89" t="s">
-        <v>60</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="I89" s="1">
+      <c r="E89" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="I89" s="4">
         <v>0</v>
       </c>
       <c r="J89" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="90" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>74</v>
+        <v>208</v>
       </c>
       <c r="B90" t="s">
-        <v>13</v>
-      </c>
-      <c r="C90" t="s">
-        <v>60</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="I90" s="1">
+        <v>209</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D90" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="I90" s="4">
         <v>0</v>
       </c>
       <c r="J90" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K90" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="91" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>207</v>
+        <v>30</v>
       </c>
       <c r="B91" t="s">
-        <v>13</v>
-      </c>
-      <c r="C91" t="s">
-        <v>60</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="I91" s="1">
+        <v>71</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D91" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="I91" s="4">
         <v>0</v>
       </c>
       <c r="J91" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="92" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="B92" t="s">
-        <v>13</v>
-      </c>
-      <c r="C92" t="s">
-        <v>60</v>
-      </c>
-      <c r="D92" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D92" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="I92" s="4">
+        <v>0</v>
+      </c>
+      <c r="J92" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="K92" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="L92" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A93" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B93" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D93" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="I93" s="4">
+        <v>0</v>
+      </c>
+      <c r="J93" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="K93" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="L93" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>35</v>
+      </c>
+      <c r="B94" t="s">
+        <v>76</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D94" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="I92" s="1">
-        <v>0</v>
-      </c>
-      <c r="J92" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="K92" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="L92" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
-        <v>83</v>
-      </c>
-      <c r="B93" t="s">
-        <v>13</v>
-      </c>
-      <c r="C93" t="s">
-        <v>60</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="I93" s="1">
-        <v>0</v>
-      </c>
-      <c r="J93" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="K93" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="L93" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B94" t="s">
-        <v>13</v>
-      </c>
-      <c r="C94" t="s">
-        <v>60</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="I94" s="1">
+      <c r="E94" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="I94" s="4">
         <v>0</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="95" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>84</v>
+        <v>31</v>
       </c>
       <c r="B95" t="s">
-        <v>13</v>
-      </c>
-      <c r="C95" t="s">
-        <v>60</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="I95" s="1">
+        <v>72</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="I95" s="4">
         <v>0</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="96" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>80</v>
+        <v>210</v>
       </c>
       <c r="B96" t="s">
-        <v>13</v>
-      </c>
-      <c r="C96" t="s">
-        <v>60</v>
-      </c>
-      <c r="D96" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D96" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="I96" s="4">
+        <v>0</v>
+      </c>
+      <c r="J96" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="K96" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="L96" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B97" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D97" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="I97" s="4">
+        <v>0</v>
+      </c>
+      <c r="J97" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="K97" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="L97" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>212</v>
+      </c>
+      <c r="B98" t="s">
+        <v>213</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D98" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="I96" s="1">
-        <v>0</v>
-      </c>
-      <c r="J96" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="K96" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="L96" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="97" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
-        <v>208</v>
-      </c>
-      <c r="B97" t="s">
-        <v>13</v>
-      </c>
-      <c r="C97" t="s">
-        <v>60</v>
-      </c>
-      <c r="D97" s="1" t="s">
+      <c r="E98" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="I98" s="4">
+        <v>0</v>
+      </c>
+      <c r="J98" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="K98" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="L98" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B99" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D99" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="I97" s="1">
-        <v>0</v>
-      </c>
-      <c r="J97" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="K97" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="L97" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="98" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B98" t="s">
-        <v>13</v>
-      </c>
-      <c r="C98" t="s">
-        <v>60</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="I98" s="1">
-        <v>0</v>
-      </c>
-      <c r="J98" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="K98" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="L98" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="99" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
-        <v>209</v>
-      </c>
-      <c r="B99" t="s">
-        <v>13</v>
-      </c>
-      <c r="C99" t="s">
-        <v>60</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="I99" s="1">
+      <c r="I99" s="4">
         <v>0</v>
       </c>
       <c r="J99" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K99" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="100" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" t="e">
         <v>#N/A</v>
       </c>
-      <c r="B100" t="s">
-        <v>13</v>
-      </c>
-      <c r="C100" t="s">
-        <v>60</v>
-      </c>
-      <c r="D100" s="1" t="s">
+      <c r="B100" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D100" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="I100" s="4">
+        <v>0</v>
+      </c>
+      <c r="J100" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="K100" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="L100" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>214</v>
+      </c>
+      <c r="B101" t="s">
+        <v>215</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D101" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="I101" s="4">
+        <v>0</v>
+      </c>
+      <c r="J101" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="K101" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="L101" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A102" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B102" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D102" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="I100" s="1">
-        <v>0</v>
-      </c>
-      <c r="J100" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="K100" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="L100" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" t="e">
+      <c r="I102" s="4">
+        <v>0</v>
+      </c>
+      <c r="J102" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="K102" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="L102" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>216</v>
+      </c>
+      <c r="B103" t="s">
+        <v>217</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D103" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="I103" s="4">
+        <v>0</v>
+      </c>
+      <c r="J103" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="K103" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="L103" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A104" t="e">
         <v>#N/A</v>
       </c>
-      <c r="B101" t="s">
-        <v>13</v>
-      </c>
-      <c r="C101" t="s">
-        <v>60</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="I101" s="1">
-        <v>0</v>
-      </c>
-      <c r="J101" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="K101" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="L101" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="102" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
-        <v>210</v>
-      </c>
-      <c r="B102" t="s">
-        <v>13</v>
-      </c>
-      <c r="C102" t="s">
-        <v>60</v>
-      </c>
-      <c r="D102" s="1" t="s">
+      <c r="B104" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D104" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="I102" s="1">
-        <v>0</v>
-      </c>
-      <c r="J102" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="K102" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="L102" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="103" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B103" t="s">
-        <v>13</v>
-      </c>
-      <c r="C103" t="s">
-        <v>60</v>
-      </c>
-      <c r="D103" s="1" t="s">
+      <c r="I104" s="4">
+        <v>0</v>
+      </c>
+      <c r="J104" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="K104" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="L104" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>52</v>
+      </c>
+      <c r="B105" t="s">
+        <v>92</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D105" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="I103" s="1">
-        <v>0</v>
-      </c>
-      <c r="J103" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="K103" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="L103" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="104" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
-        <v>211</v>
-      </c>
-      <c r="B104" t="s">
-        <v>13</v>
-      </c>
-      <c r="C104" t="s">
-        <v>60</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="I104" s="1">
-        <v>0</v>
-      </c>
-      <c r="J104" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="K104" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="L104" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="105" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B105" t="s">
-        <v>13</v>
-      </c>
-      <c r="C105" t="s">
-        <v>60</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="I105" s="1">
+      <c r="E105" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="I105" s="4">
         <v>0</v>
       </c>
       <c r="J105" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="106" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>101</v>
+        <v>218</v>
       </c>
       <c r="B106" t="s">
-        <v>13</v>
-      </c>
-      <c r="C106" t="s">
-        <v>60</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="I106" s="1">
+        <v>219</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D106" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="I106" s="4">
         <v>0</v>
       </c>
       <c r="J106" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K106" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="107" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="B107" t="s">
-        <v>13</v>
-      </c>
-      <c r="C107" t="s">
-        <v>60</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="I107" s="1">
+        <v>221</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D107" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="I107" s="4">
         <v>0</v>
       </c>
       <c r="J107" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="108" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
-        <v>213</v>
-      </c>
-      <c r="B108" t="s">
-        <v>13</v>
-      </c>
-      <c r="C108" t="s">
-        <v>60</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="I108" s="1">
+      <c r="A108" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B108" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D108" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="I108" s="4">
         <v>0</v>
       </c>
       <c r="J108" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K108" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L108" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="109" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" t="e">
         <v>#N/A</v>
       </c>
-      <c r="B109" t="s">
-        <v>13</v>
-      </c>
-      <c r="C109" t="s">
-        <v>60</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I109" s="1">
-        <v>0</v>
+      <c r="B109" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D109" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="I109" s="4">
+        <v>1</v>
       </c>
       <c r="J109" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K109" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="110" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" t="e">
         <v>#N/A</v>
       </c>
-      <c r="B110" t="s">
-        <v>13</v>
-      </c>
-      <c r="C110" t="s">
-        <v>60</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="I110" s="1">
-        <v>1</v>
+      <c r="B110" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D110" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="I110" s="4">
+        <v>0</v>
       </c>
       <c r="J110" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L110" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="111" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" t="e">
         <v>#N/A</v>
       </c>
-      <c r="B111" t="s">
-        <v>13</v>
-      </c>
-      <c r="C111" t="s">
-        <v>60</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="I111" s="1">
+      <c r="B111" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D111" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="I111" s="4">
         <v>0</v>
       </c>
       <c r="J111" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K111" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="112" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" t="e">
         <v>#N/A</v>
       </c>
-      <c r="B112" t="s">
-        <v>13</v>
-      </c>
-      <c r="C112" t="s">
-        <v>60</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="I112" s="1">
+      <c r="B112" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D112" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="I112" s="4">
         <v>0</v>
       </c>
       <c r="J112" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K112" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="113" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" t="e">
         <v>#N/A</v>
       </c>
-      <c r="B113" t="s">
-        <v>13</v>
-      </c>
-      <c r="C113" t="s">
-        <v>60</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I113" s="1">
+      <c r="B113" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D113" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="I113" s="4">
         <v>0</v>
       </c>
       <c r="J113" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K113" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L113" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="114" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" t="e">
         <v>#N/A</v>
       </c>
-      <c r="B114" t="s">
-        <v>13</v>
-      </c>
-      <c r="C114" t="s">
-        <v>60</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="I114" s="1">
+      <c r="B114" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D114" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="I114" s="4">
         <v>0</v>
       </c>
       <c r="J114" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K114" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L114" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="115" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" t="e">
-        <v>#N/A</v>
+      <c r="A115" t="s">
+        <v>29</v>
       </c>
       <c r="B115" t="s">
-        <v>13</v>
-      </c>
-      <c r="C115" t="s">
-        <v>60</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="I115" s="1">
+        <v>70</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D115" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="I115" s="4">
         <v>0</v>
       </c>
       <c r="J115" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K115" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L115" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="116" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="B116" t="s">
-        <v>13</v>
-      </c>
-      <c r="C116" t="s">
-        <v>60</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="I116" s="1">
+        <v>68</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D116" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="I116" s="4">
         <v>0</v>
       </c>
       <c r="J116" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K116" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L116" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="117" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>76</v>
+        <v>222</v>
       </c>
       <c r="B117" t="s">
-        <v>13</v>
-      </c>
-      <c r="C117" t="s">
-        <v>60</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="I117" s="1">
+        <v>223</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D117" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="I117" s="4">
         <v>0</v>
       </c>
       <c r="J117" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K117" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L117" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="118" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="B118" t="s">
-        <v>13</v>
-      </c>
-      <c r="C118" t="s">
-        <v>60</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="I118" s="1">
+        <v>225</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D118" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="I118" s="4">
         <v>0</v>
       </c>
       <c r="J118" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K118" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L118" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="119" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" t="s">
-        <v>215</v>
-      </c>
-      <c r="B119" t="s">
-        <v>13</v>
-      </c>
-      <c r="C119" t="s">
-        <v>60</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="I119" s="1">
+      <c r="A119" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B119" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D119" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="I119" s="4">
         <v>0</v>
       </c>
       <c r="J119" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K119" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L119" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="120" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" t="e">
         <v>#N/A</v>
       </c>
-      <c r="B120" t="s">
-        <v>13</v>
-      </c>
-      <c r="C120" t="s">
-        <v>60</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="I120" s="1">
+      <c r="B120" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D120" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="I120" s="4">
         <v>0</v>
       </c>
       <c r="J120" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K120" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L120" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="121" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" t="e">
         <v>#N/A</v>
       </c>
-      <c r="B121" t="s">
-        <v>13</v>
-      </c>
-      <c r="C121" t="s">
-        <v>60</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="I121" s="1">
+      <c r="B121" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D121" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="I121" s="4">
         <v>0</v>
       </c>
       <c r="J121" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K121" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L121" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="122" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" t="e">
         <v>#N/A</v>
       </c>
-      <c r="B122" t="s">
-        <v>13</v>
-      </c>
-      <c r="C122" t="s">
-        <v>60</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="I122" s="1">
+      <c r="B122" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D122" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="I122" s="4">
         <v>0</v>
       </c>
       <c r="J122" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K122" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L122" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="123" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" t="e">
         <v>#N/A</v>
       </c>
-      <c r="B123" t="s">
-        <v>13</v>
-      </c>
-      <c r="C123" t="s">
-        <v>60</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="I123" s="1">
+      <c r="B123" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D123" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="I123" s="4">
         <v>0</v>
       </c>
       <c r="J123" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K123" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L123" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="124" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" t="e">
         <v>#N/A</v>
       </c>
-      <c r="B124" t="s">
-        <v>13</v>
-      </c>
-      <c r="C124" t="s">
-        <v>60</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="I124" s="1">
+      <c r="B124" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D124" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="I124" s="4">
         <v>0</v>
       </c>
       <c r="J124" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K124" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L124" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="125" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" t="e">
-        <v>#N/A</v>
+      <c r="A125" t="s">
+        <v>32</v>
       </c>
       <c r="B125" t="s">
-        <v>13</v>
-      </c>
-      <c r="C125" t="s">
-        <v>60</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="I125" s="1">
-        <v>0</v>
+        <v>73</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D125" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="I125" s="4">
+        <v>8</v>
       </c>
       <c r="J125" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K125" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L125" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="126" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>81</v>
+        <v>37</v>
       </c>
       <c r="B126" t="s">
-        <v>13</v>
-      </c>
-      <c r="C126" t="s">
-        <v>60</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="I126" s="1">
-        <v>8</v>
+        <v>78</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D126" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="I126" s="4">
+        <v>0</v>
       </c>
       <c r="J126" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K126" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L126" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="127" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>86</v>
+        <v>226</v>
       </c>
       <c r="B127" t="s">
-        <v>13</v>
-      </c>
-      <c r="C127" t="s">
-        <v>60</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="I127" s="1">
+        <v>227</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D127" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="I127" s="4">
         <v>0</v>
       </c>
       <c r="J127" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K127" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L127" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="128" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>216</v>
+        <v>38</v>
       </c>
       <c r="B128" t="s">
-        <v>13</v>
-      </c>
-      <c r="C128" t="s">
-        <v>60</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="I128" s="1">
+        <v>79</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D128" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="I128" s="4">
         <v>0</v>
       </c>
       <c r="J128" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K128" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L128" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="129" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B129" t="s">
-        <v>13</v>
-      </c>
-      <c r="C129" t="s">
-        <v>60</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="I129" s="1">
-        <v>0</v>
+        <v>54</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D129" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="I129" s="4">
+        <v>970</v>
       </c>
       <c r="J129" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K129" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L129" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="130" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="B130" t="s">
-        <v>13</v>
-      </c>
-      <c r="C130" t="s">
-        <v>60</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="I130" s="1">
-        <v>964</v>
+        <v>80</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D130" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="I130" s="4">
+        <v>459</v>
       </c>
       <c r="J130" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K130" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L130" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="131" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>88</v>
+        <v>15</v>
       </c>
       <c r="B131" t="s">
-        <v>13</v>
-      </c>
-      <c r="C131" t="s">
-        <v>60</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="I131" s="1">
-        <v>465</v>
+        <v>55</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D131" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="I131" s="4">
+        <v>571</v>
       </c>
       <c r="J131" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K131" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L131" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="132" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="B132" t="s">
-        <v>13</v>
-      </c>
-      <c r="C132" t="s">
-        <v>60</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="I132" s="1">
-        <v>571</v>
+        <v>81</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D132" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="I132" s="4">
+        <v>480</v>
       </c>
       <c r="J132" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K132" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L132" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="133" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>89</v>
+        <v>47</v>
       </c>
       <c r="B133" t="s">
-        <v>13</v>
-      </c>
-      <c r="C133" t="s">
-        <v>60</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="I133" s="1">
-        <v>482</v>
+        <v>88</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D133" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="I133" s="4">
+        <v>0</v>
       </c>
       <c r="J133" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K133" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L133" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="134" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="B134" t="s">
-        <v>13</v>
-      </c>
-      <c r="C134" t="s">
-        <v>60</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="I134" s="1">
+        <v>200</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D134" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="I134" s="4">
         <v>0</v>
       </c>
       <c r="J134" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K134" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L134" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="135" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>97</v>
+        <v>49</v>
       </c>
       <c r="B135" t="s">
-        <v>13</v>
-      </c>
-      <c r="C135" t="s">
-        <v>60</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="I135" s="1">
+        <v>89</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D135" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="I135" s="4">
         <v>0</v>
       </c>
       <c r="J135" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K135" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L135" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="136" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>98</v>
+        <v>50</v>
       </c>
       <c r="B136" t="s">
-        <v>13</v>
-      </c>
-      <c r="C136" t="s">
-        <v>60</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="I136" s="1">
+        <v>90</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D136" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="I136" s="4">
         <v>0</v>
       </c>
       <c r="J136" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K136" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L136" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="137" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>99</v>
+        <v>46</v>
       </c>
       <c r="B137" t="s">
-        <v>13</v>
-      </c>
-      <c r="C137" t="s">
-        <v>60</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="I137" s="1">
+        <v>87</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D137" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="I137" s="4">
         <v>0</v>
       </c>
       <c r="J137" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K137" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L137" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="138" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="B138" t="s">
-        <v>13</v>
-      </c>
-      <c r="C138" t="s">
-        <v>60</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="I138" s="1">
-        <v>0</v>
+        <v>56</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D138" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="I138" s="4">
+        <v>674</v>
       </c>
       <c r="J138" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K138" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L138" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="139" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="B139" t="s">
-        <v>13</v>
-      </c>
-      <c r="C139" t="s">
-        <v>60</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="I139" s="1">
-        <v>750</v>
+        <v>57</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D139" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="I139" s="4">
+        <v>7</v>
       </c>
       <c r="J139" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K139" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L139" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="140" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="B140" t="s">
-        <v>13</v>
-      </c>
-      <c r="C140" t="s">
-        <v>60</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="I140" s="1">
-        <v>7</v>
+        <v>58</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D140" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="I140" s="4">
+        <v>9</v>
       </c>
       <c r="J140" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K140" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L140" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="141" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>67</v>
+        <v>19</v>
       </c>
       <c r="B141" t="s">
-        <v>13</v>
-      </c>
-      <c r="C141" t="s">
-        <v>60</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="I141" s="1">
-        <v>9</v>
+        <v>59</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D141" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="I141" s="4">
+        <v>365</v>
       </c>
       <c r="J141" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K141" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L141" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="142" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="B142" t="s">
-        <v>13</v>
-      </c>
-      <c r="C142" t="s">
         <v>60</v>
       </c>
-      <c r="D142" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="I142" s="1">
-        <v>365</v>
+      <c r="C142" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D142" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="I142" s="4">
+        <v>7</v>
       </c>
       <c r="J142" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K142" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L142" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="143" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="B143" t="s">
-        <v>13</v>
-      </c>
-      <c r="C143" t="s">
-        <v>60</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="I143" s="1">
-        <v>7</v>
+        <v>61</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D143" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="I143" s="4">
+        <v>321</v>
       </c>
       <c r="J143" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K143" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L143" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="144" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="B144" t="s">
-        <v>13</v>
-      </c>
-      <c r="C144" t="s">
-        <v>60</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="I144" s="1">
-        <v>321</v>
+        <v>84</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D144" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="I144" s="4">
+        <v>0</v>
       </c>
       <c r="J144" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K144" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L144" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="145" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="B145" t="s">
-        <v>13</v>
-      </c>
-      <c r="C145" t="s">
-        <v>60</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="I145" s="1">
-        <v>0</v>
+        <v>85</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D145" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="I145" s="4">
+        <v>1</v>
       </c>
       <c r="J145" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K145" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L145" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="146" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>93</v>
+        <v>45</v>
       </c>
       <c r="B146" t="s">
-        <v>13</v>
-      </c>
-      <c r="C146" t="s">
-        <v>60</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="I146" s="1">
-        <v>1</v>
+        <v>86</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D146" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="I146" s="4">
+        <v>46</v>
       </c>
       <c r="J146" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K146" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L146" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="147" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>94</v>
+        <v>201</v>
       </c>
       <c r="B147" t="s">
-        <v>13</v>
-      </c>
-      <c r="C147" t="s">
-        <v>60</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="I147" s="1">
-        <v>46</v>
+        <v>93</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D147" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="I147" s="4">
+        <v>28</v>
       </c>
       <c r="J147" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K147" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L147" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="148" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>199</v>
+        <v>228</v>
       </c>
       <c r="B148" t="s">
-        <v>13</v>
-      </c>
-      <c r="C148" t="s">
-        <v>60</v>
-      </c>
-      <c r="D148" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D148" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="I148" s="4">
+        <v>19</v>
+      </c>
+      <c r="J148" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="K148" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="L148" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A149" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B149" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D149" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="I149" s="4">
+        <v>136</v>
+      </c>
+      <c r="J149" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="K149" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="L149" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="150" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>203</v>
+      </c>
+      <c r="B150" t="s">
+        <v>95</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D150" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="I148" s="1">
-        <v>28</v>
-      </c>
-      <c r="J148" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="K148" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="L148" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="149" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A149" t="s">
-        <v>217</v>
-      </c>
-      <c r="B149" t="s">
-        <v>13</v>
-      </c>
-      <c r="C149" t="s">
-        <v>60</v>
-      </c>
-      <c r="D149" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="I149" s="1">
-        <v>19</v>
-      </c>
-      <c r="J149" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="K149" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="L149" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="150" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A150" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B150" t="s">
-        <v>13</v>
-      </c>
-      <c r="C150" t="s">
-        <v>60</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="I150" s="1">
-        <v>139</v>
+      <c r="E150" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="I150" s="4">
+        <v>753</v>
       </c>
       <c r="J150" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K150" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L150" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="151" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B151" t="s">
-        <v>13</v>
-      </c>
-      <c r="C151" t="s">
-        <v>60</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="I151" s="1">
-        <v>753</v>
+        <v>98</v>
+      </c>
+      <c r="C151" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D151" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="I151" s="4">
+        <v>15</v>
       </c>
       <c r="J151" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K151" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L151" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="152" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B152" t="s">
-        <v>13</v>
-      </c>
-      <c r="C152" t="s">
-        <v>60</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="I152" s="1">
-        <v>15</v>
+        <v>99</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D152" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="I152" s="4">
+        <v>16</v>
       </c>
       <c r="J152" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K152" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L152" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="153" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B153" t="s">
-        <v>13</v>
-      </c>
-      <c r="C153" t="s">
-        <v>60</v>
-      </c>
-      <c r="D153" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="I153" s="1">
-        <v>16</v>
+        <v>96</v>
+      </c>
+      <c r="C153" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D153" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="I153" s="4">
+        <v>360</v>
       </c>
       <c r="J153" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K153" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L153" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="154" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B154" t="s">
-        <v>13</v>
-      </c>
-      <c r="C154" t="s">
-        <v>60</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="I154" s="1">
-        <v>360</v>
+        <v>62</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D154" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="I154" s="4">
+        <v>875</v>
       </c>
       <c r="J154" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K154" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L154" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="155" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>196</v>
+        <v>53</v>
       </c>
       <c r="B155" t="s">
-        <v>13</v>
-      </c>
-      <c r="C155" t="s">
-        <v>60</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="I155" s="1">
-        <v>877</v>
+        <v>230</v>
+      </c>
+      <c r="C155" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D155" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F155" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="I155" s="4">
+        <v>715</v>
       </c>
       <c r="J155" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K155" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L155" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="156" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>102</v>
+        <v>205</v>
       </c>
       <c r="B156" t="s">
-        <v>13</v>
-      </c>
-      <c r="C156" t="s">
-        <v>60</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="I156" s="1">
-        <v>715</v>
+        <v>97</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D156" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="I156" s="4">
+        <v>730</v>
       </c>
       <c r="J156" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K156" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L156" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="157" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="B157" t="s">
-        <v>13</v>
-      </c>
-      <c r="C157" t="s">
-        <v>60</v>
-      </c>
-      <c r="D157" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="I157" s="1">
-        <v>722</v>
+        <v>61</v>
+      </c>
+      <c r="C157" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D157" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="I157" s="6">
+        <v>50</v>
       </c>
       <c r="J157" s="1" t="s">
         <v>188</v>
       </c>
       <c r="K157" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L157" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="158" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="B158" t="s">
-        <v>13</v>
-      </c>
-      <c r="C158" t="s">
-        <v>60</v>
-      </c>
-      <c r="D158" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="I158" s="1">
+        <v>59</v>
+      </c>
+      <c r="C158" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D158" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="E158" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="I158" s="6">
         <v>50</v>
       </c>
       <c r="J158" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K158" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L158" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="159" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>68</v>
+        <v>231</v>
       </c>
       <c r="B159" t="s">
-        <v>13</v>
-      </c>
-      <c r="C159" t="s">
-        <v>60</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="I159" s="1">
-        <v>50</v>
+        <v>232</v>
+      </c>
+      <c r="C159" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D159" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F159" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="I159" s="6">
+        <v>10</v>
       </c>
       <c r="J159" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K159" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L159" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="160" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>63</v>
+        <v>233</v>
       </c>
       <c r="B160" t="s">
-        <v>13</v>
-      </c>
-      <c r="C160" t="s">
-        <v>60</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="I160" s="1">
-        <v>10</v>
+        <v>234</v>
+      </c>
+      <c r="C160" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D160" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="I160" s="6">
+        <v>50</v>
       </c>
       <c r="J160" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K160" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L160" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="161" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>64</v>
+        <v>14</v>
       </c>
       <c r="B161" t="s">
-        <v>13</v>
-      </c>
-      <c r="C161" t="s">
-        <v>60</v>
-      </c>
-      <c r="D161" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="I161" s="1">
-        <v>50</v>
+        <v>54</v>
+      </c>
+      <c r="C161" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D161" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="I161" s="4">
+        <v>3</v>
       </c>
       <c r="J161" s="1" t="s">
         <v>189</v>
       </c>
       <c r="K161" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="L161" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="162" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="B162" t="s">
-        <v>13</v>
-      </c>
-      <c r="C162" t="s">
-        <v>60</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="I162" s="1">
-        <v>3</v>
+        <v>55</v>
+      </c>
+      <c r="C162" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D162" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="E162" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="I162" s="4">
+        <v>1</v>
       </c>
       <c r="J162" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="K162" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L162" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="163" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>64</v>
+        <v>231</v>
       </c>
       <c r="B163" t="s">
-        <v>13</v>
-      </c>
-      <c r="C163" t="s">
-        <v>60</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="I163" s="1">
-        <v>1</v>
+        <v>232</v>
+      </c>
+      <c r="C163" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D163" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F163" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="I163" s="4">
+        <v>5</v>
       </c>
       <c r="J163" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="K163" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L163" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="164" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>218</v>
+        <v>16</v>
       </c>
       <c r="B164" t="s">
-        <v>13</v>
-      </c>
-      <c r="C164" t="s">
-        <v>60</v>
-      </c>
-      <c r="D164" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="I164" s="1">
-        <v>5</v>
+        <v>56</v>
+      </c>
+      <c r="C164" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D164" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="E164" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F164" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="I164" s="4">
+        <v>7</v>
       </c>
       <c r="J164" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="K164" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L164" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="165" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="B165" t="s">
-        <v>13</v>
-      </c>
-      <c r="C165" t="s">
-        <v>60</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="I165" s="1">
+        <v>57</v>
+      </c>
+      <c r="C165" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D165" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="E165" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F165" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="I165" s="4">
         <v>7</v>
       </c>
       <c r="J165" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="K165" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L165" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="166" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="B166" t="s">
-        <v>13</v>
-      </c>
-      <c r="C166" t="s">
-        <v>60</v>
-      </c>
-      <c r="D166" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="I166" s="1">
-        <v>7</v>
+        <v>59</v>
+      </c>
+      <c r="C166" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D166" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="E166" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F166" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="I166" s="4">
+        <v>3</v>
       </c>
       <c r="J166" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="K166" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L166" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="167" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="B167" t="s">
-        <v>13</v>
-      </c>
-      <c r="C167" t="s">
-        <v>60</v>
-      </c>
-      <c r="D167" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="I167" s="1">
+        <v>61</v>
+      </c>
+      <c r="C167" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D167" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="E167" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F167" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="I167" s="4">
         <v>3</v>
       </c>
       <c r="J167" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="K167" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L167" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="168" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A168" t="s">
-        <v>70</v>
-      </c>
-      <c r="B168" t="s">
-        <v>13</v>
-      </c>
-      <c r="C168" t="s">
-        <v>60</v>
-      </c>
-      <c r="D168" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="I168" s="1">
-        <v>3</v>
-      </c>
-      <c r="J168" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="K168" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="L168" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L1" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}"/>
+  <autoFilter ref="A1:L167" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="6" priority="207"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="488"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D74">
+    <cfRule type="duplicateValues" dxfId="74" priority="280" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="279" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="278" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="277"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="276"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D75:D80">
+    <cfRule type="duplicateValues" dxfId="69" priority="207" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="206" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="205" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="204"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="203"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D81:D86">
+    <cfRule type="duplicateValues" dxfId="64" priority="202" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="201" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="200" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="199"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="198"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D87:D101">
+    <cfRule type="duplicateValues" dxfId="59" priority="193"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="194"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="195" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="196" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="197" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D102:D111">
+    <cfRule type="duplicateValues" dxfId="54" priority="192" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="191" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="190"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="189"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="188"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="187"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="186"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="185"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D112:D115">
+    <cfRule type="duplicateValues" dxfId="46" priority="184" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="183" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="182"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="181"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="180"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="179"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="178"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="177"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D116:D117">
+    <cfRule type="duplicateValues" dxfId="38" priority="287"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="288"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="289"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="286" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D124:D128">
+    <cfRule type="duplicateValues" dxfId="34" priority="291"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="292"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="293"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="290" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D129:D134">
+    <cfRule type="duplicateValues" dxfId="30" priority="294"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="295"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="296"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="297"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="298"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="299"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="300" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="301" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D135:D146">
+    <cfRule type="duplicateValues" dxfId="22" priority="303"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="304"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="305"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="306"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="307"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="308" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="309" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="302"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D147:D156">
+    <cfRule type="duplicateValues" dxfId="14" priority="567" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="560"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="561"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="562"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="563"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="564"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="565"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="566" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D157:D160">
+    <cfRule type="duplicateValues" dxfId="6" priority="559"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
-    <cfRule type="duplicateValues" dxfId="5" priority="208"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="209" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="489"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="490" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="duplicateValues" dxfId="3" priority="205"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="206" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="486"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="487" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:L1">
-    <cfRule type="duplicateValues" dxfId="1" priority="203"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="204" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="485" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="484"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/input/Inventory_snapshot_WM.xlsx
+++ b/data/input/Inventory_snapshot_WM.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 10\White_Mulberry\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 11\White_Mulberry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9FB388E-4B37-4E73-AA4B-80E2726B3A2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E106261-0631-4F2F-858C-7D963554F071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D49B0F4C-5F9E-467E-8AD9-9E638F42404F}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1376" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1372" uniqueCount="248">
   <si>
     <t>SKU</t>
   </si>
@@ -75,6 +75,18 @@
     <t>Week</t>
   </si>
   <si>
+    <t>Amazon</t>
+  </si>
+  <si>
+    <t>Week 11</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>1p</t>
+  </si>
+  <si>
     <t>FBA79476</t>
   </si>
   <si>
@@ -333,22 +345,49 @@
     <t>B0FN81FD8M</t>
   </si>
   <si>
+    <t xml:space="preserve">White Mulberry </t>
+  </si>
+  <si>
     <t>White Mulberry</t>
   </si>
   <si>
-    <t>Amazon</t>
-  </si>
-  <si>
-    <t>Week 10</t>
-  </si>
-  <si>
-    <t>Marketplace</t>
-  </si>
-  <si>
-    <t>1p</t>
-  </si>
-  <si>
-    <t>1P</t>
+    <t xml:space="preserve"> Market place</t>
+  </si>
+  <si>
+    <t>MS1ML</t>
+  </si>
+  <si>
+    <t>Open Order</t>
+  </si>
+  <si>
+    <t>In-Transit Inventory</t>
+  </si>
+  <si>
+    <t>WM-GS1M-BK</t>
+  </si>
+  <si>
+    <t>WM1ML</t>
+  </si>
+  <si>
+    <t>VLMS1ML</t>
+  </si>
+  <si>
+    <t>HDWF1ML</t>
+  </si>
+  <si>
+    <t>YNT</t>
+  </si>
+  <si>
+    <t>GS2ML</t>
+  </si>
+  <si>
+    <t>HA2ML</t>
+  </si>
+  <si>
+    <t>B2B - AMPM</t>
+  </si>
+  <si>
+    <t>Warehouse</t>
   </si>
   <si>
     <t>WM-MD09-BK</t>
@@ -519,9 +558,6 @@
     <t>WM-USE06-WW</t>
   </si>
   <si>
-    <t>WM-GS1M-BK</t>
-  </si>
-  <si>
     <t>WM-GS2M-BK</t>
   </si>
   <si>
@@ -546,24 +582,12 @@
     <t>WM-LODJ-CF</t>
   </si>
   <si>
-    <t>WM1ML</t>
-  </si>
-  <si>
-    <t>MS1ML</t>
-  </si>
-  <si>
     <t>MS2ML</t>
   </si>
   <si>
-    <t>VLMS1ML</t>
-  </si>
-  <si>
     <t>HD1ML</t>
   </si>
   <si>
-    <t>HDWF1ML</t>
-  </si>
-  <si>
     <t>WM-MODL-BBW</t>
   </si>
   <si>
@@ -606,22 +630,7 @@
     <t>AMPM</t>
   </si>
   <si>
-    <t>Warehouse</t>
-  </si>
-  <si>
-    <t>GS2ML</t>
-  </si>
-  <si>
-    <t>HA2ML</t>
-  </si>
-  <si>
-    <t>B2B - AMPM</t>
-  </si>
-  <si>
-    <t>YNT</t>
-  </si>
-  <si>
-    <t>Dispatch Partner</t>
+    <t>FBA79789</t>
   </si>
   <si>
     <t>WM-LOD-BK</t>
@@ -630,9 +639,114 @@
     <t>WM-LOD-IN</t>
   </si>
   <si>
+    <t>FBA79784</t>
+  </si>
+  <si>
+    <t>FBA79786</t>
+  </si>
+  <si>
     <t>POSS-01</t>
   </si>
   <si>
+    <t>FBA79787</t>
+  </si>
+  <si>
+    <t>FBA79788</t>
+  </si>
+  <si>
+    <t>FBA79791</t>
+  </si>
+  <si>
+    <t>FBA79792</t>
+  </si>
+  <si>
+    <t>FBA79793</t>
+  </si>
+  <si>
+    <t>FBA79611</t>
+  </si>
+  <si>
+    <t>FBA79609</t>
+  </si>
+  <si>
+    <t>FBA76391</t>
+  </si>
+  <si>
+    <t>FBA79664</t>
+  </si>
+  <si>
+    <t>FBA76389</t>
+  </si>
+  <si>
+    <t>FBA76384</t>
+  </si>
+  <si>
+    <t>FBA76865</t>
+  </si>
+  <si>
+    <t>FBA76385</t>
+  </si>
+  <si>
+    <t>FBA76386</t>
+  </si>
+  <si>
+    <t>FBA79666</t>
+  </si>
+  <si>
+    <t>FBA76419</t>
+  </si>
+  <si>
+    <t>FBA79434</t>
+  </si>
+  <si>
+    <t>FBA79785</t>
+  </si>
+  <si>
+    <t>B0DQPLCZ3G</t>
+  </si>
+  <si>
+    <t>B0DSG694P2</t>
+  </si>
+  <si>
+    <t>B0DSG5PX7M</t>
+  </si>
+  <si>
+    <t>B0BF4WQNJR</t>
+  </si>
+  <si>
+    <t>B0DQPKMRN1</t>
+  </si>
+  <si>
+    <t>B0BF4XF7SD</t>
+  </si>
+  <si>
+    <t>B0BF4VWQXG</t>
+  </si>
+  <si>
+    <t>B0BF4Y92MW</t>
+  </si>
+  <si>
+    <t>B0BF4WD8Z8</t>
+  </si>
+  <si>
+    <t>B0BF51HCY4</t>
+  </si>
+  <si>
+    <t>B0DQPG9FSN</t>
+  </si>
+  <si>
+    <t>B0BFW5K3F1</t>
+  </si>
+  <si>
+    <t>B0DC3SJMZ6</t>
+  </si>
+  <si>
+    <t>B0FN4HDBN5</t>
+  </si>
+  <si>
+    <t>B0FN4GJ9S1</t>
+  </si>
+  <si>
     <t>Monitor Arm</t>
   </si>
   <si>
@@ -667,120 +781,15 @@
   </si>
   <si>
     <t>Table</t>
-  </si>
-  <si>
-    <t>FBA79789</t>
-  </si>
-  <si>
-    <t>FBA79784</t>
-  </si>
-  <si>
-    <t>FBA79786</t>
-  </si>
-  <si>
-    <t>FBA79787</t>
-  </si>
-  <si>
-    <t>FBA79788</t>
-  </si>
-  <si>
-    <t>FBA79791</t>
-  </si>
-  <si>
-    <t>FBA79792</t>
-  </si>
-  <si>
-    <t>FBA79793</t>
-  </si>
-  <si>
-    <t>FBA76391</t>
-  </si>
-  <si>
-    <t>FBA79664</t>
-  </si>
-  <si>
-    <t>FBA76389</t>
-  </si>
-  <si>
-    <t>FBA76384</t>
-  </si>
-  <si>
-    <t>FBA76865</t>
-  </si>
-  <si>
-    <t>FBA76385</t>
-  </si>
-  <si>
-    <t>FBA76386</t>
-  </si>
-  <si>
-    <t>FBA79666</t>
-  </si>
-  <si>
-    <t>FBA76419</t>
-  </si>
-  <si>
-    <t>FBA79434</t>
-  </si>
-  <si>
-    <t>FBA79785</t>
-  </si>
-  <si>
-    <t>FBA79611</t>
-  </si>
-  <si>
-    <t>FBA79609</t>
-  </si>
-  <si>
-    <t>B0DQPLCZ3G</t>
-  </si>
-  <si>
-    <t>B0FN4GJ9S1</t>
-  </si>
-  <si>
-    <t>B0BF4WQNJR</t>
-  </si>
-  <si>
-    <t>B0DQPKMRN1</t>
-  </si>
-  <si>
-    <t>B0BF4XF7SD</t>
-  </si>
-  <si>
-    <t>B0BF4VWQXG</t>
-  </si>
-  <si>
-    <t>B0BF4Y92MW</t>
-  </si>
-  <si>
-    <t>B0BF4WD8Z8</t>
-  </si>
-  <si>
-    <t>B0BF51HCY4</t>
-  </si>
-  <si>
-    <t>B0DQPG9FSN</t>
-  </si>
-  <si>
-    <t>B0BFW5K3F1</t>
-  </si>
-  <si>
-    <t>B0DC3SJMZ6</t>
-  </si>
-  <si>
-    <t>B0FN4HDBN5</t>
-  </si>
-  <si>
-    <t>B0DSG694P2</t>
-  </si>
-  <si>
-    <t>B0DSG5PX7M</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -809,10 +818,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Bookman Old Style"/>
-      <family val="1"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -853,11 +862,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -865,18 +875,104 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Comma" xfId="2" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 6" xfId="1" xr:uid="{E5F241CE-C0FC-4730-81C9-F1901EB82A3C}"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="15">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1283,7 +1379,7 @@
     <col min="1" max="1" width="12.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="42" style="1" customWidth="1"/>
+    <col min="4" max="4" width="21" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="23.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="28.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -1335,25 +1431,22 @@
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>160</v>
+        <v>108</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G2" s="1">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H2" s="1">
         <v>1341</v>
@@ -1362,36 +1455,33 @@
         <v>3</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G3" s="1">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H3" s="1">
         <v>866</v>
@@ -1400,36 +1490,33 @@
         <v>0</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C4" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G4" s="1">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H4" s="1">
         <v>1074</v>
@@ -1438,36 +1525,33 @@
         <v>0</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>170</v>
+        <v>105</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G5" s="1">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H5" s="1">
         <v>720</v>
@@ -1476,36 +1560,33 @@
         <v>0</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G6" s="1">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H6" s="1">
         <v>1015</v>
@@ -1514,36 +1595,33 @@
         <v>0</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>172</v>
+        <v>110</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G7" s="1">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H7" s="1">
         <v>1130</v>
@@ -1552,36 +1630,33 @@
         <v>0</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G8" s="1">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H8" s="1">
         <v>1566</v>
@@ -1590,36 +1665,33 @@
         <v>0</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>174</v>
+        <v>111</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G9" s="1">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H9" s="1">
         <v>1254</v>
@@ -1628,36 +1700,33 @@
         <v>2</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="G10" s="1">
-        <v>0</v>
+        <v>237</v>
       </c>
       <c r="H10" s="1">
         <v>179</v>
@@ -1666,74 +1735,68 @@
         <v>0</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>200</v>
+        <v>238</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="G11" s="1">
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="H11" s="1">
         <v>7852</v>
       </c>
       <c r="I11">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C12" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>202</v>
+        <v>240</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="G12" s="1">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="H12" s="1">
         <v>10654</v>
@@ -1742,36 +1805,33 @@
         <v>0</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>200</v>
+        <v>238</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="G13" s="1">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="H13" s="1">
         <v>10654</v>
@@ -1780,226 +1840,208 @@
         <v>0</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>203</v>
+        <v>241</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="G14" s="1">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="H14" s="1">
         <v>3943</v>
       </c>
       <c r="I14">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C15" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>203</v>
+        <v>241</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="G15" s="1">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="H15" s="1">
         <v>3943</v>
       </c>
       <c r="I15">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C16" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>203</v>
+        <v>241</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="G16" s="1">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="H16" s="1">
         <v>3943</v>
       </c>
       <c r="I16">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>203</v>
+        <v>241</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="G17" s="1">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="H17" s="1">
         <v>3943</v>
       </c>
       <c r="I17">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B18" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>200</v>
+        <v>238</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="G18" s="1">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="H18" s="1">
         <v>0</v>
       </c>
       <c r="I18">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B19" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C19" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>200</v>
+        <v>238</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="G19" s="1">
-        <v>0</v>
+        <v>243</v>
       </c>
       <c r="H19" s="1">
         <v>11345</v>
@@ -2008,36 +2050,33 @@
         <v>3</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B20" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C20" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>200</v>
+        <v>238</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="G20" s="1">
-        <v>0</v>
+        <v>243</v>
       </c>
       <c r="H20" s="1">
         <v>11345</v>
@@ -2046,74 +2085,68 @@
         <v>1</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B21" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C21" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>203</v>
+        <v>241</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="G21" s="1">
-        <v>0</v>
+        <v>244</v>
       </c>
       <c r="H21" s="1">
         <v>3269</v>
       </c>
       <c r="I21">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B22" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="C22" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>207</v>
+        <v>245</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="G22" s="1">
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="H22" s="1">
         <v>3272</v>
@@ -2122,36 +2155,33 @@
         <v>2</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B23" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C23" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>200</v>
+        <v>238</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="G23" s="1">
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="H23" s="1">
         <v>6978</v>
@@ -2160,36 +2190,33 @@
         <v>0</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B24" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C24" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>200</v>
+        <v>238</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="G24" s="1">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="H24" s="1">
         <v>7018</v>
@@ -2198,74 +2225,68 @@
         <v>0</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B25" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C25" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>200</v>
+        <v>238</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="G25" s="1">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="H25" s="1">
         <v>7018</v>
       </c>
       <c r="I25">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B26" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C26" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>200</v>
+        <v>238</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="G26" s="1">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="H26" s="1">
         <v>7018</v>
@@ -2274,36 +2295,33 @@
         <v>56</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C27" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>202</v>
+        <v>240</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="G27" s="1">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="H27" s="1">
         <v>7018</v>
@@ -2312,36 +2330,33 @@
         <v>0</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B28" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C28" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>200</v>
+        <v>238</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="G28" s="1">
-        <v>0</v>
+        <v>243</v>
       </c>
       <c r="H28" s="1">
         <v>11345</v>
@@ -2350,36 +2365,33 @@
         <v>0</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B29" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C29" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G29" s="1">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H29" s="1">
         <v>2236</v>
@@ -2388,36 +2400,33 @@
         <v>0</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B30" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C30" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G30" s="1">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H30" s="1">
         <v>1380</v>
@@ -2426,36 +2435,33 @@
         <v>0</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B31" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C31" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G31" s="1">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H31" s="1">
         <v>1015</v>
@@ -2464,36 +2470,33 @@
         <v>0</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B32" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C32" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G32" s="1">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H32" s="1">
         <v>1566</v>
@@ -2502,36 +2505,33 @@
         <v>0</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B33" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C33" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>200</v>
+        <v>238</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="G33" s="1">
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="H33" s="1">
         <v>6432</v>
@@ -2540,74 +2540,68 @@
         <v>24</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B34" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C34" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>200</v>
+        <v>238</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="G34" s="1">
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="H34" s="1">
         <v>6432</v>
       </c>
       <c r="I34">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B35" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C35" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>200</v>
+        <v>238</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="G35" s="1">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="H35" s="1">
         <v>7641</v>
@@ -2616,36 +2610,33 @@
         <v>1</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B36" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C36" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>200</v>
+        <v>238</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="G36" s="1">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="H36" s="1">
         <v>7641</v>
@@ -2654,74 +2645,68 @@
         <v>3</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B37" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C37" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>200</v>
+        <v>238</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="G37" s="1">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="H37" s="1">
         <v>7641</v>
       </c>
       <c r="I37">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B38" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C38" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>204</v>
+        <v>242</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="G38" s="1">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="H38" s="1">
         <v>3607</v>
@@ -2730,36 +2715,33 @@
         <v>0</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B39" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C39" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>203</v>
+        <v>241</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="G39" s="1">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="H39" s="1">
         <v>3272</v>
@@ -2768,36 +2750,33 @@
         <v>4</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B40" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="C40" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>207</v>
+        <v>245</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="G40" s="1">
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="H40" s="1">
         <v>3272</v>
@@ -2806,36 +2785,33 @@
         <v>1</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B41" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C41" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>203</v>
+        <v>241</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="G41" s="1">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="H41" s="1">
         <v>3262</v>
@@ -2844,36 +2820,33 @@
         <v>0</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B42" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C42" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>203</v>
+        <v>241</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="G42" s="1">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="H42" s="1">
         <v>3262</v>
@@ -2882,36 +2855,33 @@
         <v>0</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B43" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C43" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>200</v>
+        <v>238</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="G43" s="1">
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="H43" s="1">
         <v>7852</v>
@@ -2920,36 +2890,33 @@
         <v>2</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B44" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C44" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>200</v>
+        <v>238</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="G44" s="1">
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="H44" s="1">
         <v>7852</v>
@@ -2958,188 +2925,173 @@
         <v>1</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B45" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C45" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>160</v>
+        <v>108</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G45" s="1">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H45" s="1">
         <v>1341</v>
       </c>
       <c r="I45">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B46" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C46" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G46" s="1">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H46" s="1">
         <v>2236</v>
       </c>
       <c r="I46">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B47" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C47" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G47" s="1">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H47" s="1">
         <v>866</v>
       </c>
       <c r="I47">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B48" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C48" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G48" s="1">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H48" s="1">
         <v>1380</v>
       </c>
       <c r="I48">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="49" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B49" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C49" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G49" s="1">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H49" s="1">
         <v>1074</v>
@@ -3148,36 +3100,33 @@
         <v>55</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="50" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B50" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C50" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>170</v>
+        <v>105</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G50" s="1">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H50" s="1">
         <v>720</v>
@@ -3186,36 +3135,33 @@
         <v>1</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B51" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C51" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G51" s="1">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H51" s="1">
         <v>1015</v>
@@ -3224,36 +3170,33 @@
         <v>0</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="52" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B52" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C52" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>172</v>
+        <v>110</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G52" s="1">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H52" s="1">
         <v>1130</v>
@@ -3262,36 +3205,33 @@
         <v>41</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="53" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B53" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C53" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>174</v>
+        <v>111</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G53" s="1">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H53" s="1">
         <v>1254</v>
@@ -3300,74 +3240,65 @@
         <v>34</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>51</v>
-      </c>
-      <c r="B54" t="s">
-        <v>232</v>
+      <c r="A54" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B54" t="e">
+        <v>#N/A</v>
       </c>
       <c r="C54" t="s">
-        <v>98</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="G54" s="1">
-        <v>0</v>
-      </c>
-      <c r="H54" s="1">
-        <v>230</v>
+        <v>102</v>
+      </c>
+      <c r="D54" s="1" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E54" s="1" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H54" s="1" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I54">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="55" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B55" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C55" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>203</v>
+        <v>241</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="G55" s="1">
-        <v>0</v>
+        <v>244</v>
       </c>
       <c r="H55" s="1">
         <v>3269</v>
@@ -3376,36 +3307,33 @@
         <v>0</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="56" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="B56" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C56" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="G56" s="1">
-        <v>0</v>
+        <v>246</v>
       </c>
       <c r="H56" s="1">
         <v>2016</v>
@@ -3414,36 +3342,33 @@
         <v>1</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="57" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="B57" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C57" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="G57" s="1">
-        <v>0</v>
+        <v>246</v>
       </c>
       <c r="H57" s="1">
         <v>589</v>
@@ -3452,112 +3377,103 @@
         <v>90</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="58" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="B58" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C58" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="G58" s="1">
-        <v>0</v>
+        <v>237</v>
       </c>
       <c r="H58" s="1">
         <v>175</v>
       </c>
       <c r="I58">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="59" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="B59" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C59" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="G59" s="1">
-        <v>0</v>
+        <v>237</v>
       </c>
       <c r="H59" s="1">
         <v>113</v>
       </c>
       <c r="I59">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="B60" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C60" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="G60" s="1">
-        <v>0</v>
+        <v>237</v>
       </c>
       <c r="H60" s="1">
         <v>179</v>
@@ -3566,74 +3482,68 @@
         <v>180</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="61" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="B61" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C61" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="G61" s="1">
-        <v>0</v>
+        <v>237</v>
       </c>
       <c r="H61" s="1">
         <v>724</v>
       </c>
       <c r="I61">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="62" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="B62" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C62" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G62" s="1">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H62" s="1">
         <v>2043</v>
@@ -3642,36 +3552,33 @@
         <v>0</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="63" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="B63" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C63" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G63" s="1">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H63" s="1">
         <v>3200</v>
@@ -3680,879 +3587,850 @@
         <v>0</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="64" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B64" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C64" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>160</v>
+        <v>109</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G64" s="1">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H64" s="1">
-        <v>1341</v>
-      </c>
-      <c r="I64">
-        <v>88</v>
-      </c>
-      <c r="J64" s="3" t="s">
-        <v>102</v>
+        <v>1074</v>
+      </c>
+      <c r="I64" s="3">
+        <v>77</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>103</v>
+        <v>15</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="65" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B65" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C65" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>174</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G65" s="1">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H65" s="1">
-        <v>1254</v>
-      </c>
-      <c r="I65">
-        <v>28</v>
-      </c>
-      <c r="J65" s="3" t="s">
-        <v>102</v>
+        <v>866</v>
+      </c>
+      <c r="I65" t="s">
+        <v>14</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>103</v>
+        <v>15</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="66" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="B66" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="C66" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G66" s="1">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H66" s="1">
-        <v>1074</v>
-      </c>
-      <c r="I66">
-        <v>119</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>102</v>
+        <v>2236</v>
+      </c>
+      <c r="I66" s="3">
+        <v>2</v>
+      </c>
+      <c r="J66" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>103</v>
+        <v>15</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="67" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B67" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="C67" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G67" s="1">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H67" s="1">
-        <v>866</v>
-      </c>
-      <c r="I67"/>
-      <c r="J67" s="3" t="s">
-        <v>102</v>
+        <v>1254</v>
+      </c>
+      <c r="I67" s="3">
+        <v>37</v>
+      </c>
+      <c r="J67" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>103</v>
+        <v>15</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="68" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B68" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C68" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>173</v>
+        <v>108</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G68" s="1">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H68" s="1">
-        <v>1566</v>
-      </c>
-      <c r="I68">
-        <v>0</v>
-      </c>
-      <c r="J68" s="3" t="s">
-        <v>102</v>
+        <v>1341</v>
+      </c>
+      <c r="I68" s="3">
+        <v>64</v>
+      </c>
+      <c r="J68" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>103</v>
+        <v>15</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B69" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C69" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>170</v>
+        <v>105</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G69" s="1">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H69" s="1">
         <v>720</v>
       </c>
-      <c r="I69">
-        <v>0</v>
-      </c>
-      <c r="J69" s="3" t="s">
-        <v>102</v>
+      <c r="I69" s="3">
+        <v>0</v>
+      </c>
+      <c r="J69" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>103</v>
+        <v>15</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="70" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="B70" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="C70" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G70" s="1">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H70" s="1">
-        <v>2236</v>
-      </c>
-      <c r="I70">
-        <v>3</v>
-      </c>
-      <c r="J70" s="3" t="s">
-        <v>102</v>
+        <v>1566</v>
+      </c>
+      <c r="I70" s="3">
+        <v>1</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>103</v>
+        <v>15</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="71" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B71" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C71" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G71" s="1">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H71" s="1">
         <v>1380</v>
       </c>
-      <c r="I71">
+      <c r="I71" s="3">
         <v>5</v>
       </c>
-      <c r="J71" s="3" t="s">
-        <v>102</v>
+      <c r="J71" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>103</v>
+        <v>15</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="72" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B72" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C72" t="s">
-        <v>98</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>171</v>
+        <v>103</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G72" s="1">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H72" s="1">
-        <v>1015</v>
-      </c>
-      <c r="I72"/>
-      <c r="J72" s="3" t="s">
-        <v>102</v>
+        <v>720</v>
+      </c>
+      <c r="I72" s="5">
+        <v>500</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="73" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="B73" t="s">
-        <v>72</v>
-      </c>
-      <c r="C73" s="4" t="s">
-        <v>98</v>
+        <v>56</v>
+      </c>
+      <c r="C73" t="s">
+        <v>103</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>200</v>
+        <v>236</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="G73" s="1">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H73" s="1">
-        <v>6978</v>
+        <v>1341</v>
       </c>
       <c r="I73" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>188</v>
+        <v>112</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>189</v>
+        <v>107</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="74" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B74" t="s">
-        <v>61</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>98</v>
+        <v>58</v>
+      </c>
+      <c r="C74" t="s">
+        <v>103</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>200</v>
+        <v>236</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="G74" s="1">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H74" s="1">
-        <v>7852</v>
+        <v>1074</v>
       </c>
       <c r="I74" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>188</v>
+        <v>112</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>189</v>
+        <v>107</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="75" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="B75" t="s">
-        <v>89</v>
-      </c>
-      <c r="C75" s="4" t="s">
-        <v>98</v>
+        <v>59</v>
+      </c>
+      <c r="C75" t="s">
+        <v>103</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>200</v>
+        <v>236</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="G75" s="1">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H75" s="1">
-        <v>7852</v>
+        <v>720</v>
       </c>
       <c r="I75" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>188</v>
+        <v>112</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>189</v>
+        <v>107</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="76" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="B76" t="s">
-        <v>80</v>
-      </c>
-      <c r="C76" s="4" t="s">
-        <v>98</v>
+        <v>61</v>
+      </c>
+      <c r="C76" t="s">
+        <v>103</v>
       </c>
       <c r="D76" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="H76" s="1">
+        <v>1130</v>
+      </c>
+      <c r="I76" s="1">
+        <v>6</v>
+      </c>
+      <c r="J76" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="K76" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="E76" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="G76" s="1">
-        <v>0</v>
-      </c>
-      <c r="H76" s="1">
-        <v>6432</v>
-      </c>
-      <c r="I76" s="1">
-        <v>14</v>
-      </c>
-      <c r="J76" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="K76" s="1" t="s">
-        <v>189</v>
-      </c>
       <c r="L76" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="77" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="B77" t="s">
-        <v>81</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>98</v>
+        <v>63</v>
+      </c>
+      <c r="C77" t="s">
+        <v>103</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>200</v>
+        <v>236</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="G77" s="1">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H77" s="1">
-        <v>6432</v>
+        <v>1254</v>
       </c>
       <c r="I77" s="1">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>188</v>
+        <v>112</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>189</v>
+        <v>107</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="78" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B78" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C78" s="4" t="s">
-        <v>98</v>
+      <c r="A78" t="s">
+        <v>23</v>
+      </c>
+      <c r="B78" t="s">
+        <v>63</v>
+      </c>
+      <c r="C78" t="s">
+        <v>103</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="E78" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H78" s="1" t="e">
-        <v>#N/A</v>
+        <v>111</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="H78" s="1">
+        <v>1254</v>
       </c>
       <c r="I78" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>188</v>
+        <v>115</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="79" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B79" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>98</v>
+      <c r="A79" t="s">
+        <v>21</v>
+      </c>
+      <c r="B79" t="s">
+        <v>61</v>
+      </c>
+      <c r="C79" t="s">
+        <v>103</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="E79" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H79" s="1" t="e">
-        <v>#N/A</v>
+      <c r="E79" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="H79" s="1">
+        <v>1130</v>
       </c>
       <c r="I79" s="1">
+        <v>50</v>
+      </c>
+      <c r="J79" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="K79" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="L79" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>208</v>
+      </c>
+      <c r="B80" t="s">
+        <v>222</v>
+      </c>
+      <c r="C80" t="s">
+        <v>103</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="H80" s="1">
+        <v>1822</v>
+      </c>
+      <c r="I80" s="1">
         <v>15</v>
       </c>
-      <c r="J79" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="K79" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="L79" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B80" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C80" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="E80" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H80" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="I80" s="1">
-        <v>0</v>
-      </c>
       <c r="J80" s="1" t="s">
-        <v>188</v>
+        <v>115</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="81" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C81" s="4" t="s">
-        <v>98</v>
+      <c r="A81" t="s">
+        <v>209</v>
+      </c>
+      <c r="B81" t="s">
+        <v>223</v>
+      </c>
+      <c r="C81" t="s">
+        <v>103</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="E81" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H81" s="1" t="e">
-        <v>#N/A</v>
+        <v>114</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="H81" s="1">
+        <v>832</v>
       </c>
       <c r="I81" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>188</v>
+        <v>115</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="82" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B82" t="s">
-        <v>75</v>
-      </c>
-      <c r="C82" s="4" t="s">
-        <v>98</v>
+        <v>76</v>
+      </c>
+      <c r="C82" t="s">
+        <v>103</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>200</v>
+        <v>238</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="G82" s="1">
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="H82" s="1">
-        <v>7018</v>
+        <v>6978</v>
       </c>
       <c r="I82" s="1">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="83" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B83" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C83" s="4" t="s">
-        <v>98</v>
+      <c r="A83" t="s">
+        <v>24</v>
+      </c>
+      <c r="B83" t="s">
+        <v>65</v>
+      </c>
+      <c r="C83" t="s">
+        <v>103</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E83" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H83" s="1" t="e">
-        <v>#N/A</v>
+        <v>118</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="H83" s="1">
+        <v>7852</v>
       </c>
       <c r="I83" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="84" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B84" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C84" s="4" t="s">
-        <v>98</v>
+      <c r="A84" t="s">
+        <v>53</v>
+      </c>
+      <c r="B84" t="s">
+        <v>93</v>
+      </c>
+      <c r="C84" t="s">
+        <v>103</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="E84" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H84" s="1" t="e">
-        <v>#N/A</v>
+        <v>119</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="H84" s="1">
+        <v>7852</v>
       </c>
       <c r="I84" s="1">
         <v>0</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="85" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B85" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>98</v>
+      <c r="A85" t="s">
+        <v>43</v>
+      </c>
+      <c r="B85" t="s">
+        <v>84</v>
+      </c>
+      <c r="C85" t="s">
+        <v>103</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="E85" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H85" s="1" t="e">
-        <v>#N/A</v>
+        <v>120</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="H85" s="1">
+        <v>6432</v>
       </c>
       <c r="I85" s="1">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="86" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="B86" t="s">
-        <v>62</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>98</v>
+        <v>85</v>
+      </c>
+      <c r="C86" t="s">
+        <v>103</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>202</v>
+        <v>238</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="G86" s="1">
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="H86" s="1">
-        <v>10654</v>
+        <v>6432</v>
       </c>
       <c r="I86" s="1">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J86" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="87" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
-        <v>22</v>
-      </c>
-      <c r="B87" t="s">
-        <v>63</v>
-      </c>
-      <c r="C87" s="4" t="s">
-        <v>98</v>
+      <c r="A87" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B87" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C87" t="s">
+        <v>103</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="F87" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="G87" s="1">
-        <v>0</v>
-      </c>
-      <c r="H87" s="1">
-        <v>10654</v>
+        <v>122</v>
+      </c>
+      <c r="E87" s="1" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H87" s="1" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I87" s="1">
         <v>0</v>
       </c>
       <c r="J87" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="88" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -4562,11 +4440,11 @@
       <c r="B88" t="e">
         <v>#N/A</v>
       </c>
-      <c r="C88" s="4" t="s">
-        <v>98</v>
+      <c r="C88" t="s">
+        <v>103</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E88" s="1" t="e">
         <v>#N/A</v>
@@ -4575,168 +4453,147 @@
         <v>#N/A</v>
       </c>
       <c r="I88" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J88" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="89" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
-        <v>23</v>
-      </c>
-      <c r="B89" t="s">
-        <v>64</v>
-      </c>
-      <c r="C89" s="4" t="s">
-        <v>98</v>
+      <c r="A89" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B89" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C89" t="s">
+        <v>103</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="G89" s="1">
-        <v>0</v>
-      </c>
-      <c r="H89" s="1">
-        <v>3943</v>
+        <v>124</v>
+      </c>
+      <c r="E89" s="1" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H89" s="1" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I89" s="1">
         <v>0</v>
       </c>
       <c r="J89" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="90" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
-        <v>218</v>
-      </c>
-      <c r="B90" t="s">
-        <v>233</v>
-      </c>
-      <c r="C90" s="4" t="s">
-        <v>98</v>
+      <c r="A90" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B90" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C90" t="s">
+        <v>103</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="G90" s="1">
-        <v>0</v>
-      </c>
-      <c r="H90" s="1">
-        <v>0</v>
+        <v>125</v>
+      </c>
+      <c r="E90" s="1" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H90" s="1" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I90" s="1">
         <v>0</v>
       </c>
       <c r="J90" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K90" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="91" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="B91" t="s">
-        <v>69</v>
-      </c>
-      <c r="C91" s="4" t="s">
-        <v>98</v>
+        <v>79</v>
+      </c>
+      <c r="C91" t="s">
+        <v>103</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>200</v>
+        <v>238</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="G91" s="1">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="H91" s="1">
-        <v>11345</v>
+        <v>7018</v>
       </c>
       <c r="I91" s="1">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="J91" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="92" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
-        <v>32</v>
-      </c>
-      <c r="B92" t="s">
-        <v>73</v>
-      </c>
-      <c r="C92" s="4" t="s">
-        <v>98</v>
+      <c r="A92" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B92" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C92" t="s">
+        <v>103</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="F92" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="G92" s="1">
-        <v>0</v>
-      </c>
-      <c r="H92" s="1">
-        <v>7018</v>
+        <v>127</v>
+      </c>
+      <c r="E92" s="1" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H92" s="1" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I92" s="1">
         <v>0</v>
       </c>
       <c r="J92" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="93" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -4746,11 +4603,11 @@
       <c r="B93" t="e">
         <v>#N/A</v>
       </c>
-      <c r="C93" s="4" t="s">
-        <v>98</v>
+      <c r="C93" t="s">
+        <v>103</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E93" s="1" t="e">
         <v>#N/A</v>
@@ -4762,127 +4619,115 @@
         <v>0</v>
       </c>
       <c r="J93" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="94" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
-        <v>33</v>
-      </c>
-      <c r="B94" t="s">
-        <v>74</v>
-      </c>
-      <c r="C94" s="4" t="s">
-        <v>98</v>
+      <c r="A94" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B94" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C94" t="s">
+        <v>103</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="F94" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="G94" s="1">
-        <v>0</v>
-      </c>
-      <c r="H94" s="1">
-        <v>7018</v>
+        <v>129</v>
+      </c>
+      <c r="E94" s="1" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H94" s="1" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I94" s="1">
         <v>0</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="95" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B95" t="s">
-        <v>70</v>
-      </c>
-      <c r="C95" s="4" t="s">
-        <v>98</v>
+        <v>66</v>
+      </c>
+      <c r="C95" t="s">
+        <v>103</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="G95" s="1">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="H95" s="1">
-        <v>11345</v>
+        <v>10654</v>
       </c>
       <c r="I95" s="1">
         <v>0</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="96" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>219</v>
+        <v>26</v>
       </c>
       <c r="B96" t="s">
-        <v>234</v>
-      </c>
-      <c r="C96" s="4" t="s">
-        <v>98</v>
+        <v>67</v>
+      </c>
+      <c r="C96" t="s">
+        <v>103</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>204</v>
+        <v>238</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="G96" s="1">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="H96" s="1">
-        <v>3607</v>
+        <v>10654</v>
       </c>
       <c r="I96" s="1">
         <v>0</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K96" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="97" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -4892,11 +4737,11 @@
       <c r="B97" t="e">
         <v>#N/A</v>
       </c>
-      <c r="C97" s="4" t="s">
-        <v>98</v>
+      <c r="C97" t="s">
+        <v>103</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E97" s="1" t="e">
         <v>#N/A</v>
@@ -4908,153 +4753,153 @@
         <v>0</v>
       </c>
       <c r="J97" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="98" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>220</v>
+        <v>27</v>
       </c>
       <c r="B98" t="s">
-        <v>235</v>
-      </c>
-      <c r="C98" s="4" t="s">
-        <v>98</v>
+        <v>68</v>
+      </c>
+      <c r="C98" t="s">
+        <v>103</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>209</v>
+        <v>241</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="G98" s="1">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="H98" s="1">
-        <v>0</v>
+        <v>3943</v>
       </c>
       <c r="I98" s="1">
         <v>0</v>
       </c>
       <c r="J98" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="99" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B99" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C99" s="4" t="s">
-        <v>98</v>
+      <c r="A99" t="s">
+        <v>210</v>
+      </c>
+      <c r="B99" t="s">
+        <v>224</v>
+      </c>
+      <c r="C99" t="s">
+        <v>103</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E99" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H99" s="1" t="e">
-        <v>#N/A</v>
+        <v>134</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="H99" s="1">
+        <v>0</v>
       </c>
       <c r="I99" s="1">
         <v>0</v>
       </c>
       <c r="J99" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K99" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="100" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B100" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C100" s="4" t="s">
-        <v>98</v>
+      <c r="A100" t="s">
+        <v>32</v>
+      </c>
+      <c r="B100" t="s">
+        <v>73</v>
+      </c>
+      <c r="C100" t="s">
+        <v>103</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="E100" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H100" s="1" t="e">
-        <v>#N/A</v>
+        <v>135</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="H100" s="1">
+        <v>11345</v>
       </c>
       <c r="I100" s="1">
         <v>0</v>
       </c>
       <c r="J100" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K100" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="101" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>221</v>
+        <v>36</v>
       </c>
       <c r="B101" t="s">
-        <v>236</v>
-      </c>
-      <c r="C101" s="4" t="s">
-        <v>98</v>
+        <v>77</v>
+      </c>
+      <c r="C101" t="s">
+        <v>103</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>203</v>
+        <v>238</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="G101" s="1">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="H101" s="1">
-        <v>0</v>
+        <v>7018</v>
       </c>
       <c r="I101" s="1">
         <v>0</v>
       </c>
       <c r="J101" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K101" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L101" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="102" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -5064,11 +4909,11 @@
       <c r="B102" t="e">
         <v>#N/A</v>
       </c>
-      <c r="C102" s="4" t="s">
-        <v>98</v>
+      <c r="C102" t="s">
+        <v>103</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E102" s="1" t="e">
         <v>#N/A</v>
@@ -5080,182 +4925,170 @@
         <v>0</v>
       </c>
       <c r="J102" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K102" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="103" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>222</v>
+        <v>37</v>
       </c>
       <c r="B103" t="s">
-        <v>237</v>
-      </c>
-      <c r="C103" s="4" t="s">
-        <v>98</v>
+        <v>78</v>
+      </c>
+      <c r="C103" t="s">
+        <v>103</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>209</v>
+        <v>238</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="G103" s="1">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="H103" s="1">
-        <v>0</v>
+        <v>7018</v>
       </c>
       <c r="I103" s="1">
         <v>0</v>
       </c>
       <c r="J103" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K103" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="104" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B104" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C104" s="4" t="s">
-        <v>98</v>
+      <c r="A104" t="s">
+        <v>33</v>
+      </c>
+      <c r="B104" t="s">
+        <v>74</v>
+      </c>
+      <c r="C104" t="s">
+        <v>103</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="E104" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H104" s="1" t="e">
-        <v>#N/A</v>
+        <v>139</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="H104" s="1">
+        <v>11345</v>
       </c>
       <c r="I104" s="1">
         <v>0</v>
       </c>
       <c r="J104" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K104" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="105" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>50</v>
+        <v>211</v>
       </c>
       <c r="B105" t="s">
-        <v>90</v>
-      </c>
-      <c r="C105" s="4" t="s">
-        <v>98</v>
+        <v>225</v>
+      </c>
+      <c r="C105" t="s">
+        <v>103</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>200</v>
+        <v>242</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="G105" s="1">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="H105" s="1">
-        <v>7852</v>
+        <v>3607</v>
       </c>
       <c r="I105" s="1">
         <v>0</v>
       </c>
       <c r="J105" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="106" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
-        <v>223</v>
-      </c>
-      <c r="B106" t="s">
-        <v>238</v>
-      </c>
-      <c r="C106" s="4" t="s">
-        <v>98</v>
+      <c r="A106" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B106" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C106" t="s">
+        <v>103</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="F106" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="G106" s="1">
-        <v>0</v>
-      </c>
-      <c r="H106" s="1">
-        <v>0</v>
+        <v>141</v>
+      </c>
+      <c r="E106" s="1" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H106" s="1" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I106" s="1">
         <v>0</v>
       </c>
       <c r="J106" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K106" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="107" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="B107" t="s">
-        <v>239</v>
-      </c>
-      <c r="C107" s="4" t="s">
-        <v>98</v>
+        <v>226</v>
+      </c>
+      <c r="C107" t="s">
+        <v>103</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>209</v>
+        <v>247</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="G107" s="1">
-        <v>0</v>
+        <v>247</v>
       </c>
       <c r="H107" s="1">
         <v>0</v>
@@ -5264,13 +5097,13 @@
         <v>0</v>
       </c>
       <c r="J107" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="108" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -5280,11 +5113,11 @@
       <c r="B108" t="e">
         <v>#N/A</v>
       </c>
-      <c r="C108" s="4" t="s">
-        <v>98</v>
+      <c r="C108" t="s">
+        <v>103</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E108" s="1" t="e">
         <v>#N/A</v>
@@ -5296,13 +5129,13 @@
         <v>0</v>
       </c>
       <c r="J108" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K108" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L108" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="109" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -5312,11 +5145,11 @@
       <c r="B109" t="e">
         <v>#N/A</v>
       </c>
-      <c r="C109" s="4" t="s">
-        <v>98</v>
+      <c r="C109" t="s">
+        <v>103</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E109" s="1" t="e">
         <v>#N/A</v>
@@ -5325,48 +5158,51 @@
         <v>#N/A</v>
       </c>
       <c r="I109" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J109" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K109" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="110" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B110" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C110" s="4" t="s">
-        <v>98</v>
+      <c r="A110" t="s">
+        <v>213</v>
+      </c>
+      <c r="B110" t="s">
+        <v>227</v>
+      </c>
+      <c r="C110" t="s">
+        <v>103</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="E110" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H110" s="1" t="e">
-        <v>#N/A</v>
+        <v>145</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="H110" s="1">
+        <v>0</v>
       </c>
       <c r="I110" s="1">
         <v>0</v>
       </c>
       <c r="J110" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L110" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="111" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -5376,11 +5212,11 @@
       <c r="B111" t="e">
         <v>#N/A</v>
       </c>
-      <c r="C111" s="4" t="s">
-        <v>98</v>
+      <c r="C111" t="s">
+        <v>103</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E111" s="1" t="e">
         <v>#N/A</v>
@@ -5392,45 +5228,48 @@
         <v>0</v>
       </c>
       <c r="J111" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K111" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="112" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B112" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C112" s="4" t="s">
-        <v>98</v>
+      <c r="A112" t="s">
+        <v>214</v>
+      </c>
+      <c r="B112" t="s">
+        <v>228</v>
+      </c>
+      <c r="C112" t="s">
+        <v>103</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="E112" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H112" s="1" t="e">
-        <v>#N/A</v>
+        <v>147</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="H112" s="1">
+        <v>0</v>
       </c>
       <c r="I112" s="1">
         <v>0</v>
       </c>
       <c r="J112" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K112" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="113" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -5440,11 +5279,11 @@
       <c r="B113" t="e">
         <v>#N/A</v>
       </c>
-      <c r="C113" s="4" t="s">
-        <v>98</v>
+      <c r="C113" t="s">
+        <v>103</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E113" s="1" t="e">
         <v>#N/A</v>
@@ -5456,68 +5295,68 @@
         <v>0</v>
       </c>
       <c r="J113" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K113" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L113" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="114" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B114" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C114" s="4" t="s">
-        <v>98</v>
+      <c r="A114" t="s">
+        <v>54</v>
+      </c>
+      <c r="B114" t="s">
+        <v>94</v>
+      </c>
+      <c r="C114" t="s">
+        <v>103</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="E114" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H114" s="1" t="e">
-        <v>#N/A</v>
+        <v>149</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="H114" s="1">
+        <v>7852</v>
       </c>
       <c r="I114" s="1">
         <v>0</v>
       </c>
       <c r="J114" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K114" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L114" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="115" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>27</v>
+        <v>215</v>
       </c>
       <c r="B115" t="s">
-        <v>68</v>
-      </c>
-      <c r="C115" s="4" t="s">
-        <v>98</v>
+        <v>229</v>
+      </c>
+      <c r="C115" t="s">
+        <v>103</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>200</v>
+        <v>247</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="G115" s="1">
-        <v>0</v>
+        <v>247</v>
       </c>
       <c r="H115" s="1">
         <v>0</v>
@@ -5526,127 +5365,112 @@
         <v>0</v>
       </c>
       <c r="J115" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K115" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L115" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="116" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>25</v>
+        <v>216</v>
       </c>
       <c r="B116" t="s">
-        <v>66</v>
-      </c>
-      <c r="C116" s="4" t="s">
-        <v>98</v>
+        <v>230</v>
+      </c>
+      <c r="C116" t="s">
+        <v>103</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>203</v>
+        <v>247</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="G116" s="1">
-        <v>0</v>
+        <v>247</v>
       </c>
       <c r="H116" s="1">
-        <v>3943</v>
+        <v>0</v>
       </c>
       <c r="I116" s="1">
         <v>0</v>
       </c>
       <c r="J116" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K116" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L116" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="117" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
-        <v>225</v>
-      </c>
-      <c r="B117" t="s">
-        <v>240</v>
-      </c>
-      <c r="C117" s="4" t="s">
-        <v>98</v>
+      <c r="A117" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B117" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C117" t="s">
+        <v>103</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="E117" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="F117" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="G117" s="1">
-        <v>0</v>
-      </c>
-      <c r="H117" s="1">
-        <v>3607</v>
+        <v>152</v>
+      </c>
+      <c r="E117" s="1" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H117" s="1" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I117" s="1">
         <v>0</v>
       </c>
       <c r="J117" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K117" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L117" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="118" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" t="s">
-        <v>226</v>
-      </c>
-      <c r="B118" t="s">
-        <v>241</v>
-      </c>
-      <c r="C118" s="4" t="s">
-        <v>98</v>
+      <c r="A118" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B118" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C118" t="s">
+        <v>103</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="E118" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="F118" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="G118" s="1">
-        <v>0</v>
-      </c>
-      <c r="H118" s="1">
-        <v>0</v>
+        <v>153</v>
+      </c>
+      <c r="E118" s="1" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H118" s="1" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I118" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J118" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K118" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L118" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="119" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -5656,11 +5480,11 @@
       <c r="B119" t="e">
         <v>#N/A</v>
       </c>
-      <c r="C119" s="4" t="s">
-        <v>98</v>
+      <c r="C119" t="s">
+        <v>103</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E119" s="1" t="e">
         <v>#N/A</v>
@@ -5672,13 +5496,13 @@
         <v>0</v>
       </c>
       <c r="J119" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K119" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L119" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="120" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -5688,11 +5512,11 @@
       <c r="B120" t="e">
         <v>#N/A</v>
       </c>
-      <c r="C120" s="4" t="s">
-        <v>98</v>
+      <c r="C120" t="s">
+        <v>103</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E120" s="1" t="e">
         <v>#N/A</v>
@@ -5704,13 +5528,13 @@
         <v>0</v>
       </c>
       <c r="J120" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K120" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L120" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="121" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -5720,11 +5544,11 @@
       <c r="B121" t="e">
         <v>#N/A</v>
       </c>
-      <c r="C121" s="4" t="s">
-        <v>98</v>
+      <c r="C121" t="s">
+        <v>103</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E121" s="1" t="e">
         <v>#N/A</v>
@@ -5736,13 +5560,13 @@
         <v>0</v>
       </c>
       <c r="J121" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K121" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L121" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="122" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -5752,11 +5576,11 @@
       <c r="B122" t="e">
         <v>#N/A</v>
       </c>
-      <c r="C122" s="4" t="s">
-        <v>98</v>
+      <c r="C122" t="s">
+        <v>103</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E122" s="1" t="e">
         <v>#N/A</v>
@@ -5768,13 +5592,13 @@
         <v>0</v>
       </c>
       <c r="J122" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K122" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L122" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="123" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -5784,11 +5608,11 @@
       <c r="B123" t="e">
         <v>#N/A</v>
       </c>
-      <c r="C123" s="4" t="s">
-        <v>98</v>
+      <c r="C123" t="s">
+        <v>103</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E123" s="1" t="e">
         <v>#N/A</v>
@@ -5800,1616 +5624,1490 @@
         <v>0</v>
       </c>
       <c r="J123" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K123" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L123" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="124" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B124" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C124" s="4" t="s">
-        <v>98</v>
+      <c r="A124" t="s">
+        <v>31</v>
+      </c>
+      <c r="B124" t="s">
+        <v>72</v>
+      </c>
+      <c r="C124" t="s">
+        <v>103</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="E124" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H124" s="1" t="e">
-        <v>#N/A</v>
+        <v>159</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="H124" s="1">
+        <v>0</v>
       </c>
       <c r="I124" s="1">
         <v>0</v>
       </c>
       <c r="J124" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K124" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L124" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="125" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B125" t="s">
-        <v>71</v>
-      </c>
-      <c r="C125" s="4" t="s">
-        <v>98</v>
+        <v>70</v>
+      </c>
+      <c r="C125" t="s">
+        <v>103</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>203</v>
+        <v>241</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="G125" s="1">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="H125" s="1">
-        <v>3269</v>
+        <v>3943</v>
       </c>
       <c r="I125" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J125" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K125" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L125" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="126" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>35</v>
+        <v>217</v>
       </c>
       <c r="B126" t="s">
-        <v>76</v>
-      </c>
-      <c r="C126" s="4" t="s">
-        <v>98</v>
+        <v>231</v>
+      </c>
+      <c r="C126" t="s">
+        <v>103</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>202</v>
+        <v>242</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="G126" s="1">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="H126" s="1">
-        <v>7018</v>
+        <v>3607</v>
       </c>
       <c r="I126" s="1">
         <v>0</v>
       </c>
       <c r="J126" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K126" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L126" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="127" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="B127" t="s">
-        <v>242</v>
-      </c>
-      <c r="C127" s="4" t="s">
-        <v>98</v>
+        <v>232</v>
+      </c>
+      <c r="C127" t="s">
+        <v>103</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>200</v>
+        <v>241</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="G127" s="1">
-        <v>0</v>
+        <v>241</v>
       </c>
       <c r="H127" s="1">
-        <v>11345</v>
+        <v>0</v>
       </c>
       <c r="I127" s="1">
         <v>0</v>
       </c>
       <c r="J127" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K127" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L127" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="128" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A128" t="s">
-        <v>36</v>
-      </c>
-      <c r="B128" t="s">
-        <v>77</v>
-      </c>
-      <c r="C128" s="4" t="s">
-        <v>98</v>
+      <c r="A128" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B128" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C128" t="s">
+        <v>103</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="E128" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="F128" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="G128" s="1">
-        <v>0</v>
-      </c>
-      <c r="H128" s="1">
-        <v>11345</v>
+        <v>163</v>
+      </c>
+      <c r="E128" s="1" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H128" s="1" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I128" s="1">
         <v>0</v>
       </c>
       <c r="J128" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K128" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L128" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="129" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A129" t="s">
-        <v>12</v>
-      </c>
-      <c r="B129" t="s">
-        <v>52</v>
-      </c>
-      <c r="C129" s="4" t="s">
-        <v>98</v>
+      <c r="A129" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B129" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C129" t="s">
+        <v>103</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="F129" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G129" s="1">
-        <v>0</v>
-      </c>
-      <c r="H129" s="1">
-        <v>1341</v>
+        <v>164</v>
+      </c>
+      <c r="E129" s="1" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H129" s="1" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I129" s="1">
-        <v>848</v>
+        <v>0</v>
       </c>
       <c r="J129" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K129" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L129" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="130" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A130" t="s">
-        <v>37</v>
-      </c>
-      <c r="B130" t="s">
-        <v>78</v>
-      </c>
-      <c r="C130" s="4" t="s">
-        <v>98</v>
+      <c r="A130" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B130" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C130" t="s">
+        <v>103</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="E130" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="F130" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G130" s="1">
-        <v>0</v>
-      </c>
-      <c r="H130" s="1">
-        <v>2236</v>
+        <v>165</v>
+      </c>
+      <c r="E130" s="1" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H130" s="1" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I130" s="1">
-        <v>430</v>
+        <v>0</v>
       </c>
       <c r="J130" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K130" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L130" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="131" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A131" t="s">
-        <v>13</v>
-      </c>
-      <c r="B131" t="s">
-        <v>53</v>
-      </c>
-      <c r="C131" s="4" t="s">
-        <v>98</v>
+      <c r="A131" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B131" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C131" t="s">
+        <v>103</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="F131" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G131" s="1">
-        <v>0</v>
-      </c>
-      <c r="H131" s="1">
-        <v>866</v>
+        <v>166</v>
+      </c>
+      <c r="E131" s="1" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H131" s="1" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I131" s="1">
-        <v>570</v>
+        <v>0</v>
       </c>
       <c r="J131" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K131" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L131" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="132" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A132" t="s">
-        <v>38</v>
-      </c>
-      <c r="B132" t="s">
-        <v>79</v>
-      </c>
-      <c r="C132" s="4" t="s">
-        <v>98</v>
+      <c r="A132" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B132" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C132" t="s">
+        <v>103</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="E132" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="F132" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G132" s="1">
-        <v>0</v>
-      </c>
-      <c r="H132" s="1">
-        <v>1380</v>
+        <v>167</v>
+      </c>
+      <c r="E132" s="1" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H132" s="1" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I132" s="1">
-        <v>451</v>
+        <v>0</v>
       </c>
       <c r="J132" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K132" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L132" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="133" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A133" t="s">
-        <v>45</v>
-      </c>
-      <c r="B133" t="s">
-        <v>86</v>
-      </c>
-      <c r="C133" s="4" t="s">
-        <v>98</v>
+      <c r="A133" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B133" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C133" t="s">
+        <v>103</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="F133" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="G133" s="1">
-        <v>0</v>
-      </c>
-      <c r="H133" s="1">
-        <v>3272</v>
+        <v>168</v>
+      </c>
+      <c r="E133" s="1" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H133" s="1" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I133" s="1">
         <v>0</v>
       </c>
       <c r="J133" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K133" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L133" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="134" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="B134" t="s">
-        <v>231</v>
-      </c>
-      <c r="C134" s="4" t="s">
-        <v>98</v>
+        <v>75</v>
+      </c>
+      <c r="C134" t="s">
+        <v>103</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>207</v>
+        <v>241</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="G134" s="1">
-        <v>0</v>
+        <v>244</v>
       </c>
       <c r="H134" s="1">
-        <v>3272</v>
+        <v>3269</v>
       </c>
       <c r="I134" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J134" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K134" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L134" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="135" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B135" t="s">
-        <v>87</v>
-      </c>
-      <c r="C135" s="4" t="s">
-        <v>98</v>
+        <v>80</v>
+      </c>
+      <c r="C135" t="s">
+        <v>103</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>203</v>
+        <v>240</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="G135" s="1">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="H135" s="1">
-        <v>3262</v>
+        <v>7018</v>
       </c>
       <c r="I135" s="1">
         <v>0</v>
       </c>
       <c r="J135" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K135" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L135" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="136" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>48</v>
+        <v>219</v>
       </c>
       <c r="B136" t="s">
-        <v>88</v>
-      </c>
-      <c r="C136" s="4" t="s">
-        <v>98</v>
+        <v>233</v>
+      </c>
+      <c r="C136" t="s">
+        <v>103</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>203</v>
+        <v>238</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="G136" s="1">
-        <v>0</v>
+        <v>243</v>
       </c>
       <c r="H136" s="1">
-        <v>3262</v>
+        <v>11345</v>
       </c>
       <c r="I136" s="1">
         <v>0</v>
       </c>
       <c r="J136" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K136" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L136" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="137" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B137" t="s">
-        <v>85</v>
-      </c>
-      <c r="C137" s="4" t="s">
-        <v>98</v>
+        <v>81</v>
+      </c>
+      <c r="C137" t="s">
+        <v>103</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>204</v>
+        <v>238</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="G137" s="1">
-        <v>0</v>
+        <v>243</v>
       </c>
       <c r="H137" s="1">
-        <v>3607</v>
+        <v>11345</v>
       </c>
       <c r="I137" s="1">
         <v>0</v>
       </c>
       <c r="J137" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K137" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L137" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="138" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B138" t="s">
-        <v>54</v>
-      </c>
-      <c r="C138" s="4" t="s">
-        <v>98</v>
+        <v>56</v>
+      </c>
+      <c r="C138" t="s">
+        <v>103</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>169</v>
+        <v>108</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G138" s="1">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H138" s="1">
-        <v>1074</v>
+        <v>1341</v>
       </c>
       <c r="I138" s="1">
-        <v>594</v>
+        <v>821</v>
       </c>
       <c r="J138" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K138" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L138" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="139" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="B139" t="s">
-        <v>55</v>
-      </c>
-      <c r="C139" s="4" t="s">
-        <v>98</v>
+        <v>82</v>
+      </c>
+      <c r="C139" t="s">
+        <v>103</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G139" s="1">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H139" s="1">
-        <v>720</v>
+        <v>2236</v>
       </c>
       <c r="I139" s="1">
-        <v>7</v>
+        <v>428</v>
       </c>
       <c r="J139" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K139" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L139" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="140" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B140" t="s">
-        <v>56</v>
-      </c>
-      <c r="C140" s="4" t="s">
-        <v>98</v>
+        <v>57</v>
+      </c>
+      <c r="C140" t="s">
+        <v>103</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G140" s="1">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H140" s="1">
-        <v>1015</v>
+        <v>866</v>
       </c>
       <c r="I140" s="1">
-        <v>9</v>
+        <v>575</v>
       </c>
       <c r="J140" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K140" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L140" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="141" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="B141" t="s">
-        <v>57</v>
-      </c>
-      <c r="C141" s="4" t="s">
-        <v>98</v>
+        <v>83</v>
+      </c>
+      <c r="C141" t="s">
+        <v>103</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G141" s="1">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H141" s="1">
-        <v>1130</v>
+        <v>1380</v>
       </c>
       <c r="I141" s="1">
-        <v>325</v>
+        <v>425</v>
       </c>
       <c r="J141" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K141" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L141" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="142" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="B142" t="s">
-        <v>58</v>
-      </c>
-      <c r="C142" s="4" t="s">
-        <v>98</v>
+        <v>90</v>
+      </c>
+      <c r="C142" t="s">
+        <v>103</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>198</v>
+        <v>241</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G142" s="1">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="H142" s="1">
-        <v>1566</v>
+        <v>3272</v>
       </c>
       <c r="I142" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J142" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K142" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L142" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="143" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="B143" t="s">
-        <v>59</v>
-      </c>
-      <c r="C143" s="4" t="s">
-        <v>98</v>
+        <v>221</v>
+      </c>
+      <c r="C143" t="s">
+        <v>103</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>198</v>
+        <v>245</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G143" s="1">
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="H143" s="1">
-        <v>1254</v>
+        <v>3272</v>
       </c>
       <c r="I143" s="1">
-        <v>278</v>
+        <v>0</v>
       </c>
       <c r="J143" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K143" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L143" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="144" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="B144" t="s">
-        <v>82</v>
-      </c>
-      <c r="C144" s="4" t="s">
-        <v>98</v>
+        <v>91</v>
+      </c>
+      <c r="C144" t="s">
+        <v>103</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>200</v>
+        <v>241</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="G144" s="1">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="H144" s="1">
-        <v>7641</v>
+        <v>3262</v>
       </c>
       <c r="I144" s="1">
         <v>0</v>
       </c>
       <c r="J144" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K144" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L144" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="145" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="B145" t="s">
-        <v>83</v>
-      </c>
-      <c r="C145" s="4" t="s">
-        <v>98</v>
+        <v>92</v>
+      </c>
+      <c r="C145" t="s">
+        <v>103</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>200</v>
+        <v>241</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="G145" s="1">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="H145" s="1">
-        <v>7641</v>
+        <v>3262</v>
       </c>
       <c r="I145" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J145" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K145" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L145" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="146" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B146" t="s">
-        <v>84</v>
-      </c>
-      <c r="C146" s="4" t="s">
-        <v>98</v>
+        <v>89</v>
+      </c>
+      <c r="C146" t="s">
+        <v>103</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>200</v>
+        <v>242</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="G146" s="1">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="H146" s="1">
-        <v>7641</v>
+        <v>3607</v>
       </c>
       <c r="I146" s="1">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="J146" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K146" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L146" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="147" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>211</v>
+        <v>18</v>
       </c>
       <c r="B147" t="s">
-        <v>91</v>
-      </c>
-      <c r="C147" s="4" t="s">
-        <v>98</v>
+        <v>58</v>
+      </c>
+      <c r="C147" t="s">
+        <v>103</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>178</v>
+        <v>109</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="G147" s="1">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H147" s="1">
-        <v>2016</v>
+        <v>1074</v>
       </c>
       <c r="I147" s="1">
-        <v>28</v>
+        <v>527</v>
       </c>
       <c r="J147" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K147" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L147" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="148" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>228</v>
+        <v>19</v>
       </c>
       <c r="B148" t="s">
-        <v>243</v>
-      </c>
-      <c r="C148" s="4" t="s">
-        <v>98</v>
+        <v>59</v>
+      </c>
+      <c r="C148" t="s">
+        <v>103</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>179</v>
+        <v>105</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="G148" s="1">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H148" s="1">
-        <v>2722</v>
+        <v>720</v>
       </c>
       <c r="I148" s="1">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="J148" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K148" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L148" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="149" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A149" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B149" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C149" s="4" t="s">
-        <v>98</v>
+      <c r="A149" t="s">
+        <v>20</v>
+      </c>
+      <c r="B149" t="s">
+        <v>60</v>
+      </c>
+      <c r="C149" t="s">
+        <v>103</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="E149" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H149" s="1" t="e">
-        <v>#N/A</v>
+        <v>181</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="H149" s="1">
+        <v>1015</v>
       </c>
       <c r="I149" s="1">
-        <v>136</v>
+        <v>9</v>
       </c>
       <c r="J149" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K149" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L149" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="150" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>213</v>
+        <v>21</v>
       </c>
       <c r="B150" t="s">
-        <v>93</v>
-      </c>
-      <c r="C150" s="4" t="s">
-        <v>98</v>
+        <v>61</v>
+      </c>
+      <c r="C150" t="s">
+        <v>103</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>181</v>
+        <v>110</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="G150" s="1">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H150" s="1">
-        <v>175</v>
+        <v>1130</v>
       </c>
       <c r="I150" s="1">
-        <v>705</v>
+        <v>323</v>
       </c>
       <c r="J150" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K150" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L150" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="151" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>216</v>
+        <v>22</v>
       </c>
       <c r="B151" t="s">
-        <v>96</v>
-      </c>
-      <c r="C151" s="4" t="s">
-        <v>98</v>
+        <v>62</v>
+      </c>
+      <c r="C151" t="s">
+        <v>103</v>
       </c>
       <c r="D151" s="1" t="s">
         <v>182</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G151" s="1">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H151" s="1">
-        <v>2043</v>
+        <v>1566</v>
       </c>
       <c r="I151" s="1">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J151" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K151" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L151" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="152" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>217</v>
+        <v>23</v>
       </c>
       <c r="B152" t="s">
-        <v>97</v>
-      </c>
-      <c r="C152" s="4" t="s">
-        <v>98</v>
+        <v>63</v>
+      </c>
+      <c r="C152" t="s">
+        <v>103</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>183</v>
+        <v>111</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G152" s="1">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H152" s="1">
-        <v>3200</v>
+        <v>1254</v>
       </c>
       <c r="I152" s="1">
-        <v>16</v>
+        <v>309</v>
       </c>
       <c r="J152" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K152" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L152" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="153" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>214</v>
+        <v>45</v>
       </c>
       <c r="B153" t="s">
-        <v>94</v>
-      </c>
-      <c r="C153" s="4" t="s">
-        <v>98</v>
+        <v>86</v>
+      </c>
+      <c r="C153" t="s">
+        <v>103</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>198</v>
+        <v>238</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="G153" s="1">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="H153" s="1">
-        <v>113</v>
+        <v>7641</v>
       </c>
       <c r="I153" s="1">
-        <v>252</v>
+        <v>0</v>
       </c>
       <c r="J153" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K153" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L153" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="154" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>210</v>
+        <v>46</v>
       </c>
       <c r="B154" t="s">
-        <v>60</v>
-      </c>
-      <c r="C154" s="4" t="s">
-        <v>98</v>
+        <v>87</v>
+      </c>
+      <c r="C154" t="s">
+        <v>103</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>198</v>
+        <v>238</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="G154" s="1">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="H154" s="1">
-        <v>179</v>
+        <v>7641</v>
       </c>
       <c r="I154" s="1">
-        <v>873</v>
+        <v>1</v>
       </c>
       <c r="J154" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K154" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L154" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="155" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B155" t="s">
-        <v>232</v>
-      </c>
-      <c r="C155" s="4" t="s">
-        <v>98</v>
+        <v>88</v>
+      </c>
+      <c r="C155" t="s">
+        <v>103</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>198</v>
+        <v>238</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="G155" s="1">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="H155" s="1">
-        <v>230</v>
+        <v>7641</v>
       </c>
       <c r="I155" s="1">
-        <v>715</v>
+        <v>46</v>
       </c>
       <c r="J155" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K155" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L155" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="156" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="B156" t="s">
         <v>95</v>
       </c>
-      <c r="C156" s="4" t="s">
-        <v>98</v>
+      <c r="C156" t="s">
+        <v>103</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="G156" s="1">
-        <v>0</v>
+        <v>246</v>
       </c>
       <c r="H156" s="1">
-        <v>724</v>
+        <v>2016</v>
       </c>
       <c r="I156" s="1">
-        <v>610</v>
+        <v>28</v>
       </c>
       <c r="J156" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K156" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L156" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="157" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
+        <v>220</v>
+      </c>
+      <c r="B157" t="s">
+        <v>234</v>
+      </c>
+      <c r="C157" t="s">
+        <v>103</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="H157" s="1">
+        <v>2722</v>
+      </c>
+      <c r="I157" s="1">
         <v>19</v>
       </c>
-      <c r="B157" t="s">
-        <v>59</v>
-      </c>
-      <c r="C157" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="D157" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="E157" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="F157" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G157" s="1">
-        <v>0</v>
-      </c>
-      <c r="H157" s="1">
-        <v>1254</v>
-      </c>
-      <c r="I157" s="1">
-        <v>50</v>
-      </c>
       <c r="J157" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="K157" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L157" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="158" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A158" t="s">
-        <v>17</v>
-      </c>
-      <c r="B158" t="s">
-        <v>57</v>
-      </c>
-      <c r="C158" s="1" t="s">
-        <v>98</v>
+      <c r="A158" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B158" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C158" t="s">
+        <v>103</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="E158" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="F158" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G158" s="1">
-        <v>0</v>
-      </c>
-      <c r="H158" s="1">
-        <v>1130</v>
+        <v>188</v>
+      </c>
+      <c r="E158" s="1" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H158" s="1" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I158" s="1">
-        <v>50</v>
+        <v>136</v>
       </c>
       <c r="J158" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="K158" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L158" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="159" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>229</v>
+        <v>203</v>
       </c>
       <c r="B159" t="s">
-        <v>244</v>
-      </c>
-      <c r="C159" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
+      </c>
+      <c r="C159" t="s">
+        <v>103</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G159" s="1">
-        <v>0</v>
+        <v>237</v>
       </c>
       <c r="H159" s="1">
-        <v>1822</v>
+        <v>175</v>
       </c>
       <c r="I159" s="1">
-        <v>15</v>
+        <v>705</v>
       </c>
       <c r="J159" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="K159" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L159" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="160" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="B160" t="s">
-        <v>245</v>
-      </c>
-      <c r="C160" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
+      </c>
+      <c r="C160" t="s">
+        <v>103</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G160" s="1">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H160" s="1">
-        <v>832</v>
+        <v>2043</v>
       </c>
       <c r="I160" s="1">
         <v>15</v>
       </c>
       <c r="J160" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="K160" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="L160" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="161" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>12</v>
+        <v>207</v>
       </c>
       <c r="B161" t="s">
-        <v>52</v>
-      </c>
-      <c r="C161" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
+      </c>
+      <c r="C161" t="s">
+        <v>103</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>160</v>
+        <v>191</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G161" s="1">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H161" s="1">
-        <v>1341</v>
+        <v>3200</v>
       </c>
       <c r="I161" s="1">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="J161" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="K161" s="1" t="s">
-        <v>194</v>
+        <v>116</v>
       </c>
       <c r="L161" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="162" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>14</v>
+        <v>204</v>
       </c>
       <c r="B162" t="s">
-        <v>54</v>
-      </c>
-      <c r="C162" s="1" t="s">
         <v>98</v>
       </c>
+      <c r="C162" t="s">
+        <v>103</v>
+      </c>
       <c r="D162" s="1" t="s">
-        <v>169</v>
+        <v>192</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G162" s="1">
-        <v>0</v>
+        <v>237</v>
       </c>
       <c r="H162" s="1">
-        <v>1074</v>
+        <v>113</v>
       </c>
       <c r="I162" s="1">
-        <v>5</v>
+        <v>252</v>
       </c>
       <c r="J162" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="K162" s="1" t="s">
-        <v>194</v>
+        <v>116</v>
       </c>
       <c r="L162" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="163" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>15</v>
+        <v>197</v>
       </c>
       <c r="B163" t="s">
-        <v>55</v>
-      </c>
-      <c r="C163" s="1" t="s">
-        <v>98</v>
+        <v>64</v>
+      </c>
+      <c r="C163" t="s">
+        <v>103</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G163" s="1">
-        <v>0</v>
+        <v>237</v>
       </c>
       <c r="H163" s="1">
-        <v>720</v>
+        <v>179</v>
       </c>
       <c r="I163" s="1">
-        <v>7</v>
+        <v>862</v>
       </c>
       <c r="J163" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="K163" s="1" t="s">
-        <v>194</v>
+        <v>116</v>
       </c>
       <c r="L163" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="164" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="B164" t="s">
-        <v>57</v>
-      </c>
-      <c r="C164" s="1" t="s">
-        <v>98</v>
+        <v>235</v>
+      </c>
+      <c r="C164" t="s">
+        <v>103</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>172</v>
+        <v>194</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G164" s="1">
-        <v>0</v>
+        <v>237</v>
       </c>
       <c r="H164" s="1">
-        <v>1130</v>
+        <v>230</v>
       </c>
       <c r="I164" s="1">
-        <v>6</v>
+        <v>715</v>
       </c>
       <c r="J164" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="K164" s="1" t="s">
-        <v>194</v>
+        <v>116</v>
       </c>
       <c r="L164" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="165" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>19</v>
+        <v>205</v>
       </c>
       <c r="B165" t="s">
-        <v>59</v>
-      </c>
-      <c r="C165" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
+      </c>
+      <c r="C165" t="s">
+        <v>103</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G165" s="1">
-        <v>0</v>
+        <v>237</v>
       </c>
       <c r="H165" s="1">
-        <v>1254</v>
+        <v>724</v>
       </c>
       <c r="I165" s="1">
-        <v>8</v>
+        <v>610</v>
       </c>
       <c r="J165" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="K165" s="1" t="s">
-        <v>194</v>
+        <v>116</v>
       </c>
       <c r="L165" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L165" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="6" priority="488"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="496"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D72">
+    <cfRule type="duplicateValues" dxfId="13" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="7" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="8" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
-    <cfRule type="duplicateValues" dxfId="5" priority="489"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="490" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="497"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="498" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="duplicateValues" dxfId="3" priority="486"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="487" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="494"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="495" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:L1">
-    <cfRule type="duplicateValues" dxfId="1" priority="484"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="485" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="492"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="493" stopIfTrue="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/input/Inventory_snapshot_WM.xlsx
+++ b/data/input/Inventory_snapshot_WM.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 11\White_Mulberry\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E106261-0631-4F2F-858C-7D963554F071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>

--- a/data/input/Inventory_snapshot_WM.xlsx
+++ b/data/input/Inventory_snapshot_WM.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 14\White_Mulberry\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97AD98D8-846E-4406-ADED-019AACBD4F5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EECC87E-292F-42A4-A933-EEEC62FAC489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D49B0F4C-5F9E-467E-8AD9-9E638F42404F}"/>
   </bookViews>
@@ -225,9 +225,6 @@
     <t>White Mulberry</t>
   </si>
   <si>
-    <t>Ampm</t>
-  </si>
-  <si>
     <t>Warehouse</t>
   </si>
   <si>
@@ -700,6 +697,9 @@
   </si>
   <si>
     <t>YNT</t>
+  </si>
+  <si>
+    <t>AMPM</t>
   </si>
 </sst>
 </file>
@@ -872,148 +872,6 @@
         <color rgb="FF9C0006"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -1113,6 +971,58 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -1141,6 +1051,96 @@
       </font>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
@@ -1593,22 +1593,22 @@
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>93</v>
-      </c>
       <c r="C2" s="6" t="s">
         <v>61</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5">
@@ -1618,10 +1618,10 @@
         <v>1</v>
       </c>
       <c r="J2" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K2" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L2" s="5" t="s">
         <v>14</v>
@@ -1629,7 +1629,7 @@
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>15</v>
@@ -1638,13 +1638,13 @@
         <v>61</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G3" s="5"/>
       <c r="H3" s="5">
@@ -1654,10 +1654,10 @@
         <v>6</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L3" s="5" t="s">
         <v>14</v>
@@ -1665,7 +1665,7 @@
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>41</v>
@@ -1674,13 +1674,13 @@
         <v>61</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5">
@@ -1690,10 +1690,10 @@
         <v>15</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L4" s="5" t="s">
         <v>14</v>
@@ -1701,7 +1701,7 @@
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>16</v>
@@ -1710,13 +1710,13 @@
         <v>61</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5">
@@ -1726,10 +1726,10 @@
         <v>45</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L5" s="5" t="s">
         <v>14</v>
@@ -1737,7 +1737,7 @@
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>42</v>
@@ -1746,13 +1746,13 @@
         <v>61</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5">
@@ -1762,10 +1762,10 @@
         <v>15</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="K6" s="12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L6" s="5" t="s">
         <v>14</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>43</v>
@@ -1782,13 +1782,13 @@
         <v>61</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5">
@@ -1809,7 +1809,7 @@
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>43</v>
@@ -1818,13 +1818,13 @@
         <v>61</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G8" s="5">
         <v>0</v>
@@ -1834,10 +1834,10 @@
       </c>
       <c r="I8" s="5"/>
       <c r="J8" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L8" s="5" t="s">
         <v>14</v>
@@ -1845,7 +1845,7 @@
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>43</v>
@@ -1854,13 +1854,13 @@
         <v>61</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="5">
@@ -1870,10 +1870,10 @@
         <v>6</v>
       </c>
       <c r="J9" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K9" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K9" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L9" s="5" t="s">
         <v>14</v>
@@ -1881,7 +1881,7 @@
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>60</v>
@@ -1890,13 +1890,13 @@
         <v>61</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G10" s="5"/>
       <c r="H10" s="5">
@@ -1917,7 +1917,7 @@
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>60</v>
@@ -1926,13 +1926,13 @@
         <v>61</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5">
@@ -1942,10 +1942,10 @@
         <v>6</v>
       </c>
       <c r="J11" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K11" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K11" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L11" s="5" t="s">
         <v>14</v>
@@ -1953,7 +1953,7 @@
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>59</v>
@@ -1962,13 +1962,13 @@
         <v>61</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5">
@@ -1989,7 +1989,7 @@
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>59</v>
@@ -1998,13 +1998,13 @@
         <v>61</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5">
@@ -2014,10 +2014,10 @@
         <v>15</v>
       </c>
       <c r="J13" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K13" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K13" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L13" s="5" t="s">
         <v>14</v>
@@ -2025,7 +2025,7 @@
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>21</v>
@@ -2034,13 +2034,13 @@
         <v>61</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5">
@@ -2061,7 +2061,7 @@
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>21</v>
@@ -2070,13 +2070,13 @@
         <v>61</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5">
@@ -2097,7 +2097,7 @@
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>21</v>
@@ -2106,13 +2106,13 @@
         <v>61</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G16" s="5"/>
       <c r="H16" s="5">
@@ -2122,10 +2122,10 @@
         <v>33</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L16" s="5" t="s">
         <v>14</v>
@@ -2133,7 +2133,7 @@
     </row>
     <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>21</v>
@@ -2142,13 +2142,13 @@
         <v>61</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5">
@@ -2158,10 +2158,10 @@
         <v>311</v>
       </c>
       <c r="J17" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K17" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K17" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L17" s="5" t="s">
         <v>14</v>
@@ -2169,7 +2169,7 @@
     </row>
     <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>21</v>
@@ -2178,13 +2178,13 @@
         <v>61</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5">
@@ -2194,10 +2194,10 @@
         <v>50</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L18" s="5" t="s">
         <v>14</v>
@@ -2205,7 +2205,7 @@
     </row>
     <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>21</v>
@@ -2214,13 +2214,13 @@
         <v>61</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5">
@@ -2230,10 +2230,10 @@
         <v>8</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="L19" s="5" t="s">
         <v>14</v>
@@ -2241,7 +2241,7 @@
     </row>
     <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>18</v>
@@ -2250,13 +2250,13 @@
         <v>61</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G20" s="5"/>
       <c r="H20" s="5">
@@ -2277,7 +2277,7 @@
     </row>
     <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>18</v>
@@ -2286,13 +2286,13 @@
         <v>61</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G21" s="5"/>
       <c r="H21" s="5">
@@ -2313,7 +2313,7 @@
     </row>
     <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>18</v>
@@ -2322,13 +2322,13 @@
         <v>61</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5">
@@ -2338,10 +2338,10 @@
         <v>0</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L22" s="5" t="s">
         <v>14</v>
@@ -2349,7 +2349,7 @@
     </row>
     <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>18</v>
@@ -2358,13 +2358,13 @@
         <v>61</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5">
@@ -2374,10 +2374,10 @@
         <v>0</v>
       </c>
       <c r="J23" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K23" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K23" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L23" s="5" t="s">
         <v>14</v>
@@ -2385,7 +2385,7 @@
     </row>
     <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>18</v>
@@ -2394,13 +2394,13 @@
         <v>61</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="5">
@@ -2410,10 +2410,10 @@
         <v>7</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="L24" s="5" t="s">
         <v>14</v>
@@ -2421,7 +2421,7 @@
     </row>
     <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>18</v>
@@ -2430,13 +2430,13 @@
         <v>61</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G25" s="5"/>
       <c r="H25" s="5">
@@ -2446,10 +2446,10 @@
         <v>500</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="K25" s="11" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L25" s="5" t="s">
         <v>14</v>
@@ -2457,7 +2457,7 @@
     </row>
     <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>19</v>
@@ -2466,13 +2466,13 @@
         <v>61</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="5">
@@ -2493,7 +2493,7 @@
     </row>
     <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>19</v>
@@ -2502,13 +2502,13 @@
         <v>61</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5">
@@ -2529,7 +2529,7 @@
     </row>
     <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>19</v>
@@ -2538,13 +2538,13 @@
         <v>61</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G28" s="5">
         <v>0</v>
@@ -2554,10 +2554,10 @@
       </c>
       <c r="I28" s="5"/>
       <c r="J28" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L28" s="5" t="s">
         <v>14</v>
@@ -2565,7 +2565,7 @@
     </row>
     <row r="29" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>19</v>
@@ -2574,13 +2574,13 @@
         <v>61</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G29" s="5"/>
       <c r="H29" s="5">
@@ -2590,10 +2590,10 @@
         <v>5</v>
       </c>
       <c r="J29" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K29" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K29" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L29" s="5" t="s">
         <v>14</v>
@@ -2601,7 +2601,7 @@
     </row>
     <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>55</v>
@@ -2610,13 +2610,13 @@
         <v>61</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E30" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="F30" s="5" t="s">
         <v>213</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>214</v>
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="5">
@@ -2626,10 +2626,10 @@
         <v>138</v>
       </c>
       <c r="J30" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K30" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K30" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L30" s="5" t="s">
         <v>14</v>
@@ -2637,7 +2637,7 @@
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>54</v>
@@ -2646,13 +2646,13 @@
         <v>61</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E31" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="F31" s="5" t="s">
         <v>213</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>214</v>
       </c>
       <c r="G31" s="5"/>
       <c r="H31" s="5">
@@ -2673,7 +2673,7 @@
     </row>
     <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>54</v>
@@ -2682,13 +2682,13 @@
         <v>61</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E32" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="F32" s="5" t="s">
         <v>213</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>214</v>
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="5">
@@ -2698,10 +2698,10 @@
         <v>28</v>
       </c>
       <c r="J32" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K32" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K32" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L32" s="5" t="s">
         <v>14</v>
@@ -2709,22 +2709,22 @@
     </row>
     <row r="33" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="B33" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="B33" s="7" t="s">
-        <v>126</v>
-      </c>
       <c r="C33" s="6" t="s">
         <v>61</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E33" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="F33" s="5" t="s">
         <v>213</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>214</v>
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5">
@@ -2734,10 +2734,10 @@
         <v>19</v>
       </c>
       <c r="J33" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K33" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K33" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L33" s="5" t="s">
         <v>14</v>
@@ -2745,7 +2745,7 @@
     </row>
     <row r="34" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>55</v>
@@ -2754,13 +2754,13 @@
         <v>61</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E34" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="F34" s="5" t="s">
         <v>213</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>214</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5">
@@ -2781,7 +2781,7 @@
     </row>
     <row r="35" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>56</v>
@@ -2790,13 +2790,13 @@
         <v>61</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5">
@@ -2817,7 +2817,7 @@
     </row>
     <row r="36" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>56</v>
@@ -2826,13 +2826,13 @@
         <v>61</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="5">
@@ -2842,10 +2842,10 @@
         <v>705</v>
       </c>
       <c r="J36" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K36" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K36" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L36" s="5" t="s">
         <v>14</v>
@@ -2853,7 +2853,7 @@
     </row>
     <row r="37" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>57</v>
@@ -2862,13 +2862,13 @@
         <v>61</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="5">
@@ -2889,7 +2889,7 @@
     </row>
     <row r="38" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>57</v>
@@ -2898,13 +2898,13 @@
         <v>61</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="5">
@@ -2914,10 +2914,10 @@
         <v>252</v>
       </c>
       <c r="J38" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K38" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K38" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L38" s="5" t="s">
         <v>14</v>
@@ -2925,7 +2925,7 @@
     </row>
     <row r="39" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>58</v>
@@ -2934,13 +2934,13 @@
         <v>61</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="5">
@@ -2961,7 +2961,7 @@
     </row>
     <row r="40" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>58</v>
@@ -2970,13 +2970,13 @@
         <v>61</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="5">
@@ -2986,10 +2986,10 @@
         <v>610</v>
       </c>
       <c r="J40" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K40" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K40" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L40" s="5" t="s">
         <v>14</v>
@@ -2997,7 +2997,7 @@
     </row>
     <row r="41" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>53</v>
@@ -3006,13 +3006,13 @@
         <v>61</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G41" s="5"/>
       <c r="H41" s="5">
@@ -3033,16 +3033,16 @@
     </row>
     <row r="42" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="B42" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="B42" s="7" t="s">
-        <v>134</v>
-      </c>
       <c r="C42" s="6" t="s">
         <v>61</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E42" s="5" t="e">
         <v>#N/A</v>
@@ -3056,10 +3056,10 @@
         <v>655</v>
       </c>
       <c r="J42" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K42" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K42" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L42" s="5" t="s">
         <v>14</v>
@@ -3067,7 +3067,7 @@
     </row>
     <row r="43" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>22</v>
@@ -3076,13 +3076,13 @@
         <v>61</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G43" s="5"/>
       <c r="H43" s="5">
@@ -3103,7 +3103,7 @@
     </row>
     <row r="44" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>22</v>
@@ -3112,13 +3112,13 @@
         <v>61</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G44" s="5"/>
       <c r="H44" s="5">
@@ -3139,7 +3139,7 @@
     </row>
     <row r="45" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>22</v>
@@ -3148,13 +3148,13 @@
         <v>61</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="5">
@@ -3164,10 +3164,10 @@
         <v>863</v>
       </c>
       <c r="J45" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K45" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K45" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L45" s="5" t="s">
         <v>14</v>
@@ -3175,7 +3175,7 @@
     </row>
     <row r="46" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>20</v>
@@ -3184,13 +3184,13 @@
         <v>61</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G46" s="5"/>
       <c r="H46" s="5">
@@ -3211,7 +3211,7 @@
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>20</v>
@@ -3220,13 +3220,13 @@
         <v>61</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="5">
@@ -3247,7 +3247,7 @@
     </row>
     <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B48" s="7" t="s">
         <v>20</v>
@@ -3256,13 +3256,13 @@
         <v>61</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5">
@@ -3272,10 +3272,10 @@
         <v>322</v>
       </c>
       <c r="J48" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K48" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K48" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L48" s="5" t="s">
         <v>14</v>
@@ -3283,7 +3283,7 @@
     </row>
     <row r="49" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>20</v>
@@ -3292,13 +3292,13 @@
         <v>61</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G49" s="5"/>
       <c r="H49" s="5">
@@ -3308,10 +3308,10 @@
         <v>50</v>
       </c>
       <c r="J49" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="K49" s="12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L49" s="5" t="s">
         <v>14</v>
@@ -3319,7 +3319,7 @@
     </row>
     <row r="50" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>20</v>
@@ -3328,13 +3328,13 @@
         <v>61</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G50" s="5"/>
       <c r="H50" s="5">
@@ -3344,10 +3344,10 @@
         <v>6</v>
       </c>
       <c r="J50" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="K50" s="12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="L50" s="5" t="s">
         <v>14</v>
@@ -3355,7 +3355,7 @@
     </row>
     <row r="51" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>17</v>
@@ -3364,13 +3364,13 @@
         <v>61</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G51" s="5"/>
       <c r="H51" s="5">
@@ -3391,7 +3391,7 @@
     </row>
     <row r="52" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>17</v>
@@ -3400,13 +3400,13 @@
         <v>61</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G52" s="5"/>
       <c r="H52" s="5">
@@ -3427,7 +3427,7 @@
     </row>
     <row r="53" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>17</v>
@@ -3436,13 +3436,13 @@
         <v>61</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="5">
@@ -3452,10 +3452,10 @@
         <v>136</v>
       </c>
       <c r="J53" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K53" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L53" s="5" t="s">
         <v>14</v>
@@ -3463,7 +3463,7 @@
     </row>
     <row r="54" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>17</v>
@@ -3472,13 +3472,13 @@
         <v>61</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="5">
@@ -3488,10 +3488,10 @@
         <v>403</v>
       </c>
       <c r="J54" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K54" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K54" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L54" s="5" t="s">
         <v>14</v>
@@ -3499,7 +3499,7 @@
     </row>
     <row r="55" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>17</v>
@@ -3508,13 +3508,13 @@
         <v>61</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="5">
@@ -3524,10 +3524,10 @@
         <v>5</v>
       </c>
       <c r="J55" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="K55" s="12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="L55" s="5" t="s">
         <v>14</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="56" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B56" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="B56" s="7" t="s">
-        <v>86</v>
-      </c>
       <c r="C56" s="6" t="s">
         <v>61</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="5">
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="J56" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K56" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K56" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L56" s="5" t="s">
         <v>14</v>
@@ -3571,22 +3571,22 @@
     </row>
     <row r="57" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B57" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="B57" s="7" t="s">
-        <v>91</v>
-      </c>
       <c r="C57" s="6" t="s">
         <v>61</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="5">
@@ -3596,10 +3596,10 @@
         <v>0</v>
       </c>
       <c r="J57" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K57" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K57" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L57" s="5" t="s">
         <v>14</v>
@@ -3607,22 +3607,22 @@
     </row>
     <row r="58" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B58" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="B58" s="7" t="s">
-        <v>75</v>
-      </c>
       <c r="C58" s="6" t="s">
         <v>61</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="5">
@@ -3632,10 +3632,10 @@
         <v>0</v>
       </c>
       <c r="J58" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K58" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K58" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L58" s="5" t="s">
         <v>14</v>
@@ -3643,22 +3643,22 @@
     </row>
     <row r="59" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B59" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="B59" s="7" t="s">
-        <v>82</v>
-      </c>
       <c r="C59" s="6" t="s">
         <v>61</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="5">
@@ -3668,10 +3668,10 @@
         <v>0</v>
       </c>
       <c r="J59" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K59" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K59" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L59" s="5" t="s">
         <v>14</v>
@@ -3679,22 +3679,22 @@
     </row>
     <row r="60" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B60" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="B60" s="7" t="s">
-        <v>89</v>
-      </c>
       <c r="C60" s="6" t="s">
         <v>61</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="5">
@@ -3704,10 +3704,10 @@
         <v>0</v>
       </c>
       <c r="J60" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K60" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K60" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L60" s="5" t="s">
         <v>14</v>
@@ -3715,7 +3715,7 @@
     </row>
     <row r="61" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>33</v>
@@ -3724,13 +3724,13 @@
         <v>61</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="5">
@@ -3751,7 +3751,7 @@
     </row>
     <row r="62" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>33</v>
@@ -3760,13 +3760,13 @@
         <v>61</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="5">
@@ -3787,7 +3787,7 @@
     </row>
     <row r="63" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B63" s="7" t="s">
         <v>33</v>
@@ -3796,13 +3796,13 @@
         <v>61</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G63" s="5"/>
       <c r="H63" s="5">
@@ -3812,10 +3812,10 @@
         <v>0</v>
       </c>
       <c r="J63" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K63" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K63" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L63" s="5" t="s">
         <v>14</v>
@@ -3823,7 +3823,7 @@
     </row>
     <row r="64" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>15</v>
@@ -3832,13 +3832,13 @@
         <v>61</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="5">
@@ -3859,7 +3859,7 @@
     </row>
     <row r="65" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>15</v>
@@ -3868,13 +3868,13 @@
         <v>61</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G65" s="5"/>
       <c r="H65" s="5">
@@ -3895,7 +3895,7 @@
     </row>
     <row r="66" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>15</v>
@@ -3904,13 +3904,13 @@
         <v>61</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G66" s="5"/>
       <c r="H66" s="5">
@@ -3920,10 +3920,10 @@
         <v>129</v>
       </c>
       <c r="J66" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K66" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L66" s="5" t="s">
         <v>14</v>
@@ -3931,7 +3931,7 @@
     </row>
     <row r="67" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B67" s="7" t="s">
         <v>15</v>
@@ -3940,13 +3940,13 @@
         <v>61</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G67" s="5"/>
       <c r="H67" s="5">
@@ -3956,10 +3956,10 @@
         <v>694</v>
       </c>
       <c r="J67" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K67" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K67" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L67" s="5" t="s">
         <v>14</v>
@@ -3967,7 +3967,7 @@
     </row>
     <row r="68" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>15</v>
@@ -3976,13 +3976,13 @@
         <v>61</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G68" s="5"/>
       <c r="H68" s="5">
@@ -3992,10 +3992,10 @@
         <v>1</v>
       </c>
       <c r="J68" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="K68" s="12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="L68" s="5" t="s">
         <v>14</v>
@@ -4003,7 +4003,7 @@
     </row>
     <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>41</v>
@@ -4012,13 +4012,13 @@
         <v>61</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G69" s="5"/>
       <c r="H69" s="5">
@@ -4039,7 +4039,7 @@
     </row>
     <row r="70" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>41</v>
@@ -4048,13 +4048,13 @@
         <v>61</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G70" s="5"/>
       <c r="H70" s="5">
@@ -4075,7 +4075,7 @@
     </row>
     <row r="71" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>41</v>
@@ -4084,13 +4084,13 @@
         <v>61</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G71" s="5"/>
       <c r="H71" s="5">
@@ -4100,10 +4100,10 @@
         <v>19</v>
       </c>
       <c r="J71" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K71" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L71" s="5" t="s">
         <v>14</v>
@@ -4111,7 +4111,7 @@
     </row>
     <row r="72" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B72" s="7" t="s">
         <v>41</v>
@@ -4120,13 +4120,13 @@
         <v>61</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G72" s="5"/>
       <c r="H72" s="5">
@@ -4136,10 +4136,10 @@
         <v>402</v>
       </c>
       <c r="J72" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K72" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K72" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L72" s="5" t="s">
         <v>14</v>
@@ -4147,7 +4147,7 @@
     </row>
     <row r="73" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>16</v>
@@ -4156,13 +4156,13 @@
         <v>61</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G73" s="5"/>
       <c r="H73" s="5">
@@ -4183,7 +4183,7 @@
     </row>
     <row r="74" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>16</v>
@@ -4192,13 +4192,13 @@
         <v>61</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G74" s="5"/>
       <c r="H74" s="5">
@@ -4219,7 +4219,7 @@
     </row>
     <row r="75" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>16</v>
@@ -4228,13 +4228,13 @@
         <v>61</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G75" s="5"/>
       <c r="H75" s="5">
@@ -4244,10 +4244,10 @@
         <v>14</v>
       </c>
       <c r="J75" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K75" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L75" s="5" t="s">
         <v>14</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="76" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B76" s="7" t="s">
         <v>16</v>
@@ -4264,13 +4264,13 @@
         <v>61</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G76" s="5"/>
       <c r="H76" s="5">
@@ -4280,10 +4280,10 @@
         <v>595</v>
       </c>
       <c r="J76" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K76" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K76" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L76" s="5" t="s">
         <v>14</v>
@@ -4291,7 +4291,7 @@
     </row>
     <row r="77" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>42</v>
@@ -4300,13 +4300,13 @@
         <v>61</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G77" s="5"/>
       <c r="H77" s="5">
@@ -4327,7 +4327,7 @@
     </row>
     <row r="78" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>42</v>
@@ -4336,13 +4336,13 @@
         <v>61</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G78" s="5"/>
       <c r="H78" s="5">
@@ -4363,7 +4363,7 @@
     </row>
     <row r="79" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>42</v>
@@ -4372,13 +4372,13 @@
         <v>61</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G79" s="5"/>
       <c r="H79" s="5">
@@ -4388,10 +4388,10 @@
         <v>35</v>
       </c>
       <c r="J79" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K79" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L79" s="5" t="s">
         <v>14</v>
@@ -4399,7 +4399,7 @@
     </row>
     <row r="80" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B80" s="7" t="s">
         <v>42</v>
@@ -4408,13 +4408,13 @@
         <v>61</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G80" s="5"/>
       <c r="H80" s="5">
@@ -4424,10 +4424,10 @@
         <v>340</v>
       </c>
       <c r="J80" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K80" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K80" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L80" s="5" t="s">
         <v>14</v>
@@ -4435,7 +4435,7 @@
     </row>
     <row r="81" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>27</v>
@@ -4444,13 +4444,13 @@
         <v>61</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E81" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="F81" s="5" t="s">
         <v>206</v>
-      </c>
-      <c r="F81" s="5" t="s">
-        <v>207</v>
       </c>
       <c r="G81" s="5"/>
       <c r="H81" s="5">
@@ -4471,7 +4471,7 @@
     </row>
     <row r="82" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>26</v>
@@ -4480,13 +4480,13 @@
         <v>61</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E82" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="F82" s="5" t="s">
         <v>206</v>
-      </c>
-      <c r="F82" s="5" t="s">
-        <v>207</v>
       </c>
       <c r="G82" s="5"/>
       <c r="H82" s="5">
@@ -4507,7 +4507,7 @@
     </row>
     <row r="83" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B83" s="7" t="s">
         <v>26</v>
@@ -4516,13 +4516,13 @@
         <v>61</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E83" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="F83" s="5" t="s">
         <v>206</v>
-      </c>
-      <c r="F83" s="5" t="s">
-        <v>207</v>
       </c>
       <c r="G83" s="5"/>
       <c r="H83" s="5">
@@ -4532,10 +4532,10 @@
         <v>0</v>
       </c>
       <c r="J83" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K83" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K83" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L83" s="5" t="s">
         <v>14</v>
@@ -4543,7 +4543,7 @@
     </row>
     <row r="84" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B84" s="5" t="s">
         <v>29</v>
@@ -4552,13 +4552,13 @@
         <v>61</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E84" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="F84" s="5" t="s">
         <v>206</v>
-      </c>
-      <c r="F84" s="5" t="s">
-        <v>207</v>
       </c>
       <c r="G84" s="5"/>
       <c r="H84" s="5">
@@ -4579,7 +4579,7 @@
     </row>
     <row r="85" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B85" s="7" t="s">
         <v>27</v>
@@ -4588,13 +4588,13 @@
         <v>61</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E85" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="F85" s="5" t="s">
         <v>206</v>
-      </c>
-      <c r="F85" s="5" t="s">
-        <v>207</v>
       </c>
       <c r="G85" s="5"/>
       <c r="H85" s="5">
@@ -4604,10 +4604,10 @@
         <v>0</v>
       </c>
       <c r="J85" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K85" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K85" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L85" s="5" t="s">
         <v>14</v>
@@ -4615,22 +4615,22 @@
     </row>
     <row r="86" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="B86" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="B86" s="7" t="s">
-        <v>114</v>
-      </c>
       <c r="C86" s="6" t="s">
         <v>61</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G86" s="5"/>
       <c r="H86" s="5">
@@ -4640,10 +4640,10 @@
         <v>0</v>
       </c>
       <c r="J86" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K86" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K86" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L86" s="5" t="s">
         <v>14</v>
@@ -4651,7 +4651,7 @@
     </row>
     <row r="87" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B87" s="7" t="s">
         <v>29</v>
@@ -4660,13 +4660,13 @@
         <v>61</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E87" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="F87" s="5" t="s">
         <v>206</v>
-      </c>
-      <c r="F87" s="5" t="s">
-        <v>207</v>
       </c>
       <c r="G87" s="5"/>
       <c r="H87" s="5">
@@ -4676,10 +4676,10 @@
         <v>0</v>
       </c>
       <c r="J87" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K87" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K87" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L87" s="5" t="s">
         <v>14</v>
@@ -4687,7 +4687,7 @@
     </row>
     <row r="88" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B88" s="5" t="s">
         <v>34</v>
@@ -4696,13 +4696,13 @@
         <v>61</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E88" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="F88" s="5" t="s">
         <v>206</v>
-      </c>
-      <c r="F88" s="5" t="s">
-        <v>207</v>
       </c>
       <c r="G88" s="5"/>
       <c r="H88" s="5">
@@ -4723,7 +4723,7 @@
     </row>
     <row r="89" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>34</v>
@@ -4732,13 +4732,13 @@
         <v>61</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E89" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="F89" s="5" t="s">
         <v>206</v>
-      </c>
-      <c r="F89" s="5" t="s">
-        <v>207</v>
       </c>
       <c r="G89" s="5"/>
       <c r="H89" s="5">
@@ -4759,7 +4759,7 @@
     </row>
     <row r="90" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>34</v>
@@ -4768,13 +4768,13 @@
         <v>61</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E90" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="F90" s="5" t="s">
         <v>206</v>
-      </c>
-      <c r="F90" s="5" t="s">
-        <v>207</v>
       </c>
       <c r="G90" s="5"/>
       <c r="H90" s="5">
@@ -4784,10 +4784,10 @@
         <v>0</v>
       </c>
       <c r="J90" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K90" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K90" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L90" s="5" t="s">
         <v>14</v>
@@ -4795,7 +4795,7 @@
     </row>
     <row r="91" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B91" s="5" t="s">
         <v>49</v>
@@ -4804,13 +4804,13 @@
         <v>61</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E91" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="F91" s="5" t="s">
         <v>206</v>
-      </c>
-      <c r="F91" s="5" t="s">
-        <v>207</v>
       </c>
       <c r="G91" s="5"/>
       <c r="H91" s="5">
@@ -4831,7 +4831,7 @@
     </row>
     <row r="92" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B92" s="7" t="s">
         <v>49</v>
@@ -4840,13 +4840,13 @@
         <v>61</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E92" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="F92" s="5" t="s">
         <v>206</v>
-      </c>
-      <c r="F92" s="5" t="s">
-        <v>207</v>
       </c>
       <c r="G92" s="5"/>
       <c r="H92" s="5">
@@ -4856,10 +4856,10 @@
         <v>0</v>
       </c>
       <c r="J92" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K92" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K92" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L92" s="5" t="s">
         <v>14</v>
@@ -4867,7 +4867,7 @@
     </row>
     <row r="93" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>28</v>
@@ -4876,13 +4876,13 @@
         <v>61</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E93" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="F93" s="5" t="s">
         <v>206</v>
-      </c>
-      <c r="F93" s="5" t="s">
-        <v>207</v>
       </c>
       <c r="G93" s="5"/>
       <c r="H93" s="5">
@@ -4903,7 +4903,7 @@
     </row>
     <row r="94" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B94" s="7" t="s">
         <v>28</v>
@@ -4912,13 +4912,13 @@
         <v>61</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E94" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="F94" s="5" t="s">
         <v>206</v>
-      </c>
-      <c r="F94" s="5" t="s">
-        <v>207</v>
       </c>
       <c r="G94" s="5"/>
       <c r="H94" s="5">
@@ -4928,10 +4928,10 @@
         <v>0</v>
       </c>
       <c r="J94" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K94" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K94" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L94" s="5" t="s">
         <v>14</v>
@@ -4939,7 +4939,7 @@
     </row>
     <row r="95" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>50</v>
@@ -4948,13 +4948,13 @@
         <v>61</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E95" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="F95" s="5" t="s">
         <v>206</v>
-      </c>
-      <c r="F95" s="5" t="s">
-        <v>207</v>
       </c>
       <c r="G95" s="5"/>
       <c r="H95" s="5">
@@ -4975,7 +4975,7 @@
     </row>
     <row r="96" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B96" s="7" t="s">
         <v>50</v>
@@ -4984,13 +4984,13 @@
         <v>61</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E96" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="F96" s="5" t="s">
         <v>206</v>
-      </c>
-      <c r="F96" s="5" t="s">
-        <v>207</v>
       </c>
       <c r="G96" s="5"/>
       <c r="H96" s="5">
@@ -5000,10 +5000,10 @@
         <v>0</v>
       </c>
       <c r="J96" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K96" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K96" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L96" s="5" t="s">
         <v>14</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="97" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B97" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="B97" s="7" t="s">
-        <v>112</v>
-      </c>
       <c r="C97" s="6" t="s">
         <v>61</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E97" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="F97" s="5" t="s">
         <v>206</v>
-      </c>
-      <c r="F97" s="5" t="s">
-        <v>207</v>
       </c>
       <c r="G97" s="5"/>
       <c r="H97" s="5">
@@ -5036,10 +5036,10 @@
         <v>0</v>
       </c>
       <c r="J97" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K97" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K97" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L97" s="5" t="s">
         <v>14</v>
@@ -5047,7 +5047,7 @@
     </row>
     <row r="98" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>35</v>
@@ -5056,13 +5056,13 @@
         <v>61</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E98" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F98" s="5" t="s">
         <v>204</v>
-      </c>
-      <c r="F98" s="5" t="s">
-        <v>205</v>
       </c>
       <c r="G98" s="5"/>
       <c r="H98" s="5">
@@ -5083,7 +5083,7 @@
     </row>
     <row r="99" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B99" s="7" t="s">
         <v>35</v>
@@ -5092,13 +5092,13 @@
         <v>61</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E99" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F99" s="5" t="s">
         <v>204</v>
-      </c>
-      <c r="F99" s="5" t="s">
-        <v>205</v>
       </c>
       <c r="G99" s="5"/>
       <c r="H99" s="5">
@@ -5108,10 +5108,10 @@
         <v>0</v>
       </c>
       <c r="J99" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K99" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K99" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L99" s="5" t="s">
         <v>14</v>
@@ -5119,7 +5119,7 @@
     </row>
     <row r="100" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>45</v>
@@ -5128,13 +5128,13 @@
         <v>61</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E100" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F100" s="5" t="s">
         <v>204</v>
-      </c>
-      <c r="F100" s="5" t="s">
-        <v>205</v>
       </c>
       <c r="G100" s="5"/>
       <c r="H100" s="5">
@@ -5155,7 +5155,7 @@
     </row>
     <row r="101" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>45</v>
@@ -5164,13 +5164,13 @@
         <v>61</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E101" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F101" s="5" t="s">
         <v>204</v>
-      </c>
-      <c r="F101" s="5" t="s">
-        <v>205</v>
       </c>
       <c r="G101" s="5"/>
       <c r="H101" s="5">
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="J101" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K101" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K101" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L101" s="5" t="s">
         <v>14</v>
@@ -5191,7 +5191,7 @@
     </row>
     <row r="102" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>44</v>
@@ -5200,13 +5200,13 @@
         <v>61</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E102" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F102" s="5" t="s">
         <v>204</v>
-      </c>
-      <c r="F102" s="5" t="s">
-        <v>205</v>
       </c>
       <c r="G102" s="5"/>
       <c r="H102" s="5">
@@ -5227,7 +5227,7 @@
     </row>
     <row r="103" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B103" s="7" t="s">
         <v>44</v>
@@ -5236,13 +5236,13 @@
         <v>61</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E103" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F103" s="5" t="s">
         <v>204</v>
-      </c>
-      <c r="F103" s="5" t="s">
-        <v>205</v>
       </c>
       <c r="G103" s="5"/>
       <c r="H103" s="5">
@@ -5252,10 +5252,10 @@
         <v>14</v>
       </c>
       <c r="J103" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K103" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K103" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L103" s="5" t="s">
         <v>14</v>
@@ -5263,7 +5263,7 @@
     </row>
     <row r="104" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B104" s="5" t="s">
         <v>23</v>
@@ -5272,13 +5272,13 @@
         <v>61</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E104" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F104" s="5" t="s">
         <v>204</v>
-      </c>
-      <c r="F104" s="5" t="s">
-        <v>205</v>
       </c>
       <c r="G104" s="5"/>
       <c r="H104" s="5">
@@ -5299,7 +5299,7 @@
     </row>
     <row r="105" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B105" s="7" t="s">
         <v>23</v>
@@ -5308,13 +5308,13 @@
         <v>61</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E105" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F105" s="5" t="s">
         <v>204</v>
-      </c>
-      <c r="F105" s="5" t="s">
-        <v>205</v>
       </c>
       <c r="G105" s="5"/>
       <c r="H105" s="5">
@@ -5324,10 +5324,10 @@
         <v>1</v>
       </c>
       <c r="J105" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K105" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K105" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L105" s="5" t="s">
         <v>14</v>
@@ -5335,7 +5335,7 @@
     </row>
     <row r="106" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B106" s="5" t="s">
         <v>52</v>
@@ -5344,13 +5344,13 @@
         <v>61</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E106" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F106" s="5" t="s">
         <v>204</v>
-      </c>
-      <c r="F106" s="5" t="s">
-        <v>205</v>
       </c>
       <c r="G106" s="5"/>
       <c r="H106" s="5">
@@ -5371,7 +5371,7 @@
     </row>
     <row r="107" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B107" s="7" t="s">
         <v>52</v>
@@ -5380,13 +5380,13 @@
         <v>61</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E107" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F107" s="5" t="s">
         <v>204</v>
-      </c>
-      <c r="F107" s="5" t="s">
-        <v>205</v>
       </c>
       <c r="G107" s="5"/>
       <c r="H107" s="5">
@@ -5396,10 +5396,10 @@
         <v>0</v>
       </c>
       <c r="J107" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K107" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K107" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L107" s="5" t="s">
         <v>14</v>
@@ -5407,7 +5407,7 @@
     </row>
     <row r="108" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B108" s="5" t="s">
         <v>51</v>
@@ -5416,13 +5416,13 @@
         <v>61</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E108" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F108" s="5" t="s">
         <v>204</v>
-      </c>
-      <c r="F108" s="5" t="s">
-        <v>205</v>
       </c>
       <c r="G108" s="5"/>
       <c r="H108" s="5">
@@ -5443,7 +5443,7 @@
     </row>
     <row r="109" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B109" s="7" t="s">
         <v>51</v>
@@ -5452,13 +5452,13 @@
         <v>61</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E109" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F109" s="5" t="s">
         <v>204</v>
-      </c>
-      <c r="F109" s="5" t="s">
-        <v>205</v>
       </c>
       <c r="G109" s="5"/>
       <c r="H109" s="5">
@@ -5468,10 +5468,10 @@
         <v>0</v>
       </c>
       <c r="J109" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K109" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K109" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L109" s="5" t="s">
         <v>14</v>
@@ -5479,7 +5479,7 @@
     </row>
     <row r="110" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B110" s="5" t="s">
         <v>46</v>
@@ -5488,13 +5488,13 @@
         <v>61</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G110" s="5"/>
       <c r="H110" s="5">
@@ -5515,7 +5515,7 @@
     </row>
     <row r="111" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B111" s="7" t="s">
         <v>46</v>
@@ -5524,13 +5524,13 @@
         <v>61</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G111" s="5"/>
       <c r="H111" s="5">
@@ -5540,10 +5540,10 @@
         <v>0</v>
       </c>
       <c r="J111" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K111" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K111" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L111" s="5" t="s">
         <v>14</v>
@@ -5551,7 +5551,7 @@
     </row>
     <row r="112" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>47</v>
@@ -5560,13 +5560,13 @@
         <v>61</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G112" s="5"/>
       <c r="H112" s="5">
@@ -5587,7 +5587,7 @@
     </row>
     <row r="113" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B113" s="7" t="s">
         <v>47</v>
@@ -5596,13 +5596,13 @@
         <v>61</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G113" s="5"/>
       <c r="H113" s="5">
@@ -5612,10 +5612,10 @@
         <v>1</v>
       </c>
       <c r="J113" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K113" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K113" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L113" s="5" t="s">
         <v>14</v>
@@ -5623,7 +5623,7 @@
     </row>
     <row r="114" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>48</v>
@@ -5632,13 +5632,13 @@
         <v>61</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G114" s="5"/>
       <c r="H114" s="5">
@@ -5659,7 +5659,7 @@
     </row>
     <row r="115" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B115" s="7" t="s">
         <v>48</v>
@@ -5668,13 +5668,13 @@
         <v>61</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G115" s="5"/>
       <c r="H115" s="5">
@@ -5684,10 +5684,10 @@
         <v>46</v>
       </c>
       <c r="J115" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K115" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K115" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L115" s="5" t="s">
         <v>14</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="116" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B116" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="B116" s="7" t="s">
-        <v>98</v>
-      </c>
       <c r="C116" s="6" t="s">
         <v>61</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G116" s="5"/>
       <c r="H116" s="5">
@@ -5720,10 +5720,10 @@
         <v>0</v>
       </c>
       <c r="J116" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K116" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K116" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L116" s="5" t="s">
         <v>14</v>
@@ -5731,7 +5731,7 @@
     </row>
     <row r="117" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>36</v>
@@ -5740,13 +5740,13 @@
         <v>61</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G117" s="5"/>
       <c r="H117" s="5">
@@ -5767,7 +5767,7 @@
     </row>
     <row r="118" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B118" s="7" t="s">
         <v>36</v>
@@ -5776,13 +5776,13 @@
         <v>61</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G118" s="5"/>
       <c r="H118" s="5">
@@ -5792,10 +5792,10 @@
         <v>0</v>
       </c>
       <c r="J118" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K118" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K118" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L118" s="5" t="s">
         <v>14</v>
@@ -5803,7 +5803,7 @@
     </row>
     <row r="119" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>38</v>
@@ -5812,13 +5812,13 @@
         <v>61</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G119" s="5"/>
       <c r="H119" s="5">
@@ -5839,7 +5839,7 @@
     </row>
     <row r="120" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B120" s="7" t="s">
         <v>38</v>
@@ -5848,13 +5848,13 @@
         <v>61</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G120" s="5"/>
       <c r="H120" s="5">
@@ -5864,10 +5864,10 @@
         <v>59</v>
       </c>
       <c r="J120" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K120" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K120" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L120" s="5" t="s">
         <v>14</v>
@@ -5875,7 +5875,7 @@
     </row>
     <row r="121" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>39</v>
@@ -5884,13 +5884,13 @@
         <v>61</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G121" s="5"/>
       <c r="H121" s="5">
@@ -5911,7 +5911,7 @@
     </row>
     <row r="122" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B122" s="7" t="s">
         <v>39</v>
@@ -5920,13 +5920,13 @@
         <v>61</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G122" s="5"/>
       <c r="H122" s="5">
@@ -5936,10 +5936,10 @@
         <v>0</v>
       </c>
       <c r="J122" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K122" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K122" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L122" s="5" t="s">
         <v>14</v>
@@ -5947,7 +5947,7 @@
     </row>
     <row r="123" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>37</v>
@@ -5956,13 +5956,13 @@
         <v>61</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G123" s="5"/>
       <c r="H123" s="5">
@@ -5983,7 +5983,7 @@
     </row>
     <row r="124" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B124" s="7" t="s">
         <v>37</v>
@@ -5992,13 +5992,13 @@
         <v>61</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G124" s="5"/>
       <c r="H124" s="5">
@@ -6008,10 +6008,10 @@
         <v>0</v>
       </c>
       <c r="J124" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K124" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K124" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L124" s="5" t="s">
         <v>14</v>
@@ -6019,7 +6019,7 @@
     </row>
     <row r="125" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B125" s="5" t="s">
         <v>24</v>
@@ -6028,13 +6028,13 @@
         <v>61</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G125" s="5"/>
       <c r="H125" s="5">
@@ -6055,7 +6055,7 @@
     </row>
     <row r="126" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B126" s="7" t="s">
         <v>24</v>
@@ -6064,13 +6064,13 @@
         <v>61</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F126" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G126" s="5"/>
       <c r="H126" s="5">
@@ -6080,10 +6080,10 @@
         <v>0</v>
       </c>
       <c r="J126" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K126" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K126" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L126" s="5" t="s">
         <v>14</v>
@@ -6091,7 +6091,7 @@
     </row>
     <row r="127" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B127" s="5" t="s">
         <v>30</v>
@@ -6100,13 +6100,13 @@
         <v>61</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F127" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G127" s="5"/>
       <c r="H127" s="5">
@@ -6127,7 +6127,7 @@
     </row>
     <row r="128" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B128" s="7" t="s">
         <v>30</v>
@@ -6136,13 +6136,13 @@
         <v>61</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F128" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G128" s="5"/>
       <c r="H128" s="5">
@@ -6152,10 +6152,10 @@
         <v>0</v>
       </c>
       <c r="J128" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K128" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K128" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L128" s="5" t="s">
         <v>14</v>
@@ -6163,7 +6163,7 @@
     </row>
     <row r="129" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B129" s="5" t="s">
         <v>25</v>
@@ -6172,13 +6172,13 @@
         <v>61</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F129" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G129" s="5"/>
       <c r="H129" s="5">
@@ -6199,7 +6199,7 @@
     </row>
     <row r="130" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B130" s="7" t="s">
         <v>25</v>
@@ -6208,13 +6208,13 @@
         <v>61</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F130" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G130" s="5"/>
       <c r="H130" s="5">
@@ -6224,10 +6224,10 @@
         <v>0</v>
       </c>
       <c r="J130" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K130" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K130" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L130" s="5" t="s">
         <v>14</v>
@@ -6235,7 +6235,7 @@
     </row>
     <row r="131" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B131" s="7" t="s">
         <v>34</v>
@@ -6244,13 +6244,13 @@
         <v>61</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E131" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="F131" s="5" t="s">
         <v>206</v>
-      </c>
-      <c r="F131" s="5" t="s">
-        <v>207</v>
       </c>
       <c r="G131" s="5"/>
       <c r="H131" s="5">
@@ -6260,10 +6260,10 @@
         <v>15</v>
       </c>
       <c r="J131" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K131" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K131" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L131" s="5" t="s">
         <v>14</v>
@@ -6271,22 +6271,22 @@
     </row>
     <row r="132" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B132" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="B132" s="7" t="s">
-        <v>84</v>
-      </c>
       <c r="C132" s="6" t="s">
         <v>61</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G132" s="5"/>
       <c r="H132" s="5">
@@ -6296,10 +6296,10 @@
         <v>0</v>
       </c>
       <c r="J132" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K132" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K132" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L132" s="5" t="s">
         <v>14</v>
@@ -6307,7 +6307,7 @@
     </row>
     <row r="133" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B133" s="5" t="s">
         <v>31</v>
@@ -6316,13 +6316,13 @@
         <v>61</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G133" s="5"/>
       <c r="H133" s="5">
@@ -6343,7 +6343,7 @@
     </row>
     <row r="134" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>31</v>
@@ -6352,13 +6352,13 @@
         <v>61</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G134" s="5"/>
       <c r="H134" s="5">
@@ -6368,10 +6368,10 @@
         <v>0</v>
       </c>
       <c r="J134" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K134" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K134" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L134" s="5" t="s">
         <v>14</v>
@@ -6379,22 +6379,22 @@
     </row>
     <row r="135" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="B135" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="B135" s="7" t="s">
-        <v>102</v>
-      </c>
       <c r="C135" s="6" t="s">
         <v>61</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G135" s="5"/>
       <c r="H135" s="5">
@@ -6404,10 +6404,10 @@
         <v>0</v>
       </c>
       <c r="J135" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K135" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K135" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L135" s="5" t="s">
         <v>14</v>
@@ -6415,7 +6415,7 @@
     </row>
     <row r="136" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B136" s="5" t="s">
         <v>32</v>
@@ -6424,13 +6424,13 @@
         <v>61</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G136" s="5"/>
       <c r="H136" s="5">
@@ -6451,7 +6451,7 @@
     </row>
     <row r="137" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B137" s="7" t="s">
         <v>32</v>
@@ -6460,13 +6460,13 @@
         <v>61</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G137" s="5"/>
       <c r="H137" s="5">
@@ -6476,10 +6476,10 @@
         <v>0</v>
       </c>
       <c r="J137" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K137" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K137" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L137" s="5" t="s">
         <v>14</v>
@@ -6487,7 +6487,7 @@
     </row>
     <row r="138" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B138" s="5" t="s">
         <v>40</v>
@@ -6496,13 +6496,13 @@
         <v>61</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G138" s="5"/>
       <c r="H138" s="5">
@@ -6523,7 +6523,7 @@
     </row>
     <row r="139" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B139" s="7" t="s">
         <v>40</v>
@@ -6532,13 +6532,13 @@
         <v>61</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F139" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G139" s="5"/>
       <c r="H139" s="5">
@@ -6548,10 +6548,10 @@
         <v>0</v>
       </c>
       <c r="J139" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K139" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="K139" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="L139" s="5" t="s">
         <v>14</v>
@@ -6560,62 +6560,62 @@
   </sheetData>
   <autoFilter ref="A1:L139" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}"/>
   <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="A8:A9 A3:A6 A11 A13 A16:A19">
+    <cfRule type="duplicateValues" dxfId="32" priority="835"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A22:A25 A28:A29">
+    <cfRule type="duplicateValues" dxfId="31" priority="828"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A22:A25">
+    <cfRule type="duplicateValues" dxfId="30" priority="834"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A32:A33 A30">
+    <cfRule type="duplicateValues" dxfId="29" priority="827"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="826"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="32" priority="821"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="821"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D3:D6">
+    <cfRule type="duplicateValues" dxfId="26" priority="867" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="863"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="864"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="865" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="866" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D7:D10">
-    <cfRule type="duplicateValues" dxfId="31" priority="126"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="127"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="128"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="129"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="130"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="131"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="132" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="133" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="127"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="128"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="129"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="130"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="131"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="132" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="133" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="126"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D11:D12">
-    <cfRule type="duplicateValues" dxfId="23" priority="162" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="163"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="164"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="165"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="162" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="163"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="164"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="165"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D19">
+    <cfRule type="duplicateValues" dxfId="9" priority="847" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="848"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="849"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="850"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
-    <cfRule type="duplicateValues" dxfId="19" priority="824"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="825" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="824"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="825" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="duplicateValues" dxfId="17" priority="819"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="820" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="820" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="819"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:L1">
-    <cfRule type="duplicateValues" dxfId="15" priority="817"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="818" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A32:A33 A30">
-    <cfRule type="duplicateValues" dxfId="13" priority="826"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="827"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A22:A25 A28:A29">
-    <cfRule type="duplicateValues" dxfId="11" priority="828"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A22:A25">
-    <cfRule type="duplicateValues" dxfId="10" priority="834"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A8:A9 A3:A6 A11 A13 A16:A19">
-    <cfRule type="duplicateValues" dxfId="9" priority="835"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D19">
-    <cfRule type="duplicateValues" dxfId="8" priority="847" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="848"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="849"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="850"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D3:D6">
-    <cfRule type="duplicateValues" dxfId="4" priority="863"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="864"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="865" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="866" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="867" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="818" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="817"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/input/Inventory_snapshot_WM.xlsx
+++ b/data/input/Inventory_snapshot_WM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 15\White_Mulberry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B948A24B-DF61-48BA-923C-2742972BCB95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02953720-CA53-4240-A7CB-F003D57B1BE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D49B0F4C-5F9E-467E-8AD9-9E638F42404F}"/>
   </bookViews>
@@ -857,7 +857,47 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 6" xfId="1" xr:uid="{E5F241CE-C0FC-4730-81C9-F1901EB82A3C}"/>
   </cellStyles>
-  <dxfs count="134">
+  <dxfs count="135">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1128,36 +1168,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -1222,26 +1232,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -1326,6 +1316,236 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -1390,236 +1610,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -1664,46 +1654,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -1788,6 +1738,206 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -1832,206 +1982,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -2044,6 +1994,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -2156,6 +2116,96 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -2170,46 +2220,6 @@
       <font>
         <condense val="0"/>
         <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -7661,205 +7671,204 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L141" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}"/>
   <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="A3:A27">
+    <cfRule type="duplicateValues" dxfId="134" priority="1001"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A27">
-    <cfRule type="duplicateValues" dxfId="133" priority="357"/>
-    <cfRule type="duplicateValues" dxfId="132" priority="358"/>
-    <cfRule type="duplicateValues" dxfId="131" priority="359"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="362"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="363" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="364" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="130" priority="360"/>
     <cfRule type="duplicateValues" dxfId="129" priority="361"/>
-    <cfRule type="duplicateValues" dxfId="128" priority="362"/>
-    <cfRule type="duplicateValues" dxfId="127" priority="363" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="126" priority="364" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="359"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="358"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="357"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A33:A43">
+    <cfRule type="duplicateValues" dxfId="125" priority="969"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A44:A66">
+    <cfRule type="duplicateValues" dxfId="124" priority="945"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="946"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A74:A84">
-    <cfRule type="duplicateValues" dxfId="125" priority="104"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="104"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A108:A132">
-    <cfRule type="duplicateValues" dxfId="124" priority="908"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="908"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A132">
-    <cfRule type="duplicateValues" dxfId="123" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="122" priority="856"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="856"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D17 D5:D15">
+    <cfRule type="duplicateValues" dxfId="118" priority="976" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="975"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D18:D27">
-    <cfRule type="duplicateValues" dxfId="121" priority="168"/>
-    <cfRule type="duplicateValues" dxfId="120" priority="169"/>
-    <cfRule type="duplicateValues" dxfId="119" priority="170"/>
-    <cfRule type="duplicateValues" dxfId="118" priority="171"/>
-    <cfRule type="duplicateValues" dxfId="117" priority="172"/>
-    <cfRule type="duplicateValues" dxfId="116" priority="173"/>
-    <cfRule type="duplicateValues" dxfId="115" priority="174" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="114" priority="175" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="168"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="172"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="170"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="169"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="171"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="174" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="173"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="175" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D29:D32">
+    <cfRule type="duplicateValues" dxfId="108" priority="951"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="950"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="956" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="955" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="954"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="953"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="952"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="949"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D75">
-    <cfRule type="duplicateValues" dxfId="113" priority="99" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="112" priority="100"/>
-    <cfRule type="duplicateValues" dxfId="111" priority="101" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="110" priority="102"/>
-    <cfRule type="duplicateValues" dxfId="109" priority="103" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="101" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="103" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="99" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="100"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D76">
-    <cfRule type="duplicateValues" dxfId="108" priority="94"/>
-    <cfRule type="duplicateValues" dxfId="107" priority="95"/>
-    <cfRule type="duplicateValues" dxfId="106" priority="96" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="105" priority="97" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="104" priority="98" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="95"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="96" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="97" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="98" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="94"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D77">
-    <cfRule type="duplicateValues" dxfId="103" priority="89"/>
-    <cfRule type="duplicateValues" dxfId="102" priority="90"/>
-    <cfRule type="duplicateValues" dxfId="101" priority="91" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="100" priority="92" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="99" priority="93" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="92" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="91" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="93" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D78">
-    <cfRule type="duplicateValues" dxfId="98" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="88"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D82">
-    <cfRule type="duplicateValues" dxfId="97" priority="80"/>
-    <cfRule type="duplicateValues" dxfId="96" priority="81"/>
-    <cfRule type="duplicateValues" dxfId="95" priority="82"/>
-    <cfRule type="duplicateValues" dxfId="94" priority="83"/>
-    <cfRule type="duplicateValues" dxfId="93" priority="84"/>
-    <cfRule type="duplicateValues" dxfId="92" priority="85"/>
-    <cfRule type="duplicateValues" dxfId="91" priority="86" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="90" priority="87" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="87" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="86" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D83:D84">
-    <cfRule type="duplicateValues" dxfId="89" priority="72"/>
-    <cfRule type="duplicateValues" dxfId="88" priority="73"/>
-    <cfRule type="duplicateValues" dxfId="87" priority="74"/>
-    <cfRule type="duplicateValues" dxfId="86" priority="75"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="76"/>
-    <cfRule type="duplicateValues" dxfId="84" priority="77"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="78" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="82" priority="79" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="78" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="79" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D85:D107">
-    <cfRule type="duplicateValues" dxfId="81" priority="921"/>
-    <cfRule type="duplicateValues" dxfId="80" priority="922"/>
-    <cfRule type="duplicateValues" dxfId="79" priority="923"/>
-    <cfRule type="duplicateValues" dxfId="78" priority="924"/>
-    <cfRule type="duplicateValues" dxfId="77" priority="925"/>
-    <cfRule type="duplicateValues" dxfId="76" priority="926"/>
-    <cfRule type="duplicateValues" dxfId="75" priority="927" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="74" priority="928" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="928" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="927" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="926"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="924"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="923"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="922"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="921"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="925"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D113">
-    <cfRule type="duplicateValues" dxfId="73" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="72" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="55" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="56" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="57" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="57" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="56" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="55" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D114:D123 D110:D112">
-    <cfRule type="duplicateValues" dxfId="68" priority="58"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="59" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="60"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="61" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="61" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="59" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D119:D122">
-    <cfRule type="duplicateValues" dxfId="64" priority="52" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="52" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D124:D125">
-    <cfRule type="duplicateValues" dxfId="63" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="49" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="60" priority="50" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="51" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="50" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="51" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="49" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D126">
-    <cfRule type="duplicateValues" dxfId="58" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="44" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="45" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="46" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="46" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="44" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="45" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D127">
-    <cfRule type="duplicateValues" dxfId="53" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D129">
-    <cfRule type="duplicateValues" dxfId="52" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="39" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="40" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="39" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="40" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D130">
-    <cfRule type="duplicateValues" dxfId="44" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="31" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="32" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="32" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="31" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D131">
-    <cfRule type="duplicateValues" dxfId="36" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="23" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="24" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="24" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="23" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D133:D141">
+    <cfRule type="duplicateValues" dxfId="15" priority="929"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="930"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="931"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="932"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="933"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="934"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="935" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="936" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
-    <cfRule type="duplicateValues" dxfId="28" priority="906"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="907" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="1002"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1003" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="duplicateValues" dxfId="26" priority="854"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="855" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="854"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="855" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I67:I73">
-    <cfRule type="duplicateValues" dxfId="24" priority="105"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="105"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:L1">
-    <cfRule type="duplicateValues" dxfId="23" priority="852"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="853" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D133:D141">
-    <cfRule type="duplicateValues" dxfId="21" priority="929"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="930"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="931"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="932"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="933"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="934"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="935" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="936" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A44:A66">
-    <cfRule type="duplicateValues" dxfId="13" priority="945"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="946"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D29:D32">
-    <cfRule type="duplicateValues" dxfId="11" priority="949"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="950"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="951"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="952"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="953"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="954"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="955" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="956" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A33:A43">
-    <cfRule type="duplicateValues" dxfId="3" priority="969"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D17 D5:D15">
-    <cfRule type="duplicateValues" dxfId="2" priority="975"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="976" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A3:A27">
-    <cfRule type="duplicateValues" dxfId="0" priority="1001"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="852"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="853" stopIfTrue="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/input/Inventory_snapshot_WM.xlsx
+++ b/data/input/Inventory_snapshot_WM.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 16\White_Mulberry\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F08F2FEB-E7F0-4E0B-A18E-C6BF8279985D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -863,6 +863,76 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -875,6 +945,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -917,106 +997,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -1101,6 +1081,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -1113,6 +1113,36 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -1145,46 +1175,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -1259,46 +1249,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -1341,6 +1291,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -1353,6 +1323,66 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -1474,6 +1504,206 @@
         <color rgb="FF9C0006"/>
       </font>
       <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -1485,236 +1715,6 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
@@ -7320,126 +7320,126 @@
   </sheetData>
   <autoFilter ref="A1:L138" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}"/>
   <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="A66:A124">
+    <cfRule type="duplicateValues" dxfId="84" priority="1704"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A138">
+    <cfRule type="duplicateValues" dxfId="83" priority="1678"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="84" priority="1430"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="1430"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D67">
-    <cfRule type="duplicateValues" dxfId="83" priority="260"/>
-    <cfRule type="duplicateValues" dxfId="82" priority="261"/>
     <cfRule type="duplicateValues" dxfId="81" priority="262" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="80" priority="263" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="79" priority="264" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="260"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="261"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="263" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="264" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D68:D71">
-    <cfRule type="duplicateValues" dxfId="78" priority="1654"/>
-    <cfRule type="duplicateValues" dxfId="77" priority="1655"/>
-    <cfRule type="duplicateValues" dxfId="76" priority="1656" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="1658" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="75" priority="1657" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="74" priority="1658" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="1656" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="1655"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="1654"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D72:D73">
-    <cfRule type="duplicateValues" dxfId="73" priority="1634"/>
-    <cfRule type="duplicateValues" dxfId="72" priority="1635"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="1636" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="1637" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="1638" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="1635"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="1638" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="1637" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="1636" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="1634"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D74:D83">
-    <cfRule type="duplicateValues" dxfId="68" priority="1601"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="1602"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="1603" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="1604" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="1602"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="1601"/>
     <cfRule type="duplicateValues" dxfId="64" priority="1605" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="1604" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="1603" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D84:D88">
-    <cfRule type="duplicateValues" dxfId="63" priority="1530"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="1531"/>
     <cfRule type="duplicateValues" dxfId="61" priority="1532"/>
-    <cfRule type="duplicateValues" dxfId="60" priority="1533"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="1534"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="1537" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="1536" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="58" priority="1535"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="1536" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="1537" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="1534"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="1533"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="1531"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="1530"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D89">
-    <cfRule type="duplicateValues" dxfId="55" priority="1461"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="1462"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="1463"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="1464"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="1465"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="1466"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="1467" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="1468" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="1466"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="1467" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="1468" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="1461"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="1462"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="1463"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="1464"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="1465"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D90:D91">
-    <cfRule type="duplicateValues" dxfId="47" priority="270" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="271"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="272"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="273"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="273"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="270" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="271"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="272"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D93:D96">
-    <cfRule type="duplicateValues" dxfId="43" priority="1446" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="1447"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="1448"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="1449"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="1449"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="1448"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="1447"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="1446" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D97:D102">
-    <cfRule type="duplicateValues" dxfId="39" priority="278"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="279"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="280"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="281"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="282"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="283"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="284" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="281"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="279"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="280"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="282"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="283"/>
     <cfRule type="duplicateValues" dxfId="32" priority="285" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="284" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="278"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D103:D114">
-    <cfRule type="duplicateValues" dxfId="31" priority="286"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="287"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="288"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="289"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="290"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="291"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="292" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="293" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="289"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="293" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="286"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="287"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="288"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="292" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="291"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="290"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D115:D124">
+    <cfRule type="duplicateValues" dxfId="21" priority="1699"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="1696"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="1697"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="1698"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="1700"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="1701"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="1702" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="1703" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D138">
-    <cfRule type="duplicateValues" dxfId="23" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="47" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="48" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="47" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="48" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
-    <cfRule type="duplicateValues" dxfId="15" priority="1675"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="1676" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="1675"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1676" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="duplicateValues" dxfId="13" priority="1428"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="1429" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1428"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1429" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:L1">
-    <cfRule type="duplicateValues" dxfId="11" priority="1426"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="1427" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A138">
-    <cfRule type="duplicateValues" dxfId="9" priority="1678"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D115:D124">
-    <cfRule type="duplicateValues" dxfId="8" priority="1696"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="1697"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="1698"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="1699"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="1700"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="1701"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="1702" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="1703" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A66:A124">
-    <cfRule type="duplicateValues" dxfId="0" priority="1704"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1426"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1427" stopIfTrue="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/input/Inventory_snapshot_WM.xlsx
+++ b/data/input/Inventory_snapshot_WM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 24\White_Mulberry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A16D1F8-7575-46A2-83E9-0D40E7F1EA0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F89954FD-4069-4718-862D-D36987A021E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D49B0F4C-5F9E-467E-8AD9-9E638F42404F}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$71</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="99">
   <si>
     <t>SKU</t>
   </si>
@@ -315,12 +315,6 @@
     <t>B2B - AMPM</t>
   </si>
   <si>
-    <t>Pipeline</t>
-  </si>
-  <si>
-    <t>In-Transit Inventory</t>
-  </si>
-  <si>
     <t>Open Order</t>
   </si>
   <si>
@@ -334,17 +328,19 @@
   </si>
   <si>
     <t>1P</t>
+  </si>
+  <si>
+    <t>WM1ML</t>
+  </si>
+  <si>
+    <t>TVCT1ML</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -396,12 +392,6 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF1F2937"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -447,13 +437,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -479,41 +468,16 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="4">
-    <cellStyle name="Comma" xfId="3" builtinId="3"/>
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{697FC575-8A7C-4715-A8F0-2950C62D8576}"/>
     <cellStyle name="Normal 6" xfId="1" xr:uid="{E5F241CE-C0FC-4730-81C9-F1901EB82A3C}"/>
   </cellStyles>
-  <dxfs count="11">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="9">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -934,7 +898,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}">
-  <dimension ref="A1:L74"/>
+  <dimension ref="A1:L73"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.88671875" style="1" bestFit="1" customWidth="1"/>
@@ -2371,160 +2335,151 @@
       </c>
     </row>
     <row r="62" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="4" t="s">
+      <c r="A62" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B62" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I62" s="9">
+        <v>5</v>
+      </c>
+      <c r="J62" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K62" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="L62" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B63" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I63" s="9">
+        <v>4</v>
+      </c>
+      <c r="J63" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K63" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="L63" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B64" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I64" s="9">
+        <v>3</v>
+      </c>
+      <c r="J64" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K64" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="L64" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B65" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I65" s="9">
+        <v>2</v>
+      </c>
+      <c r="J65" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K65" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="L65" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B66" t="s">
+        <v>63</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I66" s="1">
+        <v>42</v>
+      </c>
+      <c r="J66" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="L66" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B67" t="s">
+        <v>50</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I67" s="1">
+        <v>22</v>
+      </c>
+      <c r="J67" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K67" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="L67" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B68" t="s">
+        <v>47</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I68" s="1">
         <v>15</v>
       </c>
-      <c r="B62" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="I62" s="10">
-        <v>500</v>
-      </c>
-      <c r="J62" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="K62" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="L62" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B63" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="I63" s="10">
-        <v>1000</v>
-      </c>
-      <c r="J63" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="K63" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="L63" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B64" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C64" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="I64" s="10">
-        <v>1000</v>
-      </c>
-      <c r="J64" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="K64" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="L64" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B65" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I65" s="11">
-        <v>5</v>
-      </c>
-      <c r="J65" s="7" t="s">
+      <c r="J68" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="K65" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="L65" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B66" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I66" s="11">
-        <v>4</v>
-      </c>
-      <c r="J66" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="K66" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="L66" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="B67" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I67" s="11">
-        <v>3</v>
-      </c>
-      <c r="J67" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="K67" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="L67" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B68" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I68" s="11">
-        <v>2</v>
-      </c>
-      <c r="J68" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="K68" s="8" t="s">
+      <c r="K68" s="1" t="s">
         <v>96</v>
       </c>
       <c r="L68" s="1" t="s">
@@ -2533,19 +2488,19 @@
     </row>
     <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>85</v>
       </c>
       <c r="I69" s="1">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="L69" s="1" t="s">
         <v>82</v>
@@ -2553,19 +2508,19 @@
     </row>
     <row r="70" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>85</v>
       </c>
       <c r="I70" s="1">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="L70" s="1" t="s">
         <v>82</v>
@@ -2573,113 +2528,86 @@
     </row>
     <row r="71" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>85</v>
       </c>
       <c r="I71" s="1">
-        <v>15</v>
+        <v>107</v>
       </c>
       <c r="J71" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="L71" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D72" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="K71" s="1" t="s">
+      <c r="I72" s="1">
+        <v>1000</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D73" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="L71" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B72" t="s">
-        <v>62</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I72" s="1">
-        <v>19</v>
-      </c>
-      <c r="J72" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="K72" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="L72" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B73" t="s">
-        <v>48</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>85</v>
-      </c>
       <c r="I73" s="1">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="K73" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="L73" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B74" t="s">
-        <v>46</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I74" s="1">
-        <v>107</v>
-      </c>
-      <c r="J74" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="K74" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="L74" s="1" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L74" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}"/>
   <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="A35:A56">
+    <cfRule type="duplicateValues" dxfId="8" priority="2168"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A62:A65">
+    <cfRule type="duplicateValues" dxfId="7" priority="2161"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="10" priority="1894"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1894"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
-    <cfRule type="duplicateValues" dxfId="9" priority="2105"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="2106" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="2105"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="2106" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="duplicateValues" dxfId="7" priority="1892"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="1893" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1892"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1893" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:L1">
-    <cfRule type="duplicateValues" dxfId="5" priority="1890"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="1891" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A65:A68">
-    <cfRule type="duplicateValues" dxfId="3" priority="2161"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A63:A64">
-    <cfRule type="duplicateValues" dxfId="2" priority="2164"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A62">
-    <cfRule type="duplicateValues" dxfId="1" priority="2165"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A35:A56">
-    <cfRule type="duplicateValues" dxfId="0" priority="2168"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1890"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1891" stopIfTrue="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/input/Inventory_snapshot_WM.xlsx
+++ b/data/input/Inventory_snapshot_WM.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -612,7 +612,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1886,6 +1886,2274 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>FBA79176</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>B0CPT25SD8</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>WM-MD09-BK</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>FBK76387</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>B0BF4S7V8C</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>WM-MH05P-WH</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>FBA79658</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>B0DQ1PKNSP</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>WM-MDL-WH</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>FBA79659</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>B0DQ1NV8D2</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>WM-MDL-BK</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>FBAA75450</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>B0B68FKVC1</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>6822-150-SIOC</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>FBAA75445</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>B0B68B17RT</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>6822-167-SIOC</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>FBA76412</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>B0BLVB8VTH</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>6023-210-SIOC</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>FBA79179</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>B0CPT3Q25C</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>WM-SE08-CF</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>FBAA75451</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>B0B68HQVXW</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>6023-7664-SIOC</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>FBAA75446</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>B0B689CVJW</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>6320-150-SIOC</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>FBA76411</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>B0BFFD156C</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>6780-3139-WHT-SIOC</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>FBA76383</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>B0BF4TKQKN</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>WM-SEH04P-BK</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>FBA76388</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>B0BF4VRJJ1</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>WM-SEH04P-WH</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>FBAA75452</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>B0B68DCXS5</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>6054-2364</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>FBA76415</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>B0BFWD6SNF</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>WM-LOD-CF</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="n">
+        <v>8</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>FBA76391</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>B0BF4WQNJR</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>WM-CT03OA-100</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>FBA79164</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>B0CPFN27Z2</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>WM-USE06-BK</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>FBA79177</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>B0CPT34B2L</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>WM-SE08-BK</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>FBAA75449</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>B0B68DWHMR</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>6779-4414-SIOC</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>FBA79178</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>B0CPT2NY5M</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>WM-SE08-WH</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>FBA79165</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>B0CPFPT6DZ</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>WM-USE06-WH</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>FBA76416</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>B0BFW59TRG</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>WM-LOD-BK</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>FBA76858</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>B0BNDYQ5ZR</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>6023-4139-CB</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>FBA76389</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>B0BF4XF7SD</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>WM-CT03OA-120</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>FBA76413</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>B0BJZNQYVB</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>6070--1723</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>FBAA75454</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>B0B6ZP6XK7</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>6070-3436</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>FBA76384</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>B0BF4VWQXG</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>WM-SWZ0021-BK</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>FBA76410</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>B0BFF9KB2T</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>6705-3871-BLK-BB</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>FBA76865</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>B0BF4Y92MW</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>WM-CT03MA-100</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>FBAA75444</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>B0B65XBXKY</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>6023-8709-SIOC</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>FBK76764</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>B0BMV1WPHL</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>WM-MH05P-CF</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>FBA76385</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>B0BF4WD8Z8</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>WM-DT02-BK</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>FBA76386</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>B0BF51HCY4</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>WM-CT03MA-120</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>FBAA75453</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>B0B68GMXR9</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>6705-3945</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>FBA76409</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>B0BFDW7HY5</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>6060-430</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>FBAA75447</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>B0B688NL1N</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>6021-3081-BB</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>FBAA75448</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>B0B68BJCL5</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>6779-4892</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>FBA76407</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>B0BFBMCTXQ</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>6486-1746-WHT</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>FBA76859</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>B0BNDY71BZ</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>6023-1168</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>FBA76765</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>B0BMQQQ7YD</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>WM-SEH04P-CF</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>FBA76417</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>B0BFVMDJ2K</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>WM-LOD-WH</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>FBA76419</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>B0BFW5K3F1</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>WM-OD-CL</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>FBA78766</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>B0CBJX85Q2</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>WM-SEH05P-WH</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>FBA78765</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>B0CBJX8WGY</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>WM-SEH05P-BK</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>FBA78767</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>B0CBJZGW7X</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>WM-SEH05P-CF</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>FBA78772</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>B0CGF7HXXL</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>WM-MH03-BK</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>FBA78774</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>B0CGF82HTJ</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>WM-SEH05R-BK</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>FBA78775</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>B0CGF7MQMF</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>WM-SEH05R-WH</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>FBA79167</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>B0CPFS24ML</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>WM-GD07-CB</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>FBA79433</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>B0DC3JRBW1</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>WM-SE08-WD</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>FBA79434</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>B0DC3SJMZ6</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>WM-USE06-WB</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>FBA79435</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>B0DC3NPKGF</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>WM-USE06-WW</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>FBA79476</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>WM-GS1M-BK</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="n">
+        <v>357</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>FBA79479</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>B0DB5YTQZV</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>WM-HA2M-BK</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="n">
+        <v>66</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>FBA79667</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>B0DQPK7MFH</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>WM-LODN-WH</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>FBA79669</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>B0DQPLMQQ7</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>WM-LWS-CF</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>FBA79670</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>B0DQPGLK2T</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>WM-LWS-GR</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>FBA79663</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>B0DQPFL835</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>WM-LODJ-CF</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>FBA79614</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>B0DP313R77</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>MS2ML</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>FBA79660</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>B0DQ4ZK2WQ</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>WM-MODL-BBW</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>FBA79661</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>B0DQ51R95T</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>WM-MODL-BK</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>FBK79792</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>B0FN4JG97R</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>HDMSP1ML</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>FBK79788</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>B0FN4D3C89</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>TVCT1ML</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/input/Inventory_snapshot_WM.xlsx
+++ b/data/input/Inventory_snapshot_WM.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 28\White_Mulberry\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 29\White_Mulberry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B14C036C-1F7E-4F3E-A5F2-0394F75E553B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6025F7A6-FDA6-42F2-864C-76D3ACDD785C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D49B0F4C-5F9E-467E-8AD9-9E638F42404F}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$41</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="90">
   <si>
     <t>SKU</t>
   </si>
@@ -114,12 +114,6 @@
     <t>FBA79662</t>
   </si>
   <si>
-    <t>FBA79668</t>
-  </si>
-  <si>
-    <t>FBA79116</t>
-  </si>
-  <si>
     <t>FBA79615</t>
   </si>
   <si>
@@ -141,9 +135,6 @@
     <t>FBK79788</t>
   </si>
   <si>
-    <t>FBK79789</t>
-  </si>
-  <si>
     <t>FBK79791</t>
   </si>
   <si>
@@ -189,9 +180,6 @@
     <t>B0DQ4YWSMC</t>
   </si>
   <si>
-    <t>B0BYHHSLPC</t>
-  </si>
-  <si>
     <t>B0DP2Z5DQ9</t>
   </si>
   <si>
@@ -210,9 +198,6 @@
     <t>B0FN4D3C89</t>
   </si>
   <si>
-    <t>B0FN4DSQ6P</t>
-  </si>
-  <si>
     <t>B0FN4HDM6Z</t>
   </si>
   <si>
@@ -279,9 +264,6 @@
     <t>WM-HA2M-BK</t>
   </si>
   <si>
-    <t>WM-LODN-BK</t>
-  </si>
-  <si>
     <t>WM1ML</t>
   </si>
   <si>
@@ -318,16 +300,10 @@
     <t>TVCT1ML</t>
   </si>
   <si>
-    <t>TVMF1ML</t>
-  </si>
-  <si>
     <t>TVLF1ML</t>
   </si>
   <si>
     <t>TVFM1ML</t>
-  </si>
-  <si>
-    <t>TC777 Pro</t>
   </si>
   <si>
     <t>1P</t>
@@ -341,7 +317,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -388,25 +364,13 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF1F2937"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF1F2937"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -422,12 +386,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -462,7 +420,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -482,14 +440,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -498,10 +450,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -511,7 +463,17 @@
     <cellStyle name="Normal 2" xfId="2" xr:uid="{697FC575-8A7C-4715-A8F0-2950C62D8576}"/>
     <cellStyle name="Normal 6" xfId="1" xr:uid="{E5F241CE-C0FC-4730-81C9-F1901EB82A3C}"/>
   </cellStyles>
-  <dxfs count="26">
+  <dxfs count="27">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1110,7 +1072,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}">
-  <dimension ref="A1:L45"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.88671875" style="1" bestFit="1" customWidth="1"/>
@@ -1171,19 +1133,19 @@
         <v>17</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="I2" s="14">
+        <v>55</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I2" s="3">
         <v>1</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1191,19 +1153,19 @@
         <v>23</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="I3" s="14">
+        <v>55</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I3" s="3">
         <v>1</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1211,19 +1173,19 @@
         <v>20</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="I4" s="14">
+        <v>55</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="I4" s="3">
         <v>15</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1231,39 +1193,39 @@
         <v>18</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="I5" s="14">
+        <v>55</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I5" s="3">
         <v>8</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="I6" s="14">
+        <v>55</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I6" s="3">
         <v>1</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1271,19 +1233,19 @@
         <v>19</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="I7" s="14">
+        <v>55</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="I7" s="3">
         <v>3</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1291,19 +1253,19 @@
         <v>12</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="I8" s="14">
-        <v>357</v>
+        <v>55</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I8" s="3">
+        <v>244</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1311,19 +1273,19 @@
         <v>21</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="I9" s="14">
-        <v>345</v>
+        <v>55</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="I9" s="3">
+        <v>337</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1331,19 +1293,19 @@
         <v>13</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="I10" s="14">
-        <v>585</v>
+        <v>55</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I10" s="3">
+        <v>573</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1351,705 +1313,626 @@
         <v>22</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="I11" s="14">
-        <v>66</v>
+        <v>55</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I11" s="3">
+        <v>28</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="I12" s="14">
-        <v>15</v>
+        <v>55</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="I12" s="3">
+        <v>3</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="I13" s="14">
-        <v>3</v>
+        <v>55</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I13" s="3">
+        <v>58</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="I14" s="14">
-        <v>172</v>
+        <v>55</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="I14" s="3">
+        <v>281</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="I15" s="14">
-        <v>281</v>
+        <v>55</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="I15" s="3">
+        <v>4</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="I16" s="3">
+        <v>140</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="I17" s="3">
+        <v>12</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="I16" s="14">
-        <v>4</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="I17" s="14">
-        <v>153</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
-        <v>24</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>49</v>
       </c>
       <c r="C18" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I18" s="3">
+        <v>8</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="B19" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="I19" s="3">
+        <v>18</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I20" s="3">
+        <v>82</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="I21" s="3">
+        <v>494</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I22" s="3">
+        <v>4</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="I23" s="3">
+        <v>687</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="I24" s="3">
+        <v>610</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="I25" s="9">
+        <v>2</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="I26" s="9">
+        <v>3</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="I27" s="9">
+        <v>4</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="I28" s="9">
+        <v>5</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I29" s="10">
+        <v>5</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="I30" s="10">
+        <v>4</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="I31" s="10">
+        <v>3</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="I32" s="10">
+        <v>2</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B33" t="s">
+        <v>34</v>
+      </c>
+      <c r="C33" t="s">
+        <v>55</v>
+      </c>
+      <c r="I33">
+        <v>83</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B34" t="s">
+        <v>38</v>
+      </c>
+      <c r="C34" t="s">
+        <v>55</v>
+      </c>
+      <c r="I34">
+        <v>57</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B35" t="s">
+        <v>44</v>
+      </c>
+      <c r="C35" t="s">
+        <v>55</v>
+      </c>
+      <c r="I35">
+        <v>18</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B36" t="s">
+        <v>37</v>
+      </c>
+      <c r="C36" t="s">
+        <v>55</v>
+      </c>
+      <c r="I36">
+        <v>93</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B37" t="s">
+        <v>43</v>
+      </c>
+      <c r="C37" t="s">
+        <v>55</v>
+      </c>
+      <c r="I37">
+        <v>3</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B38" t="s">
+        <v>36</v>
+      </c>
+      <c r="C38" t="s">
+        <v>55</v>
+      </c>
+      <c r="I38">
+        <v>4</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B39" t="s">
+        <v>35</v>
+      </c>
+      <c r="C39" t="s">
+        <v>55</v>
+      </c>
+      <c r="I39">
+        <v>15</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I40" s="7">
+        <v>1000</v>
+      </c>
+      <c r="J40" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D41" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="I18" s="14">
-        <v>12</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="I19" s="14">
-        <v>8</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="I20" s="14">
-        <v>18</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="I21" s="14">
-        <v>97</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="I22" s="14">
-        <v>542</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="I23" s="14">
-        <v>6</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="I24" s="14">
-        <v>52</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="I25" s="14">
-        <v>687</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="I26" s="14">
-        <v>610</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="D27" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="I27" s="11">
-        <v>4</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="C28" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="I28" s="11">
-        <v>2</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B29" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="I29" s="11">
-        <v>3</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B30" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="I30" s="11">
-        <v>4</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="C31" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="D31" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="I31" s="11">
-        <v>5</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D32" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="I32" s="8">
-        <v>1000</v>
-      </c>
-      <c r="J32" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="K32" s="7"/>
-    </row>
-    <row r="33" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B33" s="4" t="s">
+      <c r="I41" s="7">
+        <v>1008</v>
+      </c>
+      <c r="J41" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C33" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D33" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="I33" s="8">
-        <v>1008</v>
-      </c>
-      <c r="J33" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="K33" s="7"/>
-    </row>
-    <row r="34" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I34" s="3">
-        <v>5</v>
-      </c>
-      <c r="J34" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="K34" s="9"/>
-    </row>
-    <row r="35" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="I35" s="3">
-        <v>4</v>
-      </c>
-      <c r="J35" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="K35" s="9"/>
-    </row>
-    <row r="36" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="I36" s="3">
-        <v>3</v>
-      </c>
-      <c r="J36" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="K36" s="9"/>
-    </row>
-    <row r="37" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I37" s="3">
-        <v>2</v>
-      </c>
-      <c r="J37" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="K37" s="9"/>
-    </row>
-    <row r="38" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B38" t="s">
-        <v>46</v>
-      </c>
-      <c r="C38" t="s">
-        <v>60</v>
-      </c>
-      <c r="I38">
-        <v>3</v>
-      </c>
-      <c r="J38" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B39" t="s">
-        <v>47</v>
-      </c>
-      <c r="C39" t="s">
-        <v>60</v>
-      </c>
-      <c r="I39">
-        <v>13</v>
-      </c>
-      <c r="J39" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B40" t="s">
-        <v>38</v>
-      </c>
-      <c r="C40" t="s">
-        <v>60</v>
-      </c>
-      <c r="I40">
-        <v>17</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B41" t="s">
-        <v>39</v>
-      </c>
-      <c r="C41" t="s">
-        <v>60</v>
-      </c>
-      <c r="I41">
-        <v>4</v>
-      </c>
-      <c r="J41" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B42" t="s">
-        <v>52</v>
-      </c>
-      <c r="C42" t="s">
-        <v>60</v>
-      </c>
-      <c r="I42">
-        <v>3</v>
-      </c>
-      <c r="J42" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B43" t="s">
-        <v>41</v>
-      </c>
-      <c r="C43" t="s">
-        <v>60</v>
-      </c>
-      <c r="I43">
-        <v>69</v>
-      </c>
-      <c r="J43" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B44" t="s">
-        <v>40</v>
-      </c>
-      <c r="C44" t="s">
-        <v>60</v>
-      </c>
-      <c r="I44">
-        <v>117</v>
-      </c>
-      <c r="J44" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B45" t="s">
-        <v>37</v>
-      </c>
-      <c r="C45" t="s">
-        <v>60</v>
-      </c>
-      <c r="I45">
-        <v>40</v>
-      </c>
-      <c r="J45" s="1" t="s">
-        <v>97</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L45" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}"/>
+  <autoFilter ref="A1:L41" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="25" priority="2134"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="2241"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D32">
-    <cfRule type="duplicateValues" dxfId="24" priority="68"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="69"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="70"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="72"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="73"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="74" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="75" stopIfTrue="1"/>
+  <conditionalFormatting sqref="D40">
+    <cfRule type="duplicateValues" dxfId="25" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="68" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="69" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D33">
-    <cfRule type="duplicateValues" dxfId="16" priority="60"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="61"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="63"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="64"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="65"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="66" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="67" stopIfTrue="1"/>
+  <conditionalFormatting sqref="D41">
+    <cfRule type="duplicateValues" dxfId="17" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="60" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="61" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
-    <cfRule type="duplicateValues" dxfId="8" priority="2345"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="2346" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="2452"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="2453" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="duplicateValues" dxfId="6" priority="2132"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="2133" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="2239"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="2240" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:L1">
-    <cfRule type="duplicateValues" dxfId="4" priority="2130"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="2131" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="2237"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="2238" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A34:A37">
-    <cfRule type="duplicateValues" dxfId="2" priority="2408"/>
+  <conditionalFormatting sqref="A40:A41">
+    <cfRule type="duplicateValues" dxfId="3" priority="2519"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A32:A33">
-    <cfRule type="duplicateValues" dxfId="1" priority="2409"/>
+  <conditionalFormatting sqref="A29:A32">
+    <cfRule type="duplicateValues" dxfId="2" priority="2528"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2529"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A26">
-    <cfRule type="duplicateValues" dxfId="0" priority="2412"/>
+  <conditionalFormatting sqref="A2:A24">
+    <cfRule type="duplicateValues" dxfId="0" priority="2532"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/input/Inventory_snapshot_WM.xlsx
+++ b/data/input/Inventory_snapshot_WM.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 29\White_Mulberry\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\Nitesh Gdrive\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 30\White_Mulberry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6025F7A6-FDA6-42F2-864C-76D3ACDD785C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB03A3B9-76DB-4FC7-9F6E-D3BBF14B1F09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D49B0F4C-5F9E-467E-8AD9-9E638F42404F}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="93">
   <si>
     <t>SKU</t>
   </si>
@@ -135,6 +135,9 @@
     <t>FBK79788</t>
   </si>
   <si>
+    <t>FBK79789</t>
+  </si>
+  <si>
     <t>FBK79791</t>
   </si>
   <si>
@@ -198,6 +201,9 @@
     <t>B0FN4D3C89</t>
   </si>
   <si>
+    <t>B0FN4DSQ6P</t>
+  </si>
+  <si>
     <t>B0FN4HDM6Z</t>
   </si>
   <si>
@@ -298,6 +304,9 @@
   </si>
   <si>
     <t>TVCT1ML</t>
+  </si>
+  <si>
+    <t>TVMF1ML</t>
   </si>
   <si>
     <t>TVLF1ML</t>
@@ -526,46 +535,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -664,6 +633,46 @@
       <font>
         <condense val="0"/>
         <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1133,19 +1142,19 @@
         <v>17</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I2" s="3">
         <v>1</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1153,19 +1162,19 @@
         <v>23</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I3" s="3">
         <v>1</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1173,19 +1182,19 @@
         <v>20</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I4" s="3">
         <v>15</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1193,39 +1202,39 @@
         <v>18</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I5" s="3">
         <v>8</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I6" s="3">
         <v>1</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1233,19 +1242,19 @@
         <v>19</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I7" s="3">
         <v>3</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1253,19 +1262,19 @@
         <v>12</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I8" s="3">
-        <v>244</v>
+        <v>209</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1273,19 +1282,19 @@
         <v>21</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I9" s="3">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1293,19 +1302,19 @@
         <v>13</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I10" s="3">
         <v>573</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1313,19 +1322,19 @@
         <v>22</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I11" s="3">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1333,219 +1342,219 @@
         <v>14</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I12" s="3">
         <v>3</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I13" s="3">
-        <v>58</v>
+        <v>254</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I14" s="3">
-        <v>281</v>
+        <v>4</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I15" s="3">
-        <v>4</v>
+        <v>137</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I16" s="3">
-        <v>140</v>
+        <v>12</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I17" s="3">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I18" s="3">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D19" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I19" s="3">
         <v>82</v>
       </c>
-      <c r="I19" s="3">
-        <v>18</v>
-      </c>
       <c r="J19" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I20" s="3">
-        <v>82</v>
+        <v>494</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="I21" s="3">
-        <v>494</v>
+        <v>4</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>54</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I22" s="3">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1553,39 +1562,39 @@
         <v>27</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I23" s="3">
-        <v>687</v>
+        <v>623</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I24" s="3">
         <v>610</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1593,19 +1602,19 @@
         <v>16</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I25" s="9">
         <v>2</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1613,19 +1622,19 @@
         <v>25</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I26" s="9">
         <v>3</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1633,19 +1642,19 @@
         <v>14</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I27" s="9">
         <v>4</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1653,19 +1662,19 @@
         <v>15</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I28" s="9">
         <v>5</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1673,19 +1682,19 @@
         <v>12</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I29" s="10">
         <v>5</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1693,19 +1702,19 @@
         <v>13</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I30" s="10">
         <v>4</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1713,19 +1722,19 @@
         <v>25</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I31" s="10">
         <v>3</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1733,103 +1742,115 @@
         <v>16</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I32" s="10">
         <v>2</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" t="s">
-        <v>34</v>
-      </c>
-      <c r="C33" t="s">
-        <v>55</v>
-      </c>
-      <c r="I33">
-        <v>83</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>89</v>
+      <c r="A33" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="I33" s="7">
+        <v>1000</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" t="s">
-        <v>38</v>
-      </c>
-      <c r="C34" t="s">
-        <v>55</v>
-      </c>
-      <c r="I34">
-        <v>57</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>89</v>
+      <c r="A34" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="I34" s="7">
+        <v>1008</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C35" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I35">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C36" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I36">
-        <v>93</v>
+        <v>29</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C37" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I37">
         <v>3</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C38" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I38">
-        <v>4</v>
+        <v>138</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1837,102 +1858,90 @@
         <v>35</v>
       </c>
       <c r="C39" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I39">
-        <v>15</v>
+        <v>138</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D40" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="I40" s="7">
-        <v>1000</v>
-      </c>
-      <c r="J40" s="6" t="s">
-        <v>56</v>
+      <c r="B40" t="s">
+        <v>39</v>
+      </c>
+      <c r="C40" t="s">
+        <v>57</v>
+      </c>
+      <c r="I40">
+        <v>61</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D41" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="I41" s="7">
-        <v>1008</v>
-      </c>
-      <c r="J41" s="6" t="s">
-        <v>56</v>
+      <c r="B41" t="s">
+        <v>44</v>
+      </c>
+      <c r="C41" t="s">
+        <v>57</v>
+      </c>
+      <c r="I41">
+        <v>5</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L41" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}"/>
   <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="A2:A24">
+    <cfRule type="duplicateValues" dxfId="26" priority="2652"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A29:A32">
+    <cfRule type="duplicateValues" dxfId="25" priority="2648"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="2649"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A33:A34">
+    <cfRule type="duplicateValues" dxfId="23" priority="2641"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="26" priority="2241"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="2365"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D40">
-    <cfRule type="duplicateValues" dxfId="25" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="63"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="64"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="65"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="66"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="67"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="68" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="69" stopIfTrue="1"/>
+  <conditionalFormatting sqref="D33">
+    <cfRule type="duplicateValues" dxfId="21" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="80" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="81" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D41">
-    <cfRule type="duplicateValues" dxfId="17" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="57"/>
+  <conditionalFormatting sqref="D34">
     <cfRule type="duplicateValues" dxfId="13" priority="58"/>
     <cfRule type="duplicateValues" dxfId="12" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="60" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="61" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="64" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="65" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
-    <cfRule type="duplicateValues" dxfId="9" priority="2452"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="2453" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="2576"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="2577" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="duplicateValues" dxfId="7" priority="2239"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="2240" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="2363"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2364" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:L1">
-    <cfRule type="duplicateValues" dxfId="5" priority="2237"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="2238" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A40:A41">
-    <cfRule type="duplicateValues" dxfId="3" priority="2519"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A29:A32">
-    <cfRule type="duplicateValues" dxfId="2" priority="2528"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="2529"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A24">
-    <cfRule type="duplicateValues" dxfId="0" priority="2532"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2361"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2362" stopIfTrue="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/input/Inventory_snapshot_WM.xlsx
+++ b/data/input/Inventory_snapshot_WM.xlsx
@@ -1785,12 +1785,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FBA79612</t>
+          <t>FBA79477</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>WM1ML</t>
+          <t>WM-GS2M-BK</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -1808,11 +1808,11 @@
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -1821,12 +1821,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>FBK79788</t>
+          <t>FBA79479</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>B0FN4D3C89</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>TVCT1ML</t>
+          <t>WM-HA2M-BK</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -1844,11 +1844,11 @@
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="n">
-        <v>1008</v>
+        <v>700</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -1857,12 +1857,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FBA79476</t>
+          <t>FBK79789</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0FN4DSQ6P</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>WM-GS1M-BK</t>
+          <t>TVMF1ML</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -1880,7 +1880,7 @@
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="n">
-        <v>1000</v>
+        <v>1008</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -1893,12 +1893,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>FBA79477</t>
+          <t>FBA79613</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DP2VVRND</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>WM-GS2M-BK</t>
+          <t>MS1ML</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -1916,7 +1916,7 @@
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -1929,12 +1929,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FBA79479</t>
+          <t>FBA79617</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>WM-HA2M-BK</t>
+          <t>HDWF1ML</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -1952,7 +1952,7 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -2001,12 +2001,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>FBA79613</t>
+          <t>FBA79612</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>B0DP2VVRND</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>MS1ML</t>
+          <t>WM1ML</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -2037,12 +2037,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FBA79617</t>
+          <t>FBA79476</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>HDWF1ML</t>
+          <t>WM-GS1M-BK</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -2060,7 +2060,7 @@
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2073,12 +2073,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FBK79789</t>
+          <t>FBK79788</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>B0FN4DSQ6P</t>
+          <t>B0FN4D3C89</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>TVMF1ML</t>
+          <t>TVCT1ML</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>

--- a/data/input/Inventory_snapshot_WM.xlsx
+++ b/data/input/Inventory_snapshot_WM.xlsx
@@ -479,10 +479,14 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>FBA76382</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0BF4T7SWK</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -492,7 +496,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>WM-GS2M-BK</t>
+          <t>WM-MH05P-BK</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -500,21 +504,25 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1P</t>
+          <t>AMPM</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FBA79659</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DQ1NV8D2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -524,7 +532,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>WM-GS1M-BK</t>
+          <t>WM-MDL-BK</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -532,21 +540,25 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>84</v>
+        <v>1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1P</t>
+          <t>AMPM</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FBA79175</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0CPT2YJX2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -556,7 +568,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>WM-HA2M-BK</t>
+          <t>WM-SMD09-WH</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -564,21 +576,25 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1P</t>
+          <t>AMPM</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FBA76415</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -588,7 +604,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>WM1ML</t>
+          <t>WM-LOD-CF</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -596,21 +612,25 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1P</t>
+          <t>AMPM</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FBA76408</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0BFBLLZJG</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -620,7 +640,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>WM-HA1M-BK</t>
+          <t>6780-4679-WHT-SIOC</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -628,21 +648,25 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1P</t>
+          <t>AMPM</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FBA76418</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0BFVNS8HS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -652,7 +676,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>HDWF1ML</t>
+          <t>WM-LOD-IN</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -660,21 +684,25 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>120</v>
+        <v>3</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1P</t>
+          <t>AMPM</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FBA79477</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B0DP2VVRND</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -684,7 +712,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MS1ML</t>
+          <t>WM-GS2M-BK</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -692,11 +720,11 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>200</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1P</t>
+          <t>AMPM</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -705,12 +733,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FBA76382</t>
+          <t>FBA79478</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>B0BF4T7SWK</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -720,7 +748,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>WM-MH05P-BK</t>
+          <t>WM-HA1M-BK</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -728,7 +756,7 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>573</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -741,12 +769,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FBA79659</t>
+          <t>FBA79479</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>B0DQ1NV8D2</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -756,7 +784,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>WM-MDL-BK</t>
+          <t>WM-HA2M-BK</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -764,7 +792,7 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -777,12 +805,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FBA79175</t>
+          <t>FBA79612</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>B0CPT2YJX2</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -792,7 +820,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>WM-SMD09-WH</t>
+          <t>WM1ML</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -800,7 +828,7 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -813,12 +841,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79615</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -828,7 +856,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>WM-LOD-CF</t>
+          <t>VLMS1ML</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -836,7 +864,7 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>8</v>
+        <v>194</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -849,12 +877,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FBA76408</t>
+          <t>FBA79616</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>B0BFBLLZJG</t>
+          <t>B0DP3194QN</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -864,7 +892,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6780-4679-WHT-SIOC</t>
+          <t>HD1ML</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -872,7 +900,7 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -885,12 +913,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FBA76418</t>
+          <t>FBA79617</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>B0BFVNS8HS</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -900,7 +928,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>WM-LOD-IN</t>
+          <t>HDWF1ML</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -908,7 +936,7 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -921,12 +949,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FBA79477</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -936,7 +964,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>WM-GS2M-BK</t>
+          <t>WM-MODL-WH</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -944,7 +972,7 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>205</v>
+        <v>12</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -957,12 +985,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FBA79478</t>
+          <t>FBK79784</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0FN4FHH5Y</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -972,7 +1000,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>WM-HA1M-BK</t>
+          <t>POS2M</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -980,7 +1008,7 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>573</v>
+        <v>8</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -993,12 +1021,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FBA79479</t>
+          <t>FBK79785</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0FN4HDBN5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1008,7 +1036,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>WM-HA2M-BK</t>
+          <t>POS2MK</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -1016,7 +1044,7 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1029,12 +1057,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FBA79612</t>
+          <t>FBK79786</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0FN4FPJ83</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1044,7 +1072,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>WM1ML</t>
+          <t>POS BRACKET</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -1052,7 +1080,7 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>6</v>
+        <v>85</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1065,12 +1093,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FBA79615</t>
+          <t>FBK79787</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0FN4GQ9HT</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1080,7 +1108,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VLMS1ML</t>
+          <t>TVCF1ML</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -1088,7 +1116,7 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1101,12 +1129,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FBA79616</t>
+          <t>FBK79793</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>B0DP3194QN</t>
+          <t>B0FN81FD8M</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1116,7 +1144,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>HD1ML</t>
+          <t>HDGS1ML</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -1124,7 +1152,7 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1137,12 +1165,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FBA79617</t>
+          <t>FBK79789</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0FN4DSQ6P</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1152,7 +1180,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>HDWF1ML</t>
+          <t>TVMF1ML</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -1160,7 +1188,7 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1173,12 +1201,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA79790</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0FN4GJ9S1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1188,7 +1216,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>WM-MODL-WH</t>
+          <t>TVLF1ML</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -1196,7 +1224,7 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>12</v>
+        <v>583</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1209,12 +1237,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FBK79784</t>
+          <t>FBK79791</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>B0FN4FHH5Y</t>
+          <t>B0FN4HDM6Z</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1224,7 +1252,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>POS2M</t>
+          <t>TVFM1ML</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -1232,7 +1260,7 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>8</v>
+        <v>544</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1245,12 +1273,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FBK79785</t>
+          <t>FBA79476</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>B0FN4HDBN5</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1260,7 +1288,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>POS2MK</t>
+          <t>WM-GS1M-BK</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -1268,11 +1296,11 @@
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1281,12 +1309,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FBK79786</t>
+          <t>FBA79478</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>B0FN4FPJ83</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1296,7 +1324,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>POS BRACKET</t>
+          <t>WM-HA1M-BK</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -1304,11 +1332,11 @@
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>85</v>
+        <v>4</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1317,12 +1345,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FBK79787</t>
+          <t>FBA79615</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>B0FN4GQ9HT</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1332,7 +1360,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>TVCF1ML</t>
+          <t>VLMS1ML</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -1340,11 +1368,11 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>470</v>
+        <v>3</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -1353,12 +1381,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FBK79793</t>
+          <t>FBA79617</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>B0FN81FD8M</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1368,7 +1396,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>HDGS1ML</t>
+          <t>HDWF1ML</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
@@ -1376,11 +1404,11 @@
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -1389,12 +1417,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FBK79789</t>
+          <t>FBA79617</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>B0FN4DSQ6P</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1404,7 +1432,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>TVMF1ML</t>
+          <t>HDWF1ML</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -1412,11 +1440,11 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -1425,12 +1453,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FBA79790</t>
+          <t>FBA79615</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>B0FN4GJ9S1</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1440,7 +1468,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>TVLF1ML</t>
+          <t>VLMS1ML</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -1448,11 +1476,11 @@
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>583</v>
+        <v>3</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -1461,12 +1489,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>FBK79791</t>
+          <t>FBA79612</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>B0FN4HDM6Z</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1476,7 +1504,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>TVFM1ML</t>
+          <t>WM1ML</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -1484,11 +1512,11 @@
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>592</v>
+        <v>4</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -1497,12 +1525,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>FBA79617</t>
+          <t>FBA79613</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DP2VVRND</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1512,7 +1540,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>HDWF1ML</t>
+          <t>MS1ML</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -1520,25 +1548,21 @@
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>FBA79615</t>
-        </is>
-      </c>
+      <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1548,7 +1572,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VLMS1ML</t>
+          <t>WM1ML</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -1560,21 +1584,17 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>1P</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>FBA79612</t>
-        </is>
-      </c>
+      <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1584,7 +1604,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>WM1ML</t>
+          <t>WM-GS1M-BK</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -1592,25 +1612,21 @@
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>1P</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>FBA79613</t>
-        </is>
-      </c>
+      <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>B0DP2VVRND</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1620,7 +1636,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>MS1ML</t>
+          <t>WM-GS2M-BK</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -1628,25 +1644,21 @@
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>1P</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>FBA79476</t>
-        </is>
-      </c>
+      <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1656,7 +1668,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>WM-GS1M-BK</t>
+          <t>WM-HA2M-BK</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -1664,25 +1676,21 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>1P</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>FBA79478</t>
-        </is>
-      </c>
+      <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DP2VVRND</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1692,7 +1700,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>WM-HA1M-BK</t>
+          <t>MS1ML</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -1700,25 +1708,21 @@
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>1P</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>FBA79615</t>
-        </is>
-      </c>
+      <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1728,7 +1732,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VLMS1ML</t>
+          <t>WM-HA1M-BK</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -1736,22 +1740,18 @@
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>1P</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>FBA79617</t>
-        </is>
-      </c>
+      <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
           <t>B0DP32F346</t>
@@ -1772,11 +1772,11 @@
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>111</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>1P</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>

--- a/data/input/Inventory_snapshot_WM.xlsx
+++ b/data/input/Inventory_snapshot_WM.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L47"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,12 +661,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FBA76418</t>
+          <t>FBA79477</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>B0BFVNS8HS</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>WM-LOD-IN</t>
+          <t>WM-GS2M-BK</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -684,7 +684,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>200</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -697,12 +697,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FBA79477</t>
+          <t>FBA79478</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>WM-GS2M-BK</t>
+          <t>WM-HA1M-BK</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -720,7 +720,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>200</v>
+        <v>573</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -733,12 +733,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FBA79478</t>
+          <t>FBA79479</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>WM-HA1M-BK</t>
+          <t>WM-HA2M-BK</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -756,7 +756,7 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>573</v>
+        <v>4</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -769,12 +769,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FBA79479</t>
+          <t>FBA79612</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>WM-HA2M-BK</t>
+          <t>WM1ML</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -792,7 +792,7 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -805,12 +805,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FBA79612</t>
+          <t>FBA79615</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>WM1ML</t>
+          <t>VLMS1ML</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -828,7 +828,7 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>194</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -841,12 +841,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FBA79615</t>
+          <t>FBA79617</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VLMS1ML</t>
+          <t>HDWF1ML</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -864,7 +864,7 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>194</v>
+        <v>20</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -877,12 +877,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FBA79616</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>B0DP3194QN</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HD1ML</t>
+          <t>WM-MODL-WH</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -900,7 +900,7 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -913,12 +913,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FBA79617</t>
+          <t>FBK79784</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0FN4FHH5Y</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>HDWF1ML</t>
+          <t>POS2M</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -936,7 +936,7 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -949,12 +949,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBK79785</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0FN4HDBN5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>WM-MODL-WH</t>
+          <t>POS2MK</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -972,7 +972,7 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -985,12 +985,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FBK79784</t>
+          <t>FBK79786</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>B0FN4FHH5Y</t>
+          <t>B0FN4FPJ83</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>POS2M</t>
+          <t>POS BRACKET</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1021,12 +1021,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FBK79785</t>
+          <t>FBK79787</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>B0FN4HDBN5</t>
+          <t>B0FN4GQ9HT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>POS2MK</t>
+          <t>TVCF1ML</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -1044,7 +1044,7 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>18</v>
+        <v>230</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1057,12 +1057,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FBK79786</t>
+          <t>FBK79793</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>B0FN4FPJ83</t>
+          <t>B0FN81FD8M</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>POS BRACKET</t>
+          <t>HDGS1ML</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -1080,7 +1080,7 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>85</v>
+        <v>10</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1093,12 +1093,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FBK79787</t>
+          <t>FBK79789</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>B0FN4GQ9HT</t>
+          <t>B0FN4DSQ6P</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>TVCF1ML</t>
+          <t>TVMF1ML</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -1116,7 +1116,7 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>230</v>
+        <v>5</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1129,12 +1129,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FBK79793</t>
+          <t>FBA79790</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>B0FN81FD8M</t>
+          <t>B0FN4GJ9S1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>HDGS1ML</t>
+          <t>TVLF1ML</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -1152,7 +1152,7 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>10</v>
+        <v>551</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1165,12 +1165,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FBK79789</t>
+          <t>FBK79791</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>B0FN4DSQ6P</t>
+          <t>B0FN4HDM6Z</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>TVMF1ML</t>
+          <t>TVFM1ML</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -1188,7 +1188,7 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>5</v>
+        <v>514</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1201,12 +1201,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FBA79790</t>
+          <t>FBA79476</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>B0FN4GJ9S1</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>TVLF1ML</t>
+          <t>WM-GS1M-BK</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -1224,11 +1224,11 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>583</v>
+        <v>5</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1237,12 +1237,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FBK79791</t>
+          <t>FBA79478</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>B0FN4HDM6Z</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>TVFM1ML</t>
+          <t>WM-HA1M-BK</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -1260,11 +1260,11 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>544</v>
+        <v>4</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1273,12 +1273,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FBA79476</t>
+          <t>FBA79615</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>WM-GS1M-BK</t>
+          <t>VLMS1ML</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -1296,7 +1296,7 @@
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1309,12 +1309,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FBA79478</t>
+          <t>FBA79617</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>WM-HA1M-BK</t>
+          <t>HDWF1ML</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -1332,7 +1332,7 @@
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1345,12 +1345,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FBA79615</t>
+          <t>FBA79617</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VLMS1ML</t>
+          <t>HDWF1ML</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -1368,11 +1368,11 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -1381,12 +1381,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FBA79617</t>
+          <t>FBA79615</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>HDWF1ML</t>
+          <t>VLMS1ML</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
@@ -1404,11 +1404,11 @@
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -1417,12 +1417,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FBA79617</t>
+          <t>FBA79612</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>HDWF1ML</t>
+          <t>WM1ML</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -1440,7 +1440,7 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1453,12 +1453,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FBA79615</t>
+          <t>FBA79613</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DP2VVRND</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VLMS1ML</t>
+          <t>MS1ML</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -1476,7 +1476,7 @@
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1487,14 +1487,10 @@
       <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>FBA79612</t>
-        </is>
-      </c>
+      <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DP2VVRND</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1504,7 +1500,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>WM1ML</t>
+          <t>MS1ML</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -1512,25 +1508,21 @@
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>1P</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>FBA79613</t>
-        </is>
-      </c>
+      <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>B0DP2VVRND</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1540,7 +1532,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>MS1ML</t>
+          <t>WM-GS2M-BK</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -1548,11 +1540,11 @@
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>1P</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -1562,7 +1554,7 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1572,7 +1564,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>WM1ML</t>
+          <t>WM-HA1M-BK</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -1580,7 +1572,7 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -1594,7 +1586,7 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1604,7 +1596,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>WM-GS1M-BK</t>
+          <t>WM1ML</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -1612,7 +1604,7 @@
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -1626,7 +1618,7 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1636,7 +1628,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>WM-GS2M-BK</t>
+          <t>HDWF1ML</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -1644,7 +1636,7 @@
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -1658,7 +1650,7 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1668,7 +1660,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>WM-HA2M-BK</t>
+          <t>WM-GS1M-BK</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -1676,7 +1668,7 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -1687,10 +1679,14 @@
       <c r="L35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>FBA79477</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>B0DP2VVRND</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1700,7 +1696,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>MS1ML</t>
+          <t>WM-GS2M-BK</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -1708,21 +1704,25 @@
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
-        <v>6</v>
+        <v>500</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1P</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>FBA79479</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>WM-HA1M-BK</t>
+          <t>WM-HA2M-BK</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -1740,21 +1740,25 @@
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
-        <v>21</v>
+        <v>700</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1P</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>FBK79789</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0FN4DSQ6P</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1764,7 +1768,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>HDWF1ML</t>
+          <t>TVMF1ML</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -1772,11 +1776,11 @@
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
-        <v>111</v>
+        <v>1008</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>1P</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -1785,12 +1789,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FBA79477</t>
+          <t>FBA79613</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DP2VVRND</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1800,7 +1804,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>WM-GS2M-BK</t>
+          <t>MS1ML</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -1808,7 +1812,7 @@
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -1821,12 +1825,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>FBA79479</t>
+          <t>FBA79617</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1836,7 +1840,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>WM-HA2M-BK</t>
+          <t>HDWF1ML</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -1844,7 +1848,7 @@
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -1857,12 +1861,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FBK79789</t>
+          <t>FBA79476</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>B0FN4DSQ6P</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1872,7 +1876,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>TVMF1ML</t>
+          <t>WM-GS1M-BK</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -1880,7 +1884,7 @@
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="n">
-        <v>1008</v>
+        <v>1000</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -1893,12 +1897,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>FBA79613</t>
+          <t>FBA79612</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>B0DP2VVRND</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1908,7 +1912,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>MS1ML</t>
+          <t>WM1ML</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -1920,7 +1924,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -1929,12 +1933,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FBA79617</t>
+          <t>FBA79612</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1944,7 +1948,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>HDWF1ML</t>
+          <t>WM1ML</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -1952,7 +1956,7 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -1965,12 +1969,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FBA79612</t>
+          <t>FBK79788</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0FN4D3C89</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1980,7 +1984,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>WM1ML</t>
+          <t>TVCT1ML</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -1988,7 +1992,7 @@
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="n">
-        <v>1000</v>
+        <v>1008</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -1997,114 +2001,6 @@
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>FBA79612</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>B0DP2WC5VW</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>WM1ML</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>Open Order</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>FBA79476</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>B0DB5VG39T</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>WM-GS1M-BK</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Open Order</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>FBK79788</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>B0FN4D3C89</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>TVCT1ML</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="n">
-        <v>1008</v>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/input/Inventory_snapshot_WM.xlsx
+++ b/data/input/Inventory_snapshot_WM.xlsx
@@ -517,12 +517,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FBA79659</t>
+          <t>FBA79175</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>B0DQ1NV8D2</t>
+          <t>B0CPT2YJX2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -532,7 +532,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>WM-MDL-BK</t>
+          <t>WM-SMD09-WH</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -540,7 +540,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -553,12 +553,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FBA79175</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>B0CPT2YJX2</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>WM-SMD09-WH</t>
+          <t>WM-LOD-CF</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -576,7 +576,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -589,12 +589,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA76408</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFBLLZJG</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -604,7 +604,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>WM-LOD-CF</t>
+          <t>6780-4679-WHT-SIOC</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -612,7 +612,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -625,12 +625,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FBA76408</t>
+          <t>FBA79477</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>B0BFBLLZJG</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6780-4679-WHT-SIOC</t>
+          <t>WM-GS2M-BK</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -648,7 +648,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -661,12 +661,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FBA79477</t>
+          <t>FBA79478</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>WM-GS2M-BK</t>
+          <t>WM-HA1M-BK</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -684,7 +684,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>200</v>
+        <v>573</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -697,12 +697,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FBA79478</t>
+          <t>FBA79479</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>WM-HA1M-BK</t>
+          <t>WM-HA2M-BK</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -720,7 +720,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>573</v>
+        <v>4</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -733,12 +733,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FBA79479</t>
+          <t>FBA79612</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>WM-HA2M-BK</t>
+          <t>WM1ML</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -756,7 +756,7 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>566</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -769,12 +769,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FBA79612</t>
+          <t>FBA79615</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>WM1ML</t>
+          <t>VLMS1ML</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -792,7 +792,7 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>6</v>
+        <v>194</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -805,12 +805,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FBA79615</t>
+          <t>FBA79617</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VLMS1ML</t>
+          <t>HDWF1ML</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -828,7 +828,7 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>194</v>
+        <v>20</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -841,12 +841,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FBA79617</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HDWF1ML</t>
+          <t>WM-MODL-WH</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -864,7 +864,7 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -877,12 +877,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBK79784</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0FN4FHH5Y</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>WM-MODL-WH</t>
+          <t>POS2M</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -900,7 +900,7 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -913,12 +913,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FBK79784</t>
+          <t>FBK79785</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>B0FN4FHH5Y</t>
+          <t>B0FN4HDBN5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>POS2M</t>
+          <t>POS2MK</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -936,7 +936,7 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -949,12 +949,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FBK79785</t>
+          <t>FBK79786</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>B0FN4HDBN5</t>
+          <t>B0FN4FPJ83</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>POS2MK</t>
+          <t>POS BRACKET</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -972,7 +972,7 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -985,12 +985,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FBK79786</t>
+          <t>FBK79787</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>B0FN4FPJ83</t>
+          <t>B0FN4GQ9HT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>POS BRACKET</t>
+          <t>TVCF1ML</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>70</v>
+        <v>230</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1021,12 +1021,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FBK79787</t>
+          <t>FBK79793</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>B0FN4GQ9HT</t>
+          <t>B0FN81FD8M</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>TVCF1ML</t>
+          <t>HDGS1ML</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -1044,7 +1044,7 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>230</v>
+        <v>10</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1057,12 +1057,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FBK79793</t>
+          <t>FBK79788</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>B0FN81FD8M</t>
+          <t>B0FN4D3C89</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>HDGS1ML</t>
+          <t>TVCT1ML</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -1080,7 +1080,7 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>10</v>
+        <v>756</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1201,12 +1201,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FBA79476</t>
+          <t>FBA79617</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>WM-GS1M-BK</t>
+          <t>HDWF1ML</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -1224,11 +1224,11 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1237,12 +1237,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FBA79478</t>
+          <t>FBA79615</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>WM-HA1M-BK</t>
+          <t>VLMS1ML</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -1260,11 +1260,11 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1273,12 +1273,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FBA79615</t>
+          <t>FBA79612</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VLMS1ML</t>
+          <t>WM1ML</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -1296,11 +1296,11 @@
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1309,12 +1309,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FBA79617</t>
+          <t>FBA79613</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DP2VVRND</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>HDWF1ML</t>
+          <t>MS1ML</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -1332,11 +1332,11 @@
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1345,12 +1345,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FBA79617</t>
+          <t>FBA79476</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>HDWF1ML</t>
+          <t>WM-GS1M-BK</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -1368,11 +1368,11 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -1381,12 +1381,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FBA79615</t>
+          <t>FBA79478</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VLMS1ML</t>
+          <t>WM-HA1M-BK</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
@@ -1404,11 +1404,11 @@
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -1417,12 +1417,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FBA79612</t>
+          <t>FBA79615</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>WM1ML</t>
+          <t>VLMS1ML</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -1440,11 +1440,11 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -1453,12 +1453,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FBA79613</t>
+          <t>FBA79617</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>B0DP2VVRND</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>MS1ML</t>
+          <t>HDWF1ML</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -1476,11 +1476,11 @@
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -1490,7 +1490,7 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>B0DP2VVRND</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>MS1ML</t>
+          <t>VLMS1ML</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -1508,7 +1508,7 @@
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>WM-GS2M-BK</t>
+          <t>WM1ML</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -1540,7 +1540,7 @@
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>WM1ML</t>
+          <t>HDWF1ML</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -1604,7 +1604,7 @@
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
-        <v>3</v>
+        <v>98</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>HDWF1ML</t>
+          <t>WM-GS2M-BK</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -1636,7 +1636,7 @@
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>

--- a/data/input/Inventory_snapshot_WM.xlsx
+++ b/data/input/Inventory_snapshot_WM.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -1933,12 +1933,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FBA79612</t>
+          <t>FBK79788</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0FN4D3C89</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>WM1ML</t>
+          <t>TVCT1ML</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -1956,51 +1956,15 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
-        <v>1000</v>
+        <v>1008</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>FBK79788</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>B0FN4D3C89</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>TVCT1ML</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="n">
-        <v>1008</v>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
